--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -641,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4094.21</v>
+        <v>4074.29</v>
       </c>
       <c r="C2" t="n">
-        <v>4103.93</v>
+        <v>4109.96</v>
       </c>
       <c r="D2" t="n">
-        <v>4077.87</v>
+        <v>4073.73</v>
       </c>
       <c r="E2" t="n">
-        <v>4091.89</v>
+        <v>4108.08</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.58</v>
+        <v>16.18</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.004</v>
       </c>
       <c r="H2" t="n">
-        <v>26.06</v>
+        <v>36.23</v>
       </c>
       <c r="I2" t="n">
-        <v>4004.96</v>
+        <v>4051.81</v>
       </c>
       <c r="J2" t="n">
-        <v>4061.55</v>
+        <v>4066.33</v>
       </c>
       <c r="K2" t="n">
-        <v>4073.42</v>
+        <v>4078.86</v>
       </c>
       <c r="L2" t="n">
-        <v>4085.29</v>
+        <v>4091.4</v>
       </c>
       <c r="M2" t="n">
-        <v>4119.52</v>
+        <v>4104.92</v>
       </c>
       <c r="N2" t="n">
-        <v>4153.75</v>
+        <v>4118.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4143.27</v>
+        <v>4129.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,16 +695,20 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -723,50 +730,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4074.29</v>
+        <v>4094.23</v>
       </c>
       <c r="C3" t="n">
-        <v>4109.96</v>
+        <v>4117.45</v>
       </c>
       <c r="D3" t="n">
-        <v>4073.73</v>
+        <v>4080.29</v>
       </c>
       <c r="E3" t="n">
-        <v>4108.08</v>
+        <v>4090.48</v>
       </c>
       <c r="F3" t="n">
-        <v>16.18</v>
+        <v>-17.6</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0043</v>
       </c>
       <c r="H3" t="n">
-        <v>36.23</v>
+        <v>37.16</v>
       </c>
       <c r="I3" t="n">
-        <v>4051.81</v>
+        <v>4037.51</v>
       </c>
       <c r="J3" t="n">
-        <v>4066.33</v>
+        <v>4079.97</v>
       </c>
       <c r="K3" t="n">
-        <v>4078.86</v>
+        <v>4089.96</v>
       </c>
       <c r="L3" t="n">
-        <v>4091.4</v>
+        <v>4099.96</v>
       </c>
       <c r="M3" t="n">
-        <v>4104.92</v>
+        <v>4126.19</v>
       </c>
       <c r="N3" t="n">
-        <v>4118.44</v>
+        <v>4152.42</v>
       </c>
       <c r="O3" t="n">
-        <v>4129.98</v>
+        <v>4146.18</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,18 +783,16 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -809,50 +814,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4094.23</v>
+        <v>4093.96</v>
       </c>
       <c r="C4" t="n">
-        <v>4117.45</v>
+        <v>4164.42</v>
       </c>
       <c r="D4" t="n">
-        <v>4080.29</v>
+        <v>4070.17</v>
       </c>
       <c r="E4" t="n">
-        <v>4090.48</v>
+        <v>4163.1</v>
       </c>
       <c r="F4" t="n">
-        <v>-17.6</v>
+        <v>72.62</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0178</v>
       </c>
       <c r="H4" t="n">
-        <v>37.16</v>
+        <v>94.25</v>
       </c>
       <c r="I4" t="n">
-        <v>4037.51</v>
+        <v>4043.14</v>
       </c>
       <c r="J4" t="n">
-        <v>4079.97</v>
+        <v>4049.13</v>
       </c>
       <c r="K4" t="n">
-        <v>4089.96</v>
+        <v>4071.9</v>
       </c>
       <c r="L4" t="n">
-        <v>4099.96</v>
+        <v>4094.68</v>
       </c>
       <c r="M4" t="n">
-        <v>4126.19</v>
+        <v>4109.06</v>
       </c>
       <c r="N4" t="n">
-        <v>4152.42</v>
+        <v>4123.44</v>
       </c>
       <c r="O4" t="n">
-        <v>4146.18</v>
+        <v>4154.61</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,22 +867,28 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -893,81 +904,77 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4093.96</v>
+        <v>4153.59</v>
       </c>
       <c r="C5" t="n">
-        <v>4164.42</v>
+        <v>4175.35</v>
       </c>
       <c r="D5" t="n">
-        <v>4070.17</v>
+        <v>4085.59</v>
       </c>
       <c r="E5" t="n">
-        <v>4163.1</v>
+        <v>4106.25</v>
       </c>
       <c r="F5" t="n">
-        <v>72.62</v>
+        <v>-56.85</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0178</v>
+        <v>-0.0137</v>
       </c>
       <c r="H5" t="n">
-        <v>94.25</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>4043.14</v>
+        <v>3975.93</v>
       </c>
       <c r="J5" t="n">
-        <v>4049.13</v>
+        <v>4091.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4071.9</v>
+        <v>4115.97</v>
       </c>
       <c r="L5" t="n">
-        <v>4094.68</v>
+        <v>4140.2</v>
       </c>
       <c r="M5" t="n">
-        <v>4109.06</v>
+        <v>4210.22</v>
       </c>
       <c r="N5" t="n">
-        <v>4123.44</v>
+        <v>4280.24</v>
       </c>
       <c r="O5" t="n">
-        <v>4154.61</v>
+        <v>4258.66</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -983,67 +990,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4153.59</v>
+        <v>4090.1</v>
       </c>
       <c r="C6" t="n">
-        <v>4175.35</v>
+        <v>4117.29</v>
       </c>
       <c r="D6" t="n">
-        <v>4085.59</v>
+        <v>4075.49</v>
       </c>
       <c r="E6" t="n">
-        <v>4106.25</v>
+        <v>4110.81</v>
       </c>
       <c r="F6" t="n">
-        <v>-56.85</v>
+        <v>4.56</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0137</v>
+        <v>0.0011</v>
       </c>
       <c r="H6" t="n">
-        <v>89.76000000000001</v>
+        <v>41.79</v>
       </c>
       <c r="I6" t="n">
-        <v>3975.93</v>
+        <v>3995.83</v>
       </c>
       <c r="J6" t="n">
-        <v>4091.75</v>
+        <v>4004.38</v>
       </c>
       <c r="K6" t="n">
-        <v>4115.97</v>
+        <v>4061.37</v>
       </c>
       <c r="L6" t="n">
-        <v>4140.2</v>
+        <v>4118.36</v>
       </c>
       <c r="M6" t="n">
-        <v>4210.22</v>
+        <v>4151.13</v>
       </c>
       <c r="N6" t="n">
-        <v>4280.24</v>
+        <v>4183.9</v>
       </c>
       <c r="O6" t="n">
-        <v>4258.66</v>
+        <v>4265.11</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1062,57 +1065,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C7" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D7" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E7" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F7" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H7" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I7" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J7" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K7" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L7" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M7" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N7" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O7" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1123,13 +1126,15 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1142,88 +1147,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C8" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D8" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E8" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F8" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H8" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I8" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J8" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K8" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L8" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M8" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N8" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O8" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>4173.19</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1231,74 +1236,70 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C9" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D9" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E9" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F9" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H9" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I9" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J9" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K9" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L9" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M9" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N9" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O9" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1310,55 +1311,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C10" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D10" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E10" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F10" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H10" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I10" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J10" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L10" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M10" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N10" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O10" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1392,57 +1397,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C11" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D11" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E11" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F11" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H11" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I11" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J11" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K11" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L11" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M11" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N11" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O11" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1466,8 +1471,10 @@
       <c r="U11" s="8" t="n">
         <v/>
       </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
@@ -1483,160 +1490,154 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C12" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D12" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E12" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F12" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H12" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J12" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K12" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L12" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M12" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N12" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O12" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>4199.09</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C13" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D13" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E13" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F13" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H13" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I13" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J13" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K13" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L13" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M13" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N13" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O13" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>4168.14</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1648,55 +1649,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C14" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D14" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E14" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F14" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I14" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J14" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K14" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L14" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M14" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N14" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O14" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1704,19 +1709,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1728,65 +1733,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C15" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D15" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E15" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H15" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I15" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J15" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K15" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L15" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M15" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N15" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O15" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1795,7 +1798,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1817,62 +1820,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C16" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D16" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E16" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F16" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H16" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I16" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J16" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K16" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L16" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M16" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N16" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O16" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
@@ -1899,50 +1900,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C17" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D17" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E17" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F17" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H17" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I17" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J17" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K17" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L17" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M17" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N17" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O17" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1952,77 +1953,87 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C18" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D18" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E18" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F18" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H18" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I18" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J18" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K18" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L18" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M18" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O18" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2032,28 +2043,22 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2069,60 +2074,62 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C19" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D19" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E19" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F19" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H19" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I19" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J19" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K19" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L19" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M19" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N19" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O19" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
@@ -2146,79 +2153,79 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C20" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D20" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E20" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F20" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H20" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J20" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K20" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L20" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M20" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N20" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O20" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
@@ -2232,57 +2239,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C21" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D21" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E21" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F21" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H21" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I21" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J21" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K21" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L21" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N21" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O21" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2290,20 +2297,16 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2318,70 +2321,76 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C22" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D22" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E22" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H22" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J22" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K22" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L22" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M22" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N22" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O22" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4019.65</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2393,64 +2402,60 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C23" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D23" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E23" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F23" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H23" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I23" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J23" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K23" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L23" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M23" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N23" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O23" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -2491,74 +2496,70 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C24" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D24" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E24" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F24" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I24" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J24" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K24" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L24" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N24" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O24" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
+        <v>3993.26</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2570,55 +2571,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C25" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D25" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E25" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F25" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H25" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I25" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J25" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K25" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L25" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N25" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O25" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2626,17 +2631,19 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U25" s="8" t="n">
@@ -2652,57 +2659,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C26" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D26" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E26" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F26" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H26" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I26" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J26" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K26" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L26" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M26" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N26" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O26" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2710,20 +2717,16 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2745,50 +2748,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C27" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D27" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E27" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F27" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H27" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I27" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J27" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K27" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L27" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M27" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N27" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2820,70 +2823,76 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C28" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D28" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E28" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F28" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H28" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I28" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J28" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K28" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L28" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M28" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N28" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O28" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3905.96</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2900,167 +2909,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C29" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D29" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E29" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H29" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I29" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J29" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K29" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L29" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M29" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O29" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C30" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D30" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E30" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F30" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H30" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I30" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J30" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K30" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L30" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M30" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N30" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O30" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3079,72 +3086,72 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C31" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D31" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E31" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F31" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H31" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I31" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J31" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K31" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L31" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M31" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N31" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O31" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3158,79 +3165,79 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C32" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D32" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E32" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F32" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H32" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I32" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J32" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K32" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L32" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N32" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O32" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3244,79 +3251,77 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C33" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D33" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E33" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F33" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H33" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I33" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J33" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K33" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L33" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M33" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N33" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O33" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3328,79 +3333,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C34" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D34" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E34" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F34" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H34" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I34" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J34" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K34" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L34" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N34" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O34" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+        <v>3871.81</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3412,79 +3417,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C35" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D35" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E35" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F35" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H35" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I35" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J35" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K35" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L35" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N35" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O35" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3496,59 +3501,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C36" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D36" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E36" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F36" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H36" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I36" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J36" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K36" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L36" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M36" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N36" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O36" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3566,14 +3567,18 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3585,50 +3590,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C37" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D37" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E37" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F37" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H37" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I37" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J37" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K37" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L37" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M37" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N37" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O37" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3646,18 +3651,14 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3669,50 +3670,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C38" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D38" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E38" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F38" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H38" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I38" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J38" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K38" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L38" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N38" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O38" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3730,14 +3731,16 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3749,50 +3752,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C39" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D39" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E39" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F39" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H39" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I39" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J39" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K39" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L39" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M39" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N39" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O39" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3810,16 +3813,14 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V39" s="8" t="n">
+        <v/>
       </c>
       <c r="W39" s="9" t="inlineStr">
         <is>
@@ -3831,79 +3832,81 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C40" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D40" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E40" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F40" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I40" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J40" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K40" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L40" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M40" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N40" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O40" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="Q40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W40" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3911,72 +3914,70 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C41" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D41" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E41" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F41" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H41" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I41" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J41" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K41" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L41" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M41" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N41" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O41" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3988,73 +3989,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C42" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D42" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E42" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F42" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H42" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I42" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J42" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K42" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L42" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M42" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N42" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O42" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U42" s="8" t="n">
@@ -4077,58 +4086,56 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C43" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D43" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E43" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F43" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H43" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I43" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J43" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K43" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L43" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M43" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N43" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O43" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4137,13 +4144,11 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4165,50 +4170,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C44" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D44" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E44" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F44" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H44" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I44" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J44" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K44" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L44" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M44" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N44" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O44" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4216,83 +4221,83 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C45" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D45" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E45" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F45" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H45" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I45" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J45" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K45" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L45" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M45" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N45" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O45" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4310,18 +4315,14 @@
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4333,79 +4334,83 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C46" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D46" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E46" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F46" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H46" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I46" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J46" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K46" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L46" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M46" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N46" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O46" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+        <v>4032.76</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr"/>
@@ -4413,69 +4418,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C47" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D47" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E47" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F47" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H47" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I47" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J47" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K47" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L47" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M47" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N47" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O47" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4042.69</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4492,55 +4491,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C48" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D48" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E48" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F48" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I48" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J48" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K48" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L48" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O48" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4548,12 +4551,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4572,72 +4577,76 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C49" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D49" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E49" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F49" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I49" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J49" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K49" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L49" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M49" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N49" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O49" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4654,78 +4663,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C50" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D50" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E50" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F50" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H50" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I50" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J50" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K50" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L50" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M50" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N50" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O50" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
+        <v>3965.13</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4742,55 +4743,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C51" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D51" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E51" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F51" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H51" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I51" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J51" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K51" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L51" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M51" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N51" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O51" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4798,18 +4803,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4824,57 +4829,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C52" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D52" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E52" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F52" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H52" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I52" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J52" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K52" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L52" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M52" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N52" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O52" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4892,11 +4897,13 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4915,50 +4922,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C53" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D53" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E53" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F53" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H53" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I53" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J53" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K53" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L53" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M53" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N53" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O53" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4971,18 +4978,14 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4994,57 +4997,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C54" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D54" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E54" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F54" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H54" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I54" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J54" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K54" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L54" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M54" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N54" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O54" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5052,81 +5055,89 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C55" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D55" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E55" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F55" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H55" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I55" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J55" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K55" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L55" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M55" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N55" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O55" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5134,30 +5145,22 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
@@ -5173,63 +5176,69 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C56" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D56" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E56" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F56" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H56" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I56" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J56" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K56" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L56" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M56" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N56" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O56" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4013.88</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5241,88 +5250,80 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C57" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D57" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E57" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F57" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H57" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I57" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J57" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K57" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L57" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M57" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N57" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O57" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
+        <v>3999.37</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5334,55 +5335,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C58" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D58" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E58" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I58" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J58" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K58" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L58" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M58" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N58" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O58" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5390,12 +5395,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5403,8 +5410,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5416,57 +5425,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C59" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D59" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E59" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F59" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H59" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I59" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J59" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K59" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L59" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M59" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N59" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O59" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5474,25 +5483,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5504,57 +5507,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C60" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D60" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E60" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F60" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H60" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I60" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J60" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K60" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L60" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M60" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N60" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O60" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5565,13 +5568,15 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5586,57 +5591,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C61" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D61" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E61" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F61" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H61" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I61" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J61" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K61" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L61" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M61" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N61" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O61" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5649,12 +5654,12 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="n">
@@ -5677,70 +5682,72 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C62" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D62" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E62" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F62" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H62" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I62" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J62" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K62" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L62" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M62" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N62" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O62" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="Q62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5752,66 +5759,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C63" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D63" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E63" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F63" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H63" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I63" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J63" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K63" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L63" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M63" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N63" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O63" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
@@ -5843,69 +5848,65 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C64" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D64" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E64" t="n">
-        <v>3888.11</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-46.29</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0118</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I64" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J64" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K64" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L64" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M64" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N64" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O64" t="n">
-        <v>3971.16</v>
+        <v>3972.62</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5922,34 +5923,38 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
-        <v>3791.74</v>
-      </c>
-      <c r="J65" s="13" t="n">
-        <v>3830.78</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>3857.96</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>3885.14</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>3918.26</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>3951.37</v>
-      </c>
-      <c r="O65" s="13" t="n">
-        <v>3972.62</v>
+      <c r="I65" s="14" t="n">
+        <v>3838.53</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>3924</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -109,20 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -490,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4074.29</v>
+        <v>4094.23</v>
       </c>
       <c r="C2" t="n">
-        <v>4109.96</v>
+        <v>4117.45</v>
       </c>
       <c r="D2" t="n">
-        <v>4073.73</v>
+        <v>4080.29</v>
       </c>
       <c r="E2" t="n">
-        <v>4108.08</v>
+        <v>4090.48</v>
       </c>
       <c r="F2" t="n">
-        <v>16.18</v>
+        <v>-17.6</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0043</v>
       </c>
       <c r="H2" t="n">
-        <v>36.23</v>
+        <v>37.16</v>
       </c>
       <c r="I2" t="n">
-        <v>4051.81</v>
+        <v>4037.51</v>
       </c>
       <c r="J2" t="n">
-        <v>4066.33</v>
+        <v>4079.97</v>
       </c>
       <c r="K2" t="n">
-        <v>4078.86</v>
+        <v>4089.96</v>
       </c>
       <c r="L2" t="n">
-        <v>4091.4</v>
+        <v>4099.96</v>
       </c>
       <c r="M2" t="n">
-        <v>4104.92</v>
+        <v>4126.19</v>
       </c>
       <c r="N2" t="n">
-        <v>4118.44</v>
+        <v>4152.42</v>
       </c>
       <c r="O2" t="n">
-        <v>4129.98</v>
+        <v>4146.18</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,18 +694,16 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -730,50 +725,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4094.23</v>
+        <v>4093.96</v>
       </c>
       <c r="C3" t="n">
-        <v>4117.45</v>
+        <v>4164.42</v>
       </c>
       <c r="D3" t="n">
-        <v>4080.29</v>
+        <v>4070.17</v>
       </c>
       <c r="E3" t="n">
-        <v>4090.48</v>
+        <v>4163.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-17.6</v>
+        <v>72.62</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0178</v>
       </c>
       <c r="H3" t="n">
-        <v>37.16</v>
+        <v>94.25</v>
       </c>
       <c r="I3" t="n">
-        <v>4037.51</v>
+        <v>4043.14</v>
       </c>
       <c r="J3" t="n">
-        <v>4079.97</v>
+        <v>4049.13</v>
       </c>
       <c r="K3" t="n">
-        <v>4089.96</v>
+        <v>4071.9</v>
       </c>
       <c r="L3" t="n">
-        <v>4099.96</v>
+        <v>4094.68</v>
       </c>
       <c r="M3" t="n">
-        <v>4126.19</v>
+        <v>4109.06</v>
       </c>
       <c r="N3" t="n">
-        <v>4152.42</v>
+        <v>4123.44</v>
       </c>
       <c r="O3" t="n">
-        <v>4146.18</v>
+        <v>4154.61</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -783,22 +778,28 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -814,81 +815,77 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4093.96</v>
+        <v>4153.59</v>
       </c>
       <c r="C4" t="n">
-        <v>4164.42</v>
+        <v>4175.35</v>
       </c>
       <c r="D4" t="n">
-        <v>4070.17</v>
+        <v>4085.59</v>
       </c>
       <c r="E4" t="n">
-        <v>4163.1</v>
+        <v>4106.25</v>
       </c>
       <c r="F4" t="n">
-        <v>72.62</v>
+        <v>-56.85</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0178</v>
+        <v>-0.0137</v>
       </c>
       <c r="H4" t="n">
-        <v>94.25</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>4043.14</v>
+        <v>3975.93</v>
       </c>
       <c r="J4" t="n">
-        <v>4049.13</v>
+        <v>4091.75</v>
       </c>
       <c r="K4" t="n">
-        <v>4071.9</v>
+        <v>4115.97</v>
       </c>
       <c r="L4" t="n">
-        <v>4094.68</v>
+        <v>4140.2</v>
       </c>
       <c r="M4" t="n">
-        <v>4109.06</v>
+        <v>4210.22</v>
       </c>
       <c r="N4" t="n">
-        <v>4123.44</v>
+        <v>4280.24</v>
       </c>
       <c r="O4" t="n">
-        <v>4154.61</v>
+        <v>4258.66</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -904,67 +901,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4153.59</v>
+        <v>4090.1</v>
       </c>
       <c r="C5" t="n">
-        <v>4175.35</v>
+        <v>4117.29</v>
       </c>
       <c r="D5" t="n">
-        <v>4085.59</v>
+        <v>4075.49</v>
       </c>
       <c r="E5" t="n">
-        <v>4106.25</v>
+        <v>4110.81</v>
       </c>
       <c r="F5" t="n">
-        <v>-56.85</v>
+        <v>4.56</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0137</v>
+        <v>0.0011</v>
       </c>
       <c r="H5" t="n">
-        <v>89.76000000000001</v>
+        <v>41.79</v>
       </c>
       <c r="I5" t="n">
-        <v>3975.93</v>
+        <v>3995.83</v>
       </c>
       <c r="J5" t="n">
-        <v>4091.75</v>
+        <v>4004.38</v>
       </c>
       <c r="K5" t="n">
-        <v>4115.97</v>
+        <v>4061.37</v>
       </c>
       <c r="L5" t="n">
-        <v>4140.2</v>
+        <v>4118.36</v>
       </c>
       <c r="M5" t="n">
-        <v>4210.22</v>
+        <v>4151.13</v>
       </c>
       <c r="N5" t="n">
-        <v>4280.24</v>
+        <v>4183.9</v>
       </c>
       <c r="O5" t="n">
-        <v>4258.66</v>
+        <v>4265.11</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -983,57 +976,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C6" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D6" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E6" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F6" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H6" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I6" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J6" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K6" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L6" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M6" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N6" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O6" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1046,11 +1039,13 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1063,78 +1058,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C7" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D7" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E7" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F7" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H7" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I7" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J7" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K7" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L7" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M7" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O7" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>4173.19</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1142,9 +1137,9 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1152,74 +1147,70 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C8" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D8" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E8" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F8" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H8" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I8" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J8" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K8" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L8" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M8" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N8" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O8" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1231,55 +1222,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C9" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D9" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E9" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F9" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H9" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I9" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J9" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K9" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L9" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M9" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N9" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O9" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1290,7 +1285,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1313,57 +1308,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C10" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D10" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E10" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F10" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H10" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I10" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J10" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K10" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L10" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M10" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N10" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O10" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1374,7 +1369,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1387,8 +1382,10 @@
       <c r="U10" s="8" t="n">
         <v/>
       </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
@@ -1404,160 +1401,154 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C11" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D11" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E11" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F11" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H11" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J11" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K11" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L11" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M11" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N11" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O11" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C12" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D12" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E12" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F12" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H12" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I12" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J12" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K12" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L12" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M12" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N12" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O12" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>4168.14</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1569,55 +1560,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C13" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D13" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E13" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F13" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I13" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J13" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K13" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L13" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M13" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N13" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O13" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1625,18 +1620,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1649,74 +1644,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C14" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D14" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E14" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H14" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I14" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J14" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K14" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L14" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M14" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N14" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O14" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1738,65 +1731,63 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C15" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D15" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E15" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F15" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H15" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I15" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J15" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K15" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L15" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M15" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N15" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O15" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1820,50 +1811,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C16" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D16" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E16" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F16" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H16" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I16" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K16" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L16" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M16" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N16" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O16" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1873,77 +1864,87 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C17" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D17" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E17" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F17" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H17" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I17" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J17" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K17" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L17" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M17" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O17" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1953,28 +1954,22 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1990,63 +1985,65 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C18" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D18" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E18" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F18" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H18" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I18" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J18" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K18" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L18" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M18" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N18" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O18" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2067,79 +2064,79 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C19" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D19" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E19" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F19" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H19" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J19" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K19" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L19" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M19" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N19" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O19" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2153,57 +2150,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C20" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D20" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E20" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F20" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H20" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I20" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J20" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L20" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N20" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O20" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2211,20 +2208,16 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2239,70 +2232,76 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C21" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D21" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E21" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F21" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H21" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J21" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K21" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L21" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M21" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N21" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O21" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2314,64 +2313,60 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C22" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D22" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E22" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F22" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H22" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I22" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J22" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K22" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L22" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M22" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N22" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O22" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -2388,7 +2383,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2412,74 +2407,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C23" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D23" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E23" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I23" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J23" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K23" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L23" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N23" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O23" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
+        <v>3993.26</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2491,55 +2482,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C24" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D24" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E24" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F24" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H24" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I24" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J24" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K24" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L24" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M24" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N24" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O24" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2547,17 +2542,19 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U24" s="8" t="n">
@@ -2573,57 +2570,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C25" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D25" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E25" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F25" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H25" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I25" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J25" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K25" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L25" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M25" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N25" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O25" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2631,20 +2628,16 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2666,50 +2659,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C26" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D26" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E26" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F26" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H26" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I26" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J26" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K26" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L26" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M26" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N26" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O26" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2720,7 +2713,7 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2741,70 +2734,76 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C27" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D27" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E27" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F27" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H27" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I27" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J27" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K27" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L27" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M27" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N27" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O27" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2821,167 +2820,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C28" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D28" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E28" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H28" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I28" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J28" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K28" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L28" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M28" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O28" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C29" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D29" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E29" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F29" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H29" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I29" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J29" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K29" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L29" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M29" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N29" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O29" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -3000,72 +2997,72 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C30" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D30" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E30" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F30" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H30" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I30" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J30" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K30" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L30" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M30" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N30" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O30" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3079,78 +3076,78 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C31" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D31" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E31" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F31" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H31" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I31" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J31" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K31" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L31" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N31" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O31" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3165,79 +3162,77 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C32" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D32" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E32" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F32" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H32" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I32" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J32" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K32" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L32" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M32" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N32" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O32" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3249,78 +3244,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C33" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D33" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E33" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F33" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H33" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I33" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J33" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K33" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L33" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M33" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N33" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O33" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3333,79 +3328,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C34" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D34" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E34" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F34" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H34" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I34" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J34" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K34" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L34" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M34" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N34" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O34" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3417,59 +3412,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C35" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D35" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E35" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F35" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H35" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I35" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J35" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K35" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L35" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M35" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N35" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O35" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3480,21 +3471,25 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3506,50 +3501,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C36" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D36" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E36" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F36" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H36" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I36" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J36" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K36" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L36" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M36" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N36" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O36" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3560,25 +3555,21 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3590,50 +3581,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C37" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D37" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E37" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F37" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H37" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I37" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J37" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K37" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L37" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M37" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N37" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O37" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3644,21 +3635,23 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3670,50 +3663,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C38" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D38" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E38" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F38" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H38" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I38" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J38" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K38" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L38" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M38" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N38" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O38" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3724,23 +3717,21 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3752,69 +3743,71 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C39" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D39" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E39" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F39" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I39" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J39" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K39" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L39" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M39" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N39" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O39" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3822,9 +3815,9 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3832,72 +3825,70 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C40" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D40" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E40" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F40" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H40" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I40" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J40" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K40" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L40" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M40" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N40" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O40" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3909,73 +3900,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C41" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D41" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E41" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F41" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H41" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I41" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J41" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K41" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L41" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M41" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N41" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O41" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U41" s="8" t="n">
@@ -3998,73 +3997,69 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C42" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D42" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E42" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F42" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H42" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I42" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J42" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K42" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L42" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M42" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N42" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O42" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4086,50 +4081,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C43" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D43" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E43" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F43" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H43" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I43" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J43" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K43" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L43" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M43" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N43" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O43" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4137,83 +4132,83 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C44" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D44" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E44" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F44" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H44" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I44" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J44" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K44" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L44" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M44" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N44" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O44" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4224,25 +4219,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
@@ -4254,69 +4245,73 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C45" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D45" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E45" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F45" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H45" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I45" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J45" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K45" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L45" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M45" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N45" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O45" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4324,9 +4319,9 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr"/>
@@ -4334,69 +4329,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C46" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D46" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E46" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F46" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H46" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I46" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J46" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K46" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L46" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M46" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N46" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O46" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4413,55 +4402,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C47" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D47" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E47" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F47" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I47" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J47" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K47" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L47" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O47" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4469,12 +4462,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4493,63 +4488,67 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C48" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D48" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E48" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F48" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I48" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J48" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K48" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L48" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M48" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N48" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O48" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4558,7 +4557,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4575,78 +4574,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C49" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D49" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E49" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F49" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H49" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I49" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J49" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K49" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L49" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M49" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N49" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O49" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
+        <v>3965.13</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4663,55 +4654,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C50" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D50" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E50" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F50" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H50" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I50" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J50" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K50" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L50" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M50" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N50" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O50" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4719,18 +4714,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4745,57 +4740,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C51" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D51" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E51" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F51" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H51" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I51" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J51" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K51" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L51" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M51" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N51" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O51" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4806,18 +4801,20 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4836,50 +4833,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C52" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D52" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E52" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F52" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H52" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I52" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J52" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K52" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L52" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M52" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N52" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O52" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4890,20 +4887,16 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4915,57 +4908,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C53" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D53" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E53" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F53" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H53" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I53" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J53" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K53" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L53" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M53" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N53" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O53" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4973,81 +4966,89 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C54" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D54" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E54" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F54" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H54" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I54" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J54" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K54" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L54" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M54" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N54" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O54" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5055,30 +5056,22 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5094,63 +5087,69 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C55" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D55" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E55" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F55" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H55" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I55" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J55" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K55" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L55" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M55" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N55" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O55" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5162,88 +5161,80 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C56" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D56" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E56" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F56" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H56" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I56" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J56" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K56" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L56" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M56" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N56" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O56" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
+        <v>3999.37</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5255,55 +5246,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C57" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D57" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E57" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H57" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I57" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J57" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K57" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L57" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M57" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N57" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O57" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5311,12 +5306,14 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5324,8 +5321,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5337,57 +5336,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C58" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D58" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E58" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F58" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I58" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J58" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K58" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L58" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M58" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N58" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O58" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5395,25 +5394,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5425,57 +5418,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C59" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D59" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E59" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F59" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H59" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I59" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J59" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K59" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L59" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M59" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N59" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O59" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5488,11 +5481,13 @@
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5507,57 +5502,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C60" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D60" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E60" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F60" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H60" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I60" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J60" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K60" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L60" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M60" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N60" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O60" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5568,14 +5563,14 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U60" s="8" t="n">
@@ -5598,69 +5593,71 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C61" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D61" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E61" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F61" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H61" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I61" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J61" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K61" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L61" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M61" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N61" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O61" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5673,66 +5670,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C62" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D62" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E62" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F62" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H62" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I62" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J62" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K62" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L62" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M62" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N62" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O62" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
@@ -5740,7 +5735,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5764,69 +5759,63 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C63" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D63" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E63" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F63" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H63" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I63" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J63" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K63" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L63" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M63" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N63" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O63" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5843,117 +5832,37 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3867.02</v>
-      </c>
-      <c r="C64" t="n">
-        <v>3895.51</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3867.02</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>28.49</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3791.74</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3830.78</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3857.96</v>
-      </c>
-      <c r="L64" t="n">
-        <v>3885.14</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3918.26</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3951.37</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3972.62</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="14" t="n">
+      <c r="I64" s="13" t="n">
         <v>3838.53</v>
       </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
+      <c r="J64" s="13" t="n">
+        <v>3858.88</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>3871.09</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>3883.3</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>3899.58</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>3915.86</v>
+      </c>
+      <c r="O64" s="13" t="n">
         <v>3924</v>
       </c>
     </row>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5839,31 +5842,115 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3879.73</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3891.62</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3858.15</v>
+      </c>
+      <c r="E64" t="n">
+        <v/>
+      </c>
+      <c r="F64" t="n">
+        <v/>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3838.53</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3858.88</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3871.09</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3883.3</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3899.58</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3915.86</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3924</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>3838.53</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>3858.88</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>3871.09</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>3883.3</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>3899.58</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>3915.86</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>3924</v>
+      <c r="I65" s="14" t="n">
+        <v>3824.68</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>3925.09</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,50 +644,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4094.23</v>
+        <v>4093.96</v>
       </c>
       <c r="C2" t="n">
-        <v>4117.45</v>
+        <v>4164.42</v>
       </c>
       <c r="D2" t="n">
-        <v>4080.29</v>
+        <v>4070.17</v>
       </c>
       <c r="E2" t="n">
-        <v>4090.48</v>
+        <v>4163.1</v>
       </c>
       <c r="F2" t="n">
-        <v>-17.6</v>
+        <v>72.62</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0178</v>
       </c>
       <c r="H2" t="n">
-        <v>37.16</v>
+        <v>94.25</v>
       </c>
       <c r="I2" t="n">
-        <v>4037.51</v>
+        <v>4043.14</v>
       </c>
       <c r="J2" t="n">
-        <v>4079.97</v>
+        <v>4049.13</v>
       </c>
       <c r="K2" t="n">
-        <v>4089.96</v>
+        <v>4071.9</v>
       </c>
       <c r="L2" t="n">
-        <v>4099.96</v>
+        <v>4094.68</v>
       </c>
       <c r="M2" t="n">
-        <v>4126.19</v>
+        <v>4109.06</v>
       </c>
       <c r="N2" t="n">
-        <v>4152.42</v>
+        <v>4123.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4146.18</v>
+        <v>4154.61</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -697,22 +697,28 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -728,81 +734,77 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4093.96</v>
+        <v>4153.59</v>
       </c>
       <c r="C3" t="n">
-        <v>4164.42</v>
+        <v>4175.35</v>
       </c>
       <c r="D3" t="n">
-        <v>4070.17</v>
+        <v>4085.59</v>
       </c>
       <c r="E3" t="n">
-        <v>4163.1</v>
+        <v>4106.25</v>
       </c>
       <c r="F3" t="n">
-        <v>72.62</v>
+        <v>-56.85</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0178</v>
+        <v>-0.0137</v>
       </c>
       <c r="H3" t="n">
-        <v>94.25</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>4043.14</v>
+        <v>3975.93</v>
       </c>
       <c r="J3" t="n">
-        <v>4049.13</v>
+        <v>4091.75</v>
       </c>
       <c r="K3" t="n">
-        <v>4071.9</v>
+        <v>4115.97</v>
       </c>
       <c r="L3" t="n">
-        <v>4094.68</v>
+        <v>4140.2</v>
       </c>
       <c r="M3" t="n">
-        <v>4109.06</v>
+        <v>4210.22</v>
       </c>
       <c r="N3" t="n">
-        <v>4123.44</v>
+        <v>4280.24</v>
       </c>
       <c r="O3" t="n">
-        <v>4154.61</v>
+        <v>4258.66</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -818,67 +820,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4153.59</v>
+        <v>4090.1</v>
       </c>
       <c r="C4" t="n">
-        <v>4175.35</v>
+        <v>4117.29</v>
       </c>
       <c r="D4" t="n">
-        <v>4085.59</v>
+        <v>4075.49</v>
       </c>
       <c r="E4" t="n">
-        <v>4106.25</v>
+        <v>4110.81</v>
       </c>
       <c r="F4" t="n">
-        <v>-56.85</v>
+        <v>4.56</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0137</v>
+        <v>0.0011</v>
       </c>
       <c r="H4" t="n">
-        <v>89.76000000000001</v>
+        <v>41.79</v>
       </c>
       <c r="I4" t="n">
-        <v>3975.93</v>
+        <v>3995.83</v>
       </c>
       <c r="J4" t="n">
-        <v>4091.75</v>
+        <v>4004.38</v>
       </c>
       <c r="K4" t="n">
-        <v>4115.97</v>
+        <v>4061.37</v>
       </c>
       <c r="L4" t="n">
-        <v>4140.2</v>
+        <v>4118.36</v>
       </c>
       <c r="M4" t="n">
-        <v>4210.22</v>
+        <v>4151.13</v>
       </c>
       <c r="N4" t="n">
-        <v>4280.24</v>
+        <v>4183.9</v>
       </c>
       <c r="O4" t="n">
-        <v>4258.66</v>
+        <v>4265.11</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -897,57 +895,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C5" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D5" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E5" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F5" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H5" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I5" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J5" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K5" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L5" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M5" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N5" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O5" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -960,11 +958,13 @@
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -977,78 +977,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C6" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D6" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E6" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F6" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H6" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I6" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J6" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K6" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L6" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M6" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N6" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O6" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>4173.19</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1056,9 +1056,9 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1066,74 +1066,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C7" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D7" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E7" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F7" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H7" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I7" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J7" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K7" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L7" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M7" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N7" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O7" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1145,55 +1141,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C8" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D8" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E8" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F8" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H8" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I8" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J8" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K8" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L8" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M8" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N8" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O8" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1204,7 +1204,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1227,57 +1227,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C9" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D9" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E9" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F9" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H9" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I9" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J9" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K9" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L9" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M9" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N9" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O9" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1288,7 +1288,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1301,8 +1301,10 @@
       <c r="U9" s="8" t="n">
         <v/>
       </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
@@ -1318,159 +1320,153 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C10" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D10" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E10" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F10" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H10" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J10" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K10" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L10" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M10" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N10" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O10" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C11" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D11" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E11" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F11" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H11" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I11" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J11" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K11" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L11" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M11" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N11" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O11" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1483,55 +1479,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C12" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D12" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E12" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F12" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J12" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K12" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L12" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M12" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N12" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O12" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1539,18 +1539,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1563,74 +1563,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C13" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D13" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E13" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H13" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I13" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J13" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K13" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L13" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M13" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N13" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O13" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1652,65 +1650,63 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C14" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D14" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E14" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F14" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H14" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I14" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J14" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K14" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L14" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M14" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N14" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O14" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1734,50 +1730,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C15" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D15" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E15" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F15" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H15" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I15" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J15" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K15" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L15" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M15" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N15" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O15" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,77 +1783,87 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C16" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D16" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E16" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F16" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H16" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I16" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J16" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K16" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L16" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M16" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N16" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O16" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,28 +1873,22 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1904,63 +1904,65 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C17" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D17" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E17" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F17" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H17" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I17" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J17" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K17" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L17" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M17" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N17" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O17" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1981,79 +1983,79 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C18" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D18" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E18" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F18" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H18" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J18" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K18" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L18" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M18" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N18" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O18" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2067,57 +2069,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C19" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D19" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E19" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F19" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H19" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I19" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J19" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K19" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L19" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N19" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O19" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2125,20 +2127,16 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2153,70 +2151,76 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C20" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D20" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E20" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F20" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H20" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I20" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J20" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K20" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L20" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M20" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N20" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O20" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2228,64 +2232,60 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C21" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D21" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E21" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F21" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H21" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I21" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K21" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L21" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M21" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N21" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O21" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -2302,7 +2302,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2326,73 +2326,69 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C22" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D22" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E22" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F22" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I22" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J22" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K22" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L22" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N22" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O22" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2405,55 +2401,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C23" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D23" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E23" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F23" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H23" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I23" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J23" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K23" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L23" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M23" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N23" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O23" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2461,17 +2461,19 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U23" s="8" t="n">
@@ -2487,57 +2489,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C24" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D24" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E24" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F24" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H24" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I24" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J24" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K24" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L24" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M24" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N24" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2545,20 +2547,16 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2580,50 +2578,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C25" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D25" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E25" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F25" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H25" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I25" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J25" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K25" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L25" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M25" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N25" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O25" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2634,7 +2632,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2655,70 +2653,76 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C26" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D26" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E26" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F26" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H26" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I26" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J26" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K26" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L26" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M26" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N26" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O26" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2735,167 +2739,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C27" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D27" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E27" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H27" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I27" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J27" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K27" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L27" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M27" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O27" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C28" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D28" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E28" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F28" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H28" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I28" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J28" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K28" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L28" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N28" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O28" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2914,72 +2916,72 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C29" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D29" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E29" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F29" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H29" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I29" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J29" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K29" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L29" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M29" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N29" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O29" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2993,78 +2995,78 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C30" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D30" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E30" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F30" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H30" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I30" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J30" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K30" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L30" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N30" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O30" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3079,79 +3081,77 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C31" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D31" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E31" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F31" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H31" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I31" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K31" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L31" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M31" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N31" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O31" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3163,78 +3163,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C32" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D32" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E32" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F32" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H32" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I32" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J32" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K32" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L32" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M32" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N32" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O32" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3247,79 +3247,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C33" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D33" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E33" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F33" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H33" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I33" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J33" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K33" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L33" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M33" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N33" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O33" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3331,59 +3331,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C34" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D34" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E34" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F34" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H34" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I34" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J34" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K34" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L34" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M34" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N34" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O34" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3394,21 +3390,25 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3420,50 +3420,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C35" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D35" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E35" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F35" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H35" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I35" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J35" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K35" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L35" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M35" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N35" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O35" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3474,25 +3474,21 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3504,50 +3500,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C36" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D36" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E36" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F36" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H36" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I36" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J36" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K36" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L36" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M36" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N36" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O36" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3558,21 +3554,23 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3584,50 +3582,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C37" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D37" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E37" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F37" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H37" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I37" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J37" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K37" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L37" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M37" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N37" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O37" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3638,23 +3636,21 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3666,69 +3662,71 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C38" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D38" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E38" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F38" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I38" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J38" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K38" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L38" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M38" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N38" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O38" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3736,9 +3734,9 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3746,72 +3744,70 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C39" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D39" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E39" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F39" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H39" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I39" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J39" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K39" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L39" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M39" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N39" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O39" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3823,73 +3819,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C40" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D40" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E40" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F40" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H40" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I40" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J40" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K40" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L40" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M40" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N40" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O40" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U40" s="8" t="n">
@@ -3912,73 +3916,69 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C41" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D41" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E41" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F41" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H41" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I41" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J41" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K41" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L41" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M41" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N41" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O41" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -4000,50 +4000,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C42" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D42" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E42" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F42" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H42" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I42" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J42" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K42" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L42" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M42" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N42" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O42" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4051,83 +4051,83 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C43" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D43" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E43" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F43" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H43" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I43" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J43" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K43" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L43" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M43" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N43" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O43" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4138,25 +4138,21 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4168,69 +4164,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C44" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D44" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E44" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F44" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H44" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I44" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J44" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K44" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L44" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M44" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N44" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O44" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4238,9 +4238,9 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr"/>
@@ -4248,69 +4248,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C45" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D45" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E45" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F45" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H45" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I45" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J45" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K45" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L45" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M45" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N45" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O45" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4327,55 +4321,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C46" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D46" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E46" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F46" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H46" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I46" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J46" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K46" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L46" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M46" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4383,12 +4381,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4407,63 +4407,67 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C47" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D47" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E47" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F47" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I47" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J47" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K47" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L47" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M47" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N47" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O47" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4472,7 +4476,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4489,69 +4493,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C48" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D48" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E48" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F48" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H48" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I48" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J48" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K48" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L48" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M48" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N48" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O48" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4560,7 +4556,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4577,55 +4573,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C49" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D49" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E49" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F49" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I49" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J49" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K49" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L49" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M49" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N49" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O49" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4633,18 +4633,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4659,57 +4659,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C50" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D50" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E50" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F50" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H50" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I50" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J50" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K50" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L50" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M50" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N50" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O50" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4720,18 +4720,20 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4750,50 +4752,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C51" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D51" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E51" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F51" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H51" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I51" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J51" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K51" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L51" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M51" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N51" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O51" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4804,20 +4806,16 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4829,57 +4827,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C52" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D52" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E52" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H52" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I52" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J52" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K52" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L52" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M52" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N52" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O52" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4887,81 +4885,89 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C53" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D53" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E53" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F53" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H53" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I53" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J53" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K53" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L53" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M53" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N53" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O53" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4969,30 +4975,22 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -5008,63 +5006,69 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C54" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D54" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E54" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F54" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H54" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I54" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J54" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K54" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L54" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M54" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N54" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O54" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5076,87 +5080,79 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C55" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D55" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E55" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F55" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H55" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I55" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J55" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K55" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L55" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M55" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N55" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O55" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5169,55 +5165,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C56" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D56" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E56" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H56" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I56" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J56" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K56" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L56" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M56" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N56" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O56" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5225,12 +5225,14 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5238,8 +5240,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5251,57 +5255,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C57" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D57" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E57" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F57" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H57" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I57" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J57" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K57" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L57" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M57" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N57" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O57" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5309,25 +5313,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5339,57 +5337,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C58" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D58" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E58" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F58" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H58" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I58" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J58" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K58" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L58" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M58" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N58" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O58" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5402,11 +5400,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5421,57 +5421,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C59" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D59" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E59" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F59" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H59" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I59" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J59" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K59" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L59" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M59" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N59" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O59" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5482,14 +5482,14 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U59" s="8" t="n">
@@ -5512,69 +5512,71 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C60" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D60" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E60" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F60" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H60" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I60" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J60" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K60" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L60" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M60" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N60" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O60" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5587,66 +5589,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C61" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D61" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E61" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F61" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H61" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I61" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J61" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K61" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L61" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M61" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N61" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O61" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
@@ -5654,7 +5654,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5678,69 +5678,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C62" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D62" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E62" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F62" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H62" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I62" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J62" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K62" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L62" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M62" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N62" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O62" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5757,68 +5751,78 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3867.02</v>
+        <v>3861.75</v>
       </c>
       <c r="C63" t="n">
-        <v>3895.51</v>
+        <v>3863.15</v>
       </c>
       <c r="D63" t="n">
-        <v>3867.02</v>
+        <v>3850.11</v>
       </c>
       <c r="E63" t="n">
-        <v>3885.33</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-2.78</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0007</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>28.49</v>
+        <v>13.03</v>
       </c>
       <c r="I63" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J63" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K63" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L63" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M63" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N63" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O63" t="n">
-        <v>3972.62</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3924</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5835,122 +5839,34 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3879.73</v>
-      </c>
-      <c r="C64" t="n">
-        <v>3891.62</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3858.15</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>33.47</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3838.53</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3858.88</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3871.09</v>
-      </c>
-      <c r="L64" t="n">
-        <v>3883.3</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3899.58</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3915.86</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3924</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="14" t="n">
-        <v>3824.68</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
-        <v>3925.09</v>
+      <c r="I64" s="14" t="n">
+        <v>3837.08</v>
+      </c>
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
+        <v>3876.18</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5764,25 +5761,25 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3861.75</v>
+        <v>3879.73</v>
       </c>
       <c r="C63" t="n">
-        <v>3863.15</v>
+        <v>3891.62</v>
       </c>
       <c r="D63" t="n">
-        <v>3850.11</v>
+        <v>3858.15</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>3864.28</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>-21.05</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>-0.0054</v>
       </c>
       <c r="H63" t="n">
-        <v>13.03</v>
+        <v>33.47</v>
       </c>
       <c r="I63" t="n">
         <v>3838.53</v>
@@ -5805,24 +5802,22 @@
       <c r="O63" t="n">
         <v>3924</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5842,31 +5837,31 @@
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="A64" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>3837.08</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>3876.18</v>
+      <c r="I64" s="13" t="n">
+        <v>3824.68</v>
+      </c>
+      <c r="J64" s="13" t="n">
+        <v>3825.51</v>
+      </c>
+      <c r="K64" s="13" t="n">
+        <v>3847.54</v>
+      </c>
+      <c r="L64" s="13" t="n">
+        <v>3869.58</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>3881.01</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>3892.45</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>3925.09</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5837,31 +5837,119 @@
       <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="12" t="inlineStr">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3861.75</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3894.66</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3842.72</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3891.6</v>
+      </c>
+      <c r="F64" t="n">
+        <v>27.32</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0.0071</v>
+      </c>
+      <c r="H64" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3824.68</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3825.51</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3847.54</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3869.58</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3881.01</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3892.45</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3925.09</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="13" t="n">
-        <v>3824.68</v>
-      </c>
-      <c r="J64" s="13" t="n">
-        <v>3825.51</v>
-      </c>
-      <c r="K64" s="13" t="n">
-        <v>3847.54</v>
-      </c>
-      <c r="L64" s="13" t="n">
-        <v>3869.58</v>
-      </c>
-      <c r="M64" s="13" t="n">
-        <v>3881.01</v>
-      </c>
-      <c r="N64" s="13" t="n">
-        <v>3892.45</v>
-      </c>
-      <c r="O64" s="13" t="n">
-        <v>3925.09</v>
+      <c r="I65" s="13" t="n">
+        <v>3790.78</v>
+      </c>
+      <c r="J65" s="13" t="n">
+        <v>3851.11</v>
+      </c>
+      <c r="K65" s="13" t="n">
+        <v>3865.63</v>
+      </c>
+      <c r="L65" s="13" t="n">
+        <v>3880.15</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>3917.57</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>3955</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>3946.61</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5852,13 +5855,13 @@
         <v>3842.72</v>
       </c>
       <c r="E64" t="n">
-        <v>3891.6</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>27.32</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0071</v>
+        <v/>
       </c>
       <c r="H64" t="n">
         <v>51.94</v>
@@ -5884,8 +5887,10 @@
       <c r="O64" t="n">
         <v>3925.09</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5895,9 +5900,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5907,7 +5912,7 @@
       </c>
       <c r="U64" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V64" s="8" t="n">
@@ -5920,35 +5925,35 @@
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="12" t="inlineStr">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="13" t="n">
+      <c r="I65" s="14" t="n">
         <v>3790.78</v>
       </c>
-      <c r="J65" s="13" t="n">
-        <v>3851.11</v>
-      </c>
-      <c r="K65" s="13" t="n">
-        <v>3865.63</v>
-      </c>
-      <c r="L65" s="13" t="n">
-        <v>3880.15</v>
-      </c>
-      <c r="M65" s="13" t="n">
-        <v>3917.57</v>
-      </c>
-      <c r="N65" s="13" t="n">
-        <v>3955</v>
-      </c>
-      <c r="O65" s="13" t="n">
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
         <v>3946.61</v>
       </c>
     </row>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -644,81 +644,77 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4093.96</v>
+        <v>4153.59</v>
       </c>
       <c r="C2" t="n">
-        <v>4164.42</v>
+        <v>4175.35</v>
       </c>
       <c r="D2" t="n">
-        <v>4070.17</v>
+        <v>4085.59</v>
       </c>
       <c r="E2" t="n">
-        <v>4163.1</v>
+        <v>4106.25</v>
       </c>
       <c r="F2" t="n">
-        <v>72.62</v>
+        <v>-56.85</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0178</v>
+        <v>-0.0137</v>
       </c>
       <c r="H2" t="n">
-        <v>94.25</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>4043.14</v>
+        <v>3975.93</v>
       </c>
       <c r="J2" t="n">
-        <v>4049.13</v>
+        <v>4091.75</v>
       </c>
       <c r="K2" t="n">
-        <v>4071.9</v>
+        <v>4115.97</v>
       </c>
       <c r="L2" t="n">
-        <v>4094.68</v>
+        <v>4140.2</v>
       </c>
       <c r="M2" t="n">
-        <v>4109.06</v>
+        <v>4210.22</v>
       </c>
       <c r="N2" t="n">
-        <v>4123.44</v>
+        <v>4280.24</v>
       </c>
       <c r="O2" t="n">
-        <v>4154.61</v>
+        <v>4258.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -734,67 +730,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4153.59</v>
+        <v>4090.1</v>
       </c>
       <c r="C3" t="n">
-        <v>4175.35</v>
+        <v>4117.29</v>
       </c>
       <c r="D3" t="n">
-        <v>4085.59</v>
+        <v>4075.49</v>
       </c>
       <c r="E3" t="n">
-        <v>4106.25</v>
+        <v>4110.81</v>
       </c>
       <c r="F3" t="n">
-        <v>-56.85</v>
+        <v>4.56</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0137</v>
+        <v>0.0011</v>
       </c>
       <c r="H3" t="n">
-        <v>89.76000000000001</v>
+        <v>41.79</v>
       </c>
       <c r="I3" t="n">
-        <v>3975.93</v>
+        <v>3995.83</v>
       </c>
       <c r="J3" t="n">
-        <v>4091.75</v>
+        <v>4004.38</v>
       </c>
       <c r="K3" t="n">
-        <v>4115.97</v>
+        <v>4061.37</v>
       </c>
       <c r="L3" t="n">
-        <v>4140.2</v>
+        <v>4118.36</v>
       </c>
       <c r="M3" t="n">
-        <v>4210.22</v>
+        <v>4151.13</v>
       </c>
       <c r="N3" t="n">
-        <v>4280.24</v>
+        <v>4183.9</v>
       </c>
       <c r="O3" t="n">
-        <v>4258.66</v>
+        <v>4265.11</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -813,57 +805,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C4" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D4" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E4" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F4" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H4" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I4" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J4" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K4" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L4" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M4" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N4" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O4" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -876,11 +868,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -893,78 +887,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C5" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D5" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E5" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F5" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H5" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I5" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J5" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K5" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L5" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M5" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N5" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O5" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>4173.19</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -972,9 +966,9 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -982,74 +976,70 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C6" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D6" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E6" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F6" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H6" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I6" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J6" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K6" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L6" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M6" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N6" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O6" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1061,55 +1051,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C7" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D7" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E7" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F7" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H7" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I7" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J7" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L7" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M7" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N7" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O7" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1120,7 +1114,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1143,57 +1137,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C8" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D8" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E8" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F8" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H8" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I8" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J8" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K8" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L8" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M8" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N8" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O8" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1204,7 +1198,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1217,8 +1211,10 @@
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
@@ -1234,159 +1230,153 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C9" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D9" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E9" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F9" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H9" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J9" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K9" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L9" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M9" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N9" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O9" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C10" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D10" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E10" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F10" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H10" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I10" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J10" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K10" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L10" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M10" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N10" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O10" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1399,55 +1389,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C11" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D11" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E11" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F11" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J11" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K11" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L11" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M11" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N11" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O11" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1455,18 +1449,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1479,74 +1473,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C12" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D12" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E12" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H12" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I12" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J12" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K12" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L12" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M12" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N12" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O12" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1568,65 +1560,63 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C13" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D13" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E13" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F13" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H13" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I13" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J13" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K13" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L13" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M13" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N13" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O13" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1650,50 +1640,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C14" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D14" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E14" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F14" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H14" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I14" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J14" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K14" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L14" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M14" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N14" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O14" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1703,77 +1693,87 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C15" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D15" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E15" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F15" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H15" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I15" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J15" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K15" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L15" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M15" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N15" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O15" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1783,28 +1783,22 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1820,63 +1814,65 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C16" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D16" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E16" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F16" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H16" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I16" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J16" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K16" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L16" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M16" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N16" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O16" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1897,79 +1893,79 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C17" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D17" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E17" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F17" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H17" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J17" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K17" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L17" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M17" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N17" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O17" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1983,57 +1979,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C18" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D18" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E18" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F18" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H18" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I18" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J18" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K18" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L18" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N18" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O18" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2041,20 +2037,16 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2069,70 +2061,76 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C19" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D19" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E19" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F19" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H19" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J19" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K19" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L19" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M19" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N19" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O19" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2144,64 +2142,60 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C20" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D20" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E20" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F20" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H20" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I20" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J20" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L20" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M20" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N20" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O20" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -2218,7 +2212,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2242,73 +2236,69 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C21" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D21" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E21" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F21" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I21" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J21" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K21" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L21" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N21" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O21" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2321,55 +2311,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C22" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D22" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E22" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F22" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H22" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I22" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J22" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K22" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L22" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N22" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O22" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2377,17 +2371,19 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U22" s="8" t="n">
@@ -2403,57 +2399,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C23" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D23" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E23" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F23" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H23" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I23" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J23" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K23" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L23" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M23" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N23" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2461,20 +2457,16 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2496,50 +2488,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C24" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D24" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E24" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F24" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H24" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I24" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J24" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K24" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L24" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M24" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N24" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O24" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2550,7 +2542,7 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2571,70 +2563,76 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C25" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D25" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E25" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F25" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H25" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I25" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J25" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K25" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L25" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M25" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N25" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2651,167 +2649,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C26" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D26" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E26" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H26" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I26" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J26" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K26" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L26" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M26" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N26" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C27" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D27" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E27" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F27" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H27" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I27" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J27" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K27" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L27" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M27" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N27" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O27" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2830,72 +2826,72 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C28" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D28" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E28" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F28" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H28" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I28" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J28" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K28" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L28" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M28" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N28" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O28" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2909,78 +2905,78 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C29" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D29" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E29" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F29" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H29" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I29" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J29" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K29" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L29" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N29" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O29" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2995,79 +2991,77 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C30" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D30" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E30" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F30" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H30" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I30" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J30" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K30" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L30" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M30" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N30" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O30" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3079,78 +3073,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C31" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D31" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E31" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F31" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H31" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I31" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K31" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L31" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M31" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N31" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O31" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3163,79 +3157,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C32" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D32" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E32" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F32" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H32" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I32" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J32" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K32" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L32" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M32" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N32" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O32" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3247,59 +3241,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C33" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D33" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E33" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F33" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H33" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I33" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J33" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K33" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L33" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M33" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N33" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O33" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3310,21 +3300,25 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3336,50 +3330,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C34" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D34" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E34" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F34" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H34" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I34" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J34" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K34" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L34" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M34" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N34" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O34" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3390,25 +3384,21 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3420,50 +3410,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C35" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D35" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E35" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F35" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H35" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I35" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J35" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K35" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L35" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M35" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N35" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3474,21 +3464,23 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3500,50 +3492,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C36" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D36" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E36" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F36" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H36" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I36" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J36" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K36" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L36" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M36" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N36" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O36" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3554,23 +3546,21 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
+      <c r="S36" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3582,69 +3572,71 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C37" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D37" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E37" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F37" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I37" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J37" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K37" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L37" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M37" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N37" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O37" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3652,9 +3644,9 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3662,72 +3654,70 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C38" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D38" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E38" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F38" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H38" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I38" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J38" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K38" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L38" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M38" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N38" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O38" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3739,73 +3729,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C39" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D39" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E39" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F39" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H39" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I39" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J39" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K39" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L39" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M39" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N39" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O39" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U39" s="8" t="n">
@@ -3828,73 +3826,69 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C40" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D40" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E40" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F40" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H40" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I40" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J40" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K40" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L40" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M40" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N40" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O40" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3916,50 +3910,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C41" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D41" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E41" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F41" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H41" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I41" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J41" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K41" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L41" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M41" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N41" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O41" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3967,83 +3961,83 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C42" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D42" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E42" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F42" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H42" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I42" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J42" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K42" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L42" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M42" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N42" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O42" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4054,25 +4048,21 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4084,69 +4074,73 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C43" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D43" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E43" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F43" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H43" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I43" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J43" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K43" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L43" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M43" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N43" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O43" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4154,9 +4148,9 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr"/>
@@ -4164,69 +4158,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C44" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D44" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E44" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F44" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H44" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I44" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J44" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K44" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L44" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M44" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N44" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O44" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4243,55 +4231,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C45" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D45" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E45" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F45" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I45" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J45" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K45" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L45" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M45" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O45" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4299,12 +4291,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4323,63 +4317,67 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C46" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D46" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E46" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F46" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I46" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J46" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K46" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L46" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M46" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N46" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O46" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4388,7 +4386,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4405,69 +4403,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C47" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D47" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E47" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F47" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H47" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I47" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J47" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K47" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L47" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M47" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N47" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O47" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4476,7 +4466,7 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4493,55 +4483,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C48" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D48" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E48" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F48" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I48" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J48" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K48" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L48" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M48" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N48" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O48" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4549,18 +4543,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4575,57 +4569,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C49" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D49" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E49" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F49" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H49" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I49" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J49" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K49" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L49" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M49" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N49" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O49" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4636,18 +4630,20 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4666,50 +4662,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C50" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D50" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E50" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F50" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H50" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I50" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J50" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K50" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L50" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M50" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N50" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O50" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4720,20 +4716,16 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4745,57 +4737,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C51" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D51" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E51" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F51" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H51" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I51" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J51" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K51" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L51" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M51" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N51" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O51" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4803,81 +4795,89 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C52" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D52" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E52" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F52" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H52" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I52" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J52" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K52" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L52" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M52" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N52" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O52" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4885,30 +4885,22 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4924,63 +4916,69 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C53" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D53" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E53" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F53" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H53" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I53" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J53" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K53" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L53" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M53" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N53" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O53" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4992,87 +4990,79 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C54" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D54" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E54" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F54" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H54" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I54" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J54" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K54" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L54" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M54" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N54" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O54" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5085,55 +5075,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C55" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D55" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E55" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H55" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I55" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J55" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K55" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L55" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M55" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N55" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O55" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5141,12 +5135,14 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5154,8 +5150,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5167,57 +5165,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C56" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D56" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E56" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F56" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H56" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I56" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J56" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K56" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L56" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M56" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N56" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O56" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5225,25 +5223,19 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5255,57 +5247,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C57" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D57" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E57" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F57" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H57" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I57" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J57" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K57" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L57" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M57" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N57" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O57" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5318,11 +5310,13 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5337,57 +5331,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C58" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D58" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E58" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F58" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H58" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I58" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J58" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K58" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L58" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M58" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N58" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O58" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5398,14 +5392,14 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U58" s="8" t="n">
@@ -5428,69 +5422,71 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C59" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D59" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E59" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F59" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H59" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I59" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J59" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K59" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L59" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M59" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N59" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O59" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5503,66 +5499,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C60" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D60" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E60" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F60" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H60" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I60" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J60" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K60" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L60" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M60" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N60" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O60" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
@@ -5570,7 +5564,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5594,69 +5588,63 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C61" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D61" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E61" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F61" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H61" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I61" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J61" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K61" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L61" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M61" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N61" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O61" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5673,68 +5661,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C62" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D62" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E62" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H62" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I62" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J62" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K62" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L62" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M62" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N62" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O62" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5751,83 +5747,83 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C63" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D63" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E63" t="n">
-        <v>3864.28</v>
+        <v/>
       </c>
       <c r="F63" t="n">
-        <v>-21.05</v>
+        <v/>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0054</v>
+        <v/>
       </c>
       <c r="H63" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I63" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J63" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K63" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L63" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M63" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N63" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O63" t="n">
-        <v>3924</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
+        <v>3925.09</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+      <c r="S63" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5837,123 +5833,37 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3861.75</v>
-      </c>
-      <c r="C64" t="n">
-        <v>3894.66</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3842.72</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3824.68</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3825.51</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3847.54</v>
-      </c>
-      <c r="L64" t="n">
-        <v>3869.58</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3881.01</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3892.45</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3925.09</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="A64" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I65" s="14" t="n">
+      <c r="I64" s="14" t="n">
         <v>3790.78</v>
       </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
+      <c r="J64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N64" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O64" s="14" t="n">
         <v>3946.61</v>
       </c>
     </row>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -490,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5765,13 +5765,13 @@
         <v>3842.72</v>
       </c>
       <c r="E63" t="n">
-        <v/>
+        <v>3891.6</v>
       </c>
       <c r="F63" t="n">
-        <v/>
+        <v>27.32</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v/>
+        <v>0.0071</v>
       </c>
       <c r="H63" t="n">
         <v>51.94</v>
@@ -5797,74 +5797,156 @@
       <c r="O63" t="n">
         <v>3925.09</v>
       </c>
-      <c r="P63" s="6" t="inlineStr">
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="12" t="inlineStr">
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>3877</v>
+      </c>
+      <c r="C64" t="n">
+        <v>3898.84</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3866.89</v>
+      </c>
+      <c r="E64" t="n">
+        <v/>
+      </c>
+      <c r="F64" t="n">
+        <v/>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H64" t="n">
+        <v>31.94</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3790.78</v>
+      </c>
+      <c r="J64" t="n">
+        <v>3851.11</v>
+      </c>
+      <c r="K64" t="n">
+        <v>3865.63</v>
+      </c>
+      <c r="L64" t="n">
+        <v>3880.15</v>
+      </c>
+      <c r="M64" t="n">
+        <v>3917.57</v>
+      </c>
+      <c r="N64" t="n">
+        <v>3955</v>
+      </c>
+      <c r="O64" t="n">
+        <v>3946.61</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
         <is>
           <t>=</t>
         </is>
       </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I64" s="14" t="n">
-        <v>3790.78</v>
-      </c>
-      <c r="J64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N64" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O64" s="14" t="n">
-        <v>3946.61</v>
+      <c r="I65" s="14" t="n">
+        <v>3834.95</v>
+      </c>
+      <c r="J65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N65" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O65" s="14" t="n">
+        <v>3930.78</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -123,8 +118,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -490,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5921,34 +5914,6 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I65" s="14" t="n">
-        <v>3834.95</v>
-      </c>
-      <c r="J65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="14" t="n">
-        <v>3930.78</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5846,13 +5843,13 @@
         <v>3866.89</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>3875.6</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-16</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0041</v>
       </c>
       <c r="H64" t="n">
         <v>31.94</v>
@@ -5878,41 +5875,121 @@
       <c r="O64" t="n">
         <v>3946.61</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>3891.96</v>
+      </c>
+      <c r="C65" t="n">
+        <v>3919.67</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3888.5</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3911.87</v>
+      </c>
+      <c r="F65" t="n">
+        <v>36.27</v>
+      </c>
+      <c r="G65" s="5" t="n">
+        <v>0.0094</v>
+      </c>
+      <c r="H65" t="n">
+        <v>31.17</v>
+      </c>
+      <c r="I65" t="n">
+        <v>3834.95</v>
+      </c>
+      <c r="J65" t="n">
+        <v>3840.03</v>
+      </c>
+      <c r="K65" t="n">
+        <v>3859.63</v>
+      </c>
+      <c r="L65" t="n">
+        <v>3879.23</v>
+      </c>
+      <c r="M65" t="n">
+        <v>3891.58</v>
+      </c>
+      <c r="N65" t="n">
+        <v>3903.92</v>
+      </c>
+      <c r="O65" t="n">
+        <v>3930.78</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R65" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U65" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W65" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,67 +637,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4153.59</v>
+        <v>4090.1</v>
       </c>
       <c r="C2" t="n">
-        <v>4175.35</v>
+        <v>4117.29</v>
       </c>
       <c r="D2" t="n">
-        <v>4085.59</v>
+        <v>4075.49</v>
       </c>
       <c r="E2" t="n">
-        <v>4106.25</v>
+        <v>4110.81</v>
       </c>
       <c r="F2" t="n">
-        <v>-56.85</v>
+        <v>4.56</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0137</v>
+        <v>0.0011</v>
       </c>
       <c r="H2" t="n">
-        <v>89.76000000000001</v>
+        <v>41.79</v>
       </c>
       <c r="I2" t="n">
-        <v>3975.93</v>
+        <v>3995.83</v>
       </c>
       <c r="J2" t="n">
-        <v>4091.75</v>
+        <v>4004.38</v>
       </c>
       <c r="K2" t="n">
-        <v>4115.97</v>
+        <v>4061.37</v>
       </c>
       <c r="L2" t="n">
-        <v>4140.2</v>
+        <v>4118.36</v>
       </c>
       <c r="M2" t="n">
-        <v>4210.22</v>
+        <v>4151.13</v>
       </c>
       <c r="N2" t="n">
-        <v>4280.24</v>
+        <v>4183.9</v>
       </c>
       <c r="O2" t="n">
-        <v>4258.66</v>
+        <v>4265.11</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -713,57 +712,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C3" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D3" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E3" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F3" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H3" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I3" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J3" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K3" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L3" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M3" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N3" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O3" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,13 +773,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,88 +794,88 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C4" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D4" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E4" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F4" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H4" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I4" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J4" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K4" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L4" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M4" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N4" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O4" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>4173.19</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -882,74 +883,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C5" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D5" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E5" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F5" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H5" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I5" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J5" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K5" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L5" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M5" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N5" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O5" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,55 +958,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C6" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D6" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E6" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F6" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H6" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I6" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J6" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K6" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L6" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M6" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N6" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O6" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1043,57 +1044,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C7" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D7" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E7" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F7" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H7" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I7" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J7" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K7" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L7" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M7" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N7" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O7" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1117,8 +1118,10 @@
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
@@ -1134,159 +1137,153 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C8" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D8" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E8" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F8" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H8" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J8" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K8" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L8" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M8" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N8" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O8" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>4199.09</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C9" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D9" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E9" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F9" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H9" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I9" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J9" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K9" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L9" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M9" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N9" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O9" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+        <v>4168.14</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1299,55 +1296,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C10" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D10" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E10" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F10" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J10" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K10" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L10" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M10" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N10" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O10" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,18 +1356,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,65 +1380,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C11" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D11" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E11" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H11" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I11" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J11" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K11" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L11" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M11" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N11" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O11" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
@@ -1446,7 +1445,7 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1468,62 +1467,60 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C12" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D12" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E12" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F12" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H12" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I12" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J12" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K12" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L12" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M12" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N12" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O12" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
@@ -1550,50 +1547,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C13" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D13" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E13" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F13" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H13" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I13" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J13" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K13" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L13" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M13" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N13" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O13" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,77 +1600,87 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C14" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D14" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E14" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F14" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H14" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I14" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J14" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K14" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L14" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M14" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N14" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O14" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1683,28 +1690,22 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1720,60 +1721,62 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C15" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D15" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E15" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F15" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H15" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I15" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J15" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K15" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L15" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M15" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N15" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O15" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
@@ -1797,79 +1800,79 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C16" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D16" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E16" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F16" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H16" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J16" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K16" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L16" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M16" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N16" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O16" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1883,57 +1886,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C17" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D17" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E17" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F17" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H17" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I17" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J17" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K17" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L17" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N17" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O17" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1941,20 +1944,16 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1969,70 +1968,76 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C18" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D18" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E18" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F18" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H18" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J18" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K18" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L18" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M18" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N18" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O18" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4019.65</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2044,64 +2049,60 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C19" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D19" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E19" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F19" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H19" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I19" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J19" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K19" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L19" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M19" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N19" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O19" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -2142,73 +2143,69 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C20" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D20" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E20" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F20" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I20" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J20" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K20" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L20" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N20" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O20" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+        <v>3993.26</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2221,55 +2218,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C21" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D21" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E21" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F21" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H21" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I21" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J21" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K21" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L21" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M21" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N21" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O21" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2277,17 +2278,19 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U21" s="8" t="n">
@@ -2303,57 +2306,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C22" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D22" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E22" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F22" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H22" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I22" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J22" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K22" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L22" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M22" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N22" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2361,20 +2364,16 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2396,50 +2395,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C23" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D23" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E23" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F23" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H23" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I23" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J23" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K23" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L23" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M23" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N23" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2471,70 +2470,76 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C24" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D24" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E24" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F24" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H24" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I24" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J24" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K24" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L24" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M24" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N24" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O24" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3905.96</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2551,167 +2556,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C25" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D25" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E25" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H25" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I25" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J25" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K25" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L25" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M25" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N25" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O25" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C26" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D26" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E26" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F26" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H26" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I26" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J26" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K26" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L26" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M26" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N26" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O26" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2730,72 +2733,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C27" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D27" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E27" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F27" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H27" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I27" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J27" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K27" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L27" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M27" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N27" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O27" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2809,79 +2812,79 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C28" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D28" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E28" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F28" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H28" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I28" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J28" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K28" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L28" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N28" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O28" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2895,79 +2898,77 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C29" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D29" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E29" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F29" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H29" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I29" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J29" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K29" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L29" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M29" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N29" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O29" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2979,79 +2980,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C30" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D30" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E30" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F30" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H30" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I30" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J30" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K30" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L30" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M30" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N30" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+        <v>3871.81</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3063,79 +3064,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C31" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D31" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E31" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F31" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H31" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I31" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J31" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K31" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L31" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M31" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N31" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O31" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3147,59 +3148,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C32" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D32" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E32" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F32" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H32" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I32" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J32" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K32" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L32" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M32" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N32" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O32" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3217,14 +3214,18 @@
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3236,50 +3237,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C33" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D33" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E33" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F33" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H33" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I33" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J33" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K33" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L33" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M33" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N33" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O33" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3297,18 +3298,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3320,50 +3317,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C34" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D34" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E34" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F34" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H34" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I34" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J34" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K34" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L34" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M34" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N34" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3381,14 +3378,16 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3400,50 +3399,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C35" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D35" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E35" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F35" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H35" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I35" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J35" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K35" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L35" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M35" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N35" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O35" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3461,16 +3460,14 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V35" s="8" t="n">
+        <v/>
       </c>
       <c r="W35" s="9" t="inlineStr">
         <is>
@@ -3482,79 +3479,81 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C36" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D36" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E36" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F36" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I36" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J36" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K36" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L36" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M36" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N36" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O36" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="Q36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3562,72 +3561,70 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C37" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D37" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E37" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F37" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H37" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I37" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J37" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K37" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L37" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M37" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N37" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O37" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3639,73 +3636,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C38" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D38" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E38" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F38" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H38" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I38" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J38" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K38" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L38" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M38" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N38" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O38" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U38" s="8" t="n">
@@ -3728,58 +3733,56 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C39" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D39" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E39" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F39" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H39" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I39" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J39" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K39" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L39" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M39" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N39" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O39" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q39" s="6" t="n">
+        <v/>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3788,13 +3791,11 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3816,50 +3817,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C40" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D40" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E40" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F40" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H40" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I40" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J40" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K40" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L40" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M40" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N40" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O40" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3867,83 +3868,83 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C41" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D41" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E41" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F41" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H41" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I41" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J41" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K41" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L41" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M41" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N41" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O41" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3961,18 +3962,14 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3984,79 +3981,83 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C42" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D42" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E42" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F42" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H42" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I42" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J42" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K42" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L42" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M42" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N42" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O42" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+        <v>4032.76</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr"/>
@@ -4064,69 +4065,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C43" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D43" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E43" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F43" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H43" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I43" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J43" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K43" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L43" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M43" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N43" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O43" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4042.69</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4143,55 +4138,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C44" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D44" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E44" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F44" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H44" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I44" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J44" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K44" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L44" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M44" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O44" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4199,12 +4198,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4223,72 +4224,76 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C45" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D45" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E45" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F45" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H45" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I45" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J45" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K45" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L45" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M45" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N45" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O45" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4305,78 +4310,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C46" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D46" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E46" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F46" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H46" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I46" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J46" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K46" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L46" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M46" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N46" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O46" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4393,55 +4390,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C47" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D47" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E47" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F47" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I47" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J47" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K47" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L47" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M47" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N47" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O47" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4449,18 +4450,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4475,57 +4476,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C48" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D48" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E48" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F48" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H48" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I48" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J48" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K48" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L48" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M48" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N48" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O48" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4543,11 +4544,13 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4566,50 +4569,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C49" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D49" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E49" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F49" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H49" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I49" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J49" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K49" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L49" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M49" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N49" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O49" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,18 +4625,14 @@
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4645,57 +4644,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C50" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D50" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E50" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H50" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I50" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J50" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K50" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L50" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M50" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N50" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O50" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4703,81 +4702,89 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C51" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D51" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E51" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F51" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H51" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I51" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J51" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K51" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L51" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N51" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O51" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,30 +4792,22 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4824,63 +4823,69 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C52" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D52" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E52" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F52" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H52" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I52" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J52" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K52" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L52" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M52" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N52" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O52" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4013.88</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4892,87 +4897,79 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C53" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D53" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E53" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F53" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H53" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I53" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J53" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K53" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L53" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M53" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N53" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O53" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3999.37</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4985,55 +4982,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C54" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D54" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E54" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H54" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I54" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J54" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K54" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L54" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M54" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N54" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O54" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5041,12 +5042,14 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5054,8 +5057,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5067,57 +5072,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C55" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D55" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E55" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F55" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H55" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I55" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J55" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K55" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L55" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M55" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N55" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O55" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5125,25 +5130,19 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5155,57 +5154,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C56" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D56" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E56" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F56" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I56" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J56" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K56" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L56" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M56" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N56" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O56" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5216,13 +5215,15 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5237,57 +5238,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C57" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D57" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E57" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F57" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H57" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I57" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J57" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K57" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L57" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M57" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N57" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O57" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5300,12 +5301,12 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U57" s="8" t="n">
@@ -5328,70 +5329,72 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C58" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D58" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E58" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F58" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H58" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I58" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J58" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K58" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L58" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M58" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N58" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O58" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5403,66 +5406,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C59" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D59" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E59" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F59" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H59" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I59" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J59" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K59" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L59" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M59" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N59" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O59" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
@@ -5494,69 +5495,63 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C60" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D60" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E60" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F60" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H60" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I60" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J60" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K60" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L60" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M60" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N60" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O60" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3972.62</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5573,68 +5568,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C61" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D61" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E61" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H61" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I61" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J61" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K61" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L61" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M61" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N61" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O61" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5651,84 +5654,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C62" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D62" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E62" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F62" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H62" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I62" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J62" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K62" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L62" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M62" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N62" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O62" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
@@ -5737,55 +5738,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C63" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D63" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E63" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F63" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H63" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I63" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J63" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K63" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L63" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M63" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N63" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O63" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5793,25 +5798,19 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
@@ -5830,50 +5829,50 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C64" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D64" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E64" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F64" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H64" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I64" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J64" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K64" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L64" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M64" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N64" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O64" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5884,81 +5883,83 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U64" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C65" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D65" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E65" t="n">
-        <v>3911.87</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>36.27</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0094</v>
+        <v/>
       </c>
       <c r="H65" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I65" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J65" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K65" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L65" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M65" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N65" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O65" t="n">
-        <v>3930.78</v>
-      </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+        <v>3950.84</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5966,9 +5967,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
@@ -5978,11 +5979,13 @@
       </c>
       <c r="U65" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,20 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4090.1</v>
+        <v>4103.48</v>
       </c>
       <c r="C2" t="n">
-        <v>4117.29</v>
+        <v>4133.1</v>
       </c>
       <c r="D2" t="n">
-        <v>4075.49</v>
+        <v>4093.01</v>
       </c>
       <c r="E2" t="n">
-        <v>4110.81</v>
+        <v>4120.28</v>
       </c>
       <c r="F2" t="n">
-        <v>4.56</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0011</v>
+        <v>0.0023</v>
       </c>
       <c r="H2" t="n">
-        <v>41.79</v>
+        <v>40.09</v>
       </c>
       <c r="I2" t="n">
-        <v>3995.83</v>
+        <v>4033.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4004.38</v>
+        <v>4076.23</v>
       </c>
       <c r="K2" t="n">
-        <v>4061.37</v>
+        <v>4089.92</v>
       </c>
       <c r="L2" t="n">
-        <v>4118.36</v>
+        <v>4103.6</v>
       </c>
       <c r="M2" t="n">
-        <v>4151.13</v>
+        <v>4131.71</v>
       </c>
       <c r="N2" t="n">
-        <v>4183.9</v>
+        <v>4159.82</v>
       </c>
       <c r="O2" t="n">
-        <v>4265.11</v>
+        <v>4159.08</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -693,11 +690,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -710,78 +709,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C3" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D3" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E3" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F3" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H3" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I3" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J3" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K3" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L3" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M3" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N3" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O3" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+        <v>4173.19</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -789,9 +788,9 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -799,74 +798,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C4" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D4" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E4" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F4" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H4" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I4" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J4" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K4" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L4" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M4" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N4" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O4" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -878,55 +873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C5" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D5" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E5" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F5" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H5" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I5" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J5" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K5" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L5" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M5" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N5" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O5" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,7 +936,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -960,57 +959,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C6" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D6" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E6" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F6" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H6" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I6" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J6" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K6" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L6" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M6" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N6" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O6" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,7 +1020,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1034,8 +1033,10 @@
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="11" t="inlineStr">
         <is>
@@ -1051,159 +1052,153 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C7" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D7" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E7" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F7" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H7" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J7" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K7" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L7" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M7" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N7" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O7" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C8" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D8" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E8" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F8" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H8" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I8" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J8" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K8" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L8" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M8" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N8" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O8" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1216,55 +1211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C9" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D9" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E9" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F9" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J9" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K9" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L9" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M9" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N9" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O9" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,18 +1271,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1296,74 +1295,72 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C10" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D10" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E10" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H10" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I10" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J10" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K10" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L10" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M10" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N10" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O10" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1385,65 +1382,63 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C11" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D11" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E11" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F11" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H11" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I11" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J11" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K11" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L11" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M11" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N11" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O11" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1467,50 +1462,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C12" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D12" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E12" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F12" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H12" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I12" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K12" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L12" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M12" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N12" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O12" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,77 +1515,87 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C13" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D13" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E13" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F13" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H13" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I13" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J13" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K13" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L13" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M13" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N13" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O13" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1600,28 +1605,22 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1637,63 +1636,65 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C14" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D14" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E14" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F14" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H14" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I14" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J14" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K14" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L14" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M14" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N14" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O14" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1714,79 +1715,79 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C15" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D15" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E15" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F15" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H15" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J15" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K15" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L15" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M15" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N15" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O15" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
@@ -1800,57 +1801,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C16" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D16" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E16" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F16" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H16" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I16" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J16" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K16" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L16" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N16" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O16" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1858,20 +1859,16 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1886,70 +1883,76 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C17" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D17" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E17" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F17" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H17" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I17" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J17" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K17" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L17" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M17" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N17" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O17" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1961,64 +1964,60 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C18" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D18" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E18" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F18" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H18" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I18" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J18" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K18" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L18" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M18" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N18" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O18" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -2035,7 +2034,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2059,73 +2058,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C19" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D19" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E19" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F19" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I19" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J19" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K19" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L19" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N19" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O19" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2138,55 +2133,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C20" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D20" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E20" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F20" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H20" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I20" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J20" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K20" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L20" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M20" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N20" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O20" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,17 +2193,19 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U20" s="8" t="n">
@@ -2220,57 +2221,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C21" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D21" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E21" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F21" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H21" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I21" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J21" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K21" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L21" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M21" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N21" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O21" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2278,20 +2279,16 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2313,50 +2310,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C22" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D22" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E22" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F22" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H22" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I22" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J22" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K22" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L22" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M22" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N22" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O22" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2367,7 +2364,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2388,70 +2385,76 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C23" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D23" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E23" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F23" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H23" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I23" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J23" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K23" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L23" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M23" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N23" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O23" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2468,167 +2471,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C24" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D24" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E24" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H24" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I24" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J24" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K24" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L24" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M24" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N24" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O24" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C25" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D25" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E25" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F25" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H25" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I25" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J25" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K25" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L25" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M25" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N25" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O25" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2647,72 +2648,72 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C26" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D26" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E26" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F26" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H26" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I26" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J26" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K26" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L26" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M26" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N26" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O26" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2726,78 +2727,78 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C27" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D27" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E27" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F27" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H27" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I27" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J27" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K27" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L27" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N27" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O27" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2812,79 +2813,77 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C28" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D28" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E28" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F28" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H28" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I28" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J28" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K28" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L28" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M28" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N28" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O28" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2896,78 +2895,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C29" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D29" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E29" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F29" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H29" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I29" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J29" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K29" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L29" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N29" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O29" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2980,79 +2979,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C30" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D30" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E30" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F30" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H30" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I30" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J30" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K30" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L30" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M30" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N30" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O30" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3064,59 +3063,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C31" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D31" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E31" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F31" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H31" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I31" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J31" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K31" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L31" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M31" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N31" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O31" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3127,21 +3122,25 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3153,50 +3152,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C32" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D32" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E32" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F32" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H32" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I32" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J32" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K32" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L32" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M32" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N32" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O32" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3207,25 +3206,21 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3237,50 +3232,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C33" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D33" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E33" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F33" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H33" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I33" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J33" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K33" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L33" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M33" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N33" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,21 +3286,23 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3317,50 +3314,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C34" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D34" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E34" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F34" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H34" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I34" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J34" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K34" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L34" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M34" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N34" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O34" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,23 +3368,21 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
@@ -3399,69 +3394,71 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C35" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D35" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E35" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F35" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I35" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J35" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K35" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L35" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M35" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N35" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O35" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3469,9 +3466,9 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3479,72 +3476,70 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C36" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D36" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E36" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F36" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H36" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I36" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J36" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K36" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L36" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M36" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N36" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O36" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3556,73 +3551,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C37" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D37" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E37" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F37" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H37" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I37" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J37" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K37" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L37" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M37" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N37" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O37" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U37" s="8" t="n">
@@ -3645,73 +3648,69 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C38" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D38" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E38" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F38" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H38" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I38" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J38" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K38" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L38" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M38" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N38" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O38" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3733,50 +3732,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C39" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D39" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E39" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F39" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H39" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I39" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J39" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K39" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L39" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M39" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N39" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O39" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3784,83 +3783,83 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C40" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D40" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E40" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F40" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H40" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I40" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J40" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K40" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L40" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M40" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N40" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O40" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3871,25 +3870,21 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V40" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V40" s="8" t="n">
+        <v/>
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
@@ -3901,69 +3896,73 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C41" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D41" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E41" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F41" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H41" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I41" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J41" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K41" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L41" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M41" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N41" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O41" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3971,9 +3970,9 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr"/>
@@ -3981,69 +3980,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C42" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D42" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E42" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F42" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H42" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I42" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J42" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K42" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L42" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M42" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N42" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O42" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4060,55 +4053,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C43" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D43" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E43" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F43" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H43" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I43" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J43" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K43" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L43" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M43" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O43" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4116,12 +4113,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4140,63 +4139,67 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C44" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D44" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E44" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F44" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H44" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I44" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J44" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K44" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L44" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M44" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N44" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O44" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
@@ -4205,7 +4208,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4222,69 +4225,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C45" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D45" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E45" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F45" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H45" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I45" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J45" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K45" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L45" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M45" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N45" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O45" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
@@ -4293,7 +4288,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4310,55 +4305,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C46" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D46" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E46" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F46" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I46" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J46" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K46" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L46" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M46" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N46" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O46" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,18 +4365,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4392,57 +4391,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C47" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D47" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E47" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F47" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H47" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I47" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J47" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K47" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L47" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M47" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N47" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O47" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4453,18 +4452,20 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4483,50 +4484,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C48" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D48" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E48" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F48" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H48" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I48" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J48" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K48" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L48" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M48" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N48" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O48" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4537,20 +4538,16 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4562,57 +4559,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C49" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D49" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E49" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F49" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H49" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I49" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J49" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K49" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L49" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M49" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N49" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O49" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4620,81 +4617,89 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C50" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D50" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E50" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F50" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I50" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J50" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K50" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L50" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M50" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N50" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O50" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4702,30 +4707,22 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4741,63 +4738,69 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C51" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D51" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E51" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F51" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H51" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I51" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J51" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K51" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L51" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M51" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N51" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O51" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4809,87 +4812,79 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W51" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C52" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D52" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E52" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F52" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H52" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I52" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J52" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K52" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L52" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M52" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N52" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O52" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4902,55 +4897,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C53" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D53" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E53" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H53" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I53" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J53" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K53" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L53" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M53" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N53" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O53" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4958,12 +4957,14 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -4971,8 +4972,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4984,57 +4987,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C54" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D54" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E54" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F54" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H54" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I54" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J54" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K54" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L54" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M54" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N54" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O54" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5042,25 +5045,19 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5072,57 +5069,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C55" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D55" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E55" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F55" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H55" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I55" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J55" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K55" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L55" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M55" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N55" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O55" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5135,11 +5132,13 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5154,57 +5153,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C56" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D56" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E56" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F56" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H56" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I56" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J56" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K56" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L56" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M56" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N56" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O56" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5215,14 +5214,14 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5245,69 +5244,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C57" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D57" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E57" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F57" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H57" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I57" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J57" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K57" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L57" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M57" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N57" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O57" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5320,66 +5321,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C58" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D58" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E58" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F58" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H58" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I58" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J58" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K58" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L58" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M58" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N58" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O58" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
@@ -5387,7 +5386,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5411,69 +5410,63 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C59" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D59" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E59" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F59" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H59" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I59" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J59" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K59" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L59" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M59" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N59" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O59" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5490,68 +5483,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C60" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D60" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E60" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H60" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I60" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J60" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K60" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L60" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M60" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N60" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O60" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5568,84 +5569,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C61" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D61" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E61" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F61" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H61" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I61" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J61" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K61" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L61" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M61" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N61" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O61" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
@@ -5654,55 +5653,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C62" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D62" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E62" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F62" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H62" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I62" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J62" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K62" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L62" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M62" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N62" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O62" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5710,25 +5713,19 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
@@ -5747,50 +5744,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C63" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D63" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E63" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F63" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H63" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I63" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J63" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K63" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L63" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M63" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N63" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O63" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5803,76 +5800,76 @@
       </c>
       <c r="S63" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C64" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D64" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E64" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F64" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H64" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I64" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J64" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K64" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L64" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M64" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N64" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O64" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P64" s="6" t="n">
         <v/>
@@ -5883,7 +5880,7 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="10" t="inlineStr">
+      <c r="S64" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5895,11 +5892,13 @@
       </c>
       <c r="U64" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V64" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
       </c>
       <c r="W64" s="9" t="inlineStr">
         <is>
@@ -5911,55 +5910,53 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C65" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D65" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E65" t="n">
-        <v/>
+        <v>3952.13</v>
       </c>
       <c r="F65" t="n">
-        <v/>
+        <v>2.22</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v/>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I65" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J65" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K65" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L65" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M65" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N65" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O65" t="n">
-        <v>3950.84</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3983.75</v>
+      </c>
+      <c r="P65" s="6" t="n">
+        <v/>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5967,9 +5964,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S65" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">
@@ -5977,15 +5974,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U65" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V65" s="8" t="n">
+        <v/>
       </c>
       <c r="W65" s="9" t="inlineStr">
         <is>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5923,13 +5926,13 @@
         <v>3945.42</v>
       </c>
       <c r="E65" t="n">
-        <v>3952.13</v>
+        <v/>
       </c>
       <c r="F65" t="n">
-        <v>2.22</v>
+        <v/>
       </c>
       <c r="G65" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v/>
       </c>
       <c r="H65" t="n">
         <v>22.26</v>
@@ -5955,8 +5958,10 @@
       <c r="O65" t="n">
         <v>3983.75</v>
       </c>
-      <c r="P65" s="6" t="n">
-        <v/>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q65" s="6" t="n">
         <v/>
@@ -5964,9 +5969,9 @@
       <c r="R65" s="6" t="n">
         <v/>
       </c>
-      <c r="S65" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S65" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T65" s="8" t="inlineStr">

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X65"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,69 +637,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4103.48</v>
+        <v>4098.69</v>
       </c>
       <c r="C2" t="n">
-        <v>4133.1</v>
+        <v>4099.78</v>
       </c>
       <c r="D2" t="n">
-        <v>4093.01</v>
+        <v>4007.86</v>
       </c>
       <c r="E2" t="n">
-        <v>4120.28</v>
+        <v>4027.26</v>
       </c>
       <c r="F2" t="n">
-        <v>9.470000000000001</v>
+        <v>-93.02</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.0226</v>
       </c>
       <c r="H2" t="n">
-        <v>40.09</v>
+        <v>91.92</v>
       </c>
       <c r="I2" t="n">
-        <v>4033.7</v>
+        <v>4052.92</v>
       </c>
       <c r="J2" t="n">
-        <v>4076.23</v>
+        <v>4083.81</v>
       </c>
       <c r="K2" t="n">
-        <v>4089.92</v>
+        <v>4100.24</v>
       </c>
       <c r="L2" t="n">
-        <v>4103.6</v>
+        <v>4116.67</v>
       </c>
       <c r="M2" t="n">
-        <v>4131.71</v>
+        <v>4140.33</v>
       </c>
       <c r="N2" t="n">
-        <v>4159.82</v>
+        <v>4163.98</v>
       </c>
       <c r="O2" t="n">
-        <v>4159.08</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>4173.19</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,7 +713,7 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -717,134 +721,134 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C3" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D3" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E3" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F3" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H3" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I3" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J3" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K3" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L3" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M3" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N3" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O3" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C4" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D4" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E4" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F4" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H4" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I4" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J4" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L4" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M4" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N4" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O4" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,7 +859,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -871,64 +875,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C5" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D5" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E5" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F5" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H5" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I5" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J5" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K5" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L5" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M5" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N5" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O5" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,7 +943,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -952,10 +956,12 @@
       <c r="U5" s="8" t="n">
         <v/>
       </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -969,159 +975,153 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C6" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D6" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E6" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F6" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H6" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J6" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K6" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L6" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M6" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N6" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O6" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="V6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C7" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D7" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E7" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F7" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H7" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I7" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J7" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K7" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L7" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M7" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N7" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O7" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1129,60 +1129,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C8" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D8" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E8" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F8" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I8" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J8" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K8" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L8" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M8" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N8" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O8" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,18 +1194,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1209,79 +1213,77 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C9" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D9" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E9" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H9" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I9" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J9" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K9" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L9" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M9" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N9" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O9" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1293,7 +1295,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1303,65 +1305,63 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C10" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D10" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E10" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F10" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H10" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I10" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J10" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K10" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L10" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M10" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N10" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O10" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1375,7 +1375,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1385,50 +1385,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C11" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D11" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E11" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F11" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H11" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I11" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J11" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K11" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L11" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M11" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N11" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O11" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,77 +1438,87 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C12" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D12" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E12" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F12" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H12" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I12" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J12" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K12" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L12" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M12" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N12" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O12" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,30 +1528,24 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W12" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1555,63 +1559,65 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C13" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D13" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E13" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F13" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H13" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I13" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J13" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K13" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L13" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M13" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N13" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O13" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1625,150 +1631,150 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C14" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D14" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E14" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F14" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H14" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J14" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K14" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L14" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M14" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N14" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O14" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C15" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D15" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E15" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F15" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H15" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I15" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J15" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K15" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L15" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N15" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O15" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,20 +1782,16 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,77 +1799,83 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C16" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D16" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E16" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F16" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H16" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I16" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J16" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K16" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L16" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M16" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N16" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O16" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1881,62 +1889,58 @@
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C17" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D17" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E17" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F17" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H17" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I17" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J17" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K17" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L17" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M17" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N17" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O17" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1953,7 +1957,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1967,7 +1971,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1977,73 +1981,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C18" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D18" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E18" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F18" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I18" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J18" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K18" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L18" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N18" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O18" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2051,60 +2051,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C19" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D19" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E19" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F19" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H19" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I19" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J19" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K19" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L19" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M19" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N19" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O19" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,17 +2116,19 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U19" s="8" t="n">
@@ -2131,64 +2137,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C20" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D20" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E20" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F20" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H20" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I20" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J20" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K20" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L20" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M20" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N20" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O20" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2196,20 +2202,16 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2217,7 +2219,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2231,50 +2233,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C21" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D21" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E21" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F21" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H21" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I21" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J21" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K21" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L21" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M21" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N21" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O21" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2285,7 +2287,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2299,77 +2301,83 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C22" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D22" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E22" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F22" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H22" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I22" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J22" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K22" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L22" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N22" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O22" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2381,177 +2389,175 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C23" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D23" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E23" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H23" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I23" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J23" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K23" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L23" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M23" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N23" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O23" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C24" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D24" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E24" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F24" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H24" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I24" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J24" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K24" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L24" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M24" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N24" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O24" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2565,157 +2571,157 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C25" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D25" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E25" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F25" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H25" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I25" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J25" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K25" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L25" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M25" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N25" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O25" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C26" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D26" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E26" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F26" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H26" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I26" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J26" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K26" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L26" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N26" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O26" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2723,169 +2729,167 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C27" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D27" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E27" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F27" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H27" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I27" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J27" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K27" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L27" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M27" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N27" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O27" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C28" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D28" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E28" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F28" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H28" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I28" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J28" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K28" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L28" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M28" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N28" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O28" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2893,148 +2897,144 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C29" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D29" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E29" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F29" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H29" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I29" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J29" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K29" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L29" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M29" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N29" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O29" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C30" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D30" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E30" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F30" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H30" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I30" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J30" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K30" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L30" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M30" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N30" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O30" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,23 +3045,27 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3071,50 +3075,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C31" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D31" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E31" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F31" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H31" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I31" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J31" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K31" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L31" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M31" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N31" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O31" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3125,27 +3129,23 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3155,50 +3155,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C32" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D32" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E32" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F32" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H32" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I32" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J32" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K32" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L32" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N32" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O32" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,23 +3209,25 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3235,50 +3237,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C33" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D33" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E33" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F33" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H33" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I33" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J33" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K33" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L33" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M33" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N33" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O33" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3289,25 +3291,23 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="V33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3317,69 +3317,71 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C34" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D34" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E34" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F34" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I34" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J34" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K34" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L34" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M34" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N34" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O34" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3389,7 +3391,7 @@
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3397,150 +3399,156 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C35" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D35" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E35" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F35" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H35" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I35" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J35" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K35" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L35" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M35" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N35" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O35" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C36" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D36" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E36" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F36" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H36" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I36" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J36" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K36" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L36" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M36" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N36" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O36" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3549,7 +3557,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3563,73 +3571,69 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C37" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D37" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E37" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F37" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H37" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I37" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J37" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K37" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L37" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M37" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N37" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O37" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q37" s="6" t="n">
+        <v/>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3637,7 +3641,7 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3651,50 +3655,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C38" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D38" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E38" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F38" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H38" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I38" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J38" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K38" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L38" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M38" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N38" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O38" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,83 +3706,83 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W38" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C39" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D39" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E39" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F39" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H39" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I39" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J39" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K39" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L39" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M39" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N39" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O39" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3789,27 +3793,23 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3819,69 +3819,73 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C40" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D40" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E40" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F40" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H40" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I40" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J40" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K40" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L40" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M40" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N40" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O40" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3891,7 +3895,7 @@
       </c>
       <c r="W40" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr"/>
@@ -3899,69 +3903,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C41" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D41" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E41" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F41" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H41" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I41" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J41" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K41" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L41" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M41" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N41" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O41" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3973,60 +3971,64 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C42" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D42" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E42" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F42" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H42" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I42" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J42" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K42" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L42" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M42" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O42" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4034,12 +4036,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4051,70 +4055,74 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C43" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D43" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E43" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F43" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H43" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I43" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J43" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K43" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L43" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M43" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N43" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O43" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4123,7 +4131,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4135,74 +4143,66 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C44" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D44" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E44" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F44" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H44" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I44" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J44" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K44" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L44" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M44" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N44" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O44" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4223,60 +4223,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C45" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D45" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E45" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F45" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H45" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I45" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J45" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K45" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L45" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M45" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N45" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O45" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,18 +4288,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4303,64 +4307,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C46" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D46" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E46" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F46" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H46" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I46" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J46" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K46" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L46" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M46" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N46" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O46" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4371,23 +4375,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4401,50 +4407,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C47" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D47" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E47" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F47" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H47" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I47" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J47" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K47" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L47" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M47" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N47" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O47" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4455,82 +4461,78 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C48" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D48" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E48" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F48" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H48" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I48" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J48" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K48" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L48" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M48" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N48" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O48" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4538,81 +4540,89 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C49" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D49" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E49" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F49" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H49" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I49" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J49" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K49" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L49" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M49" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N49" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O49" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4620,32 +4630,24 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4659,63 +4661,69 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C50" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D50" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E50" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F50" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H50" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I50" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J50" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K50" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L50" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M50" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N50" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O50" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4729,85 +4737,77 @@
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C51" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D51" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E51" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F51" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H51" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I51" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J51" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K51" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L51" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M51" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N51" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O51" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4815,60 +4815,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C52" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D52" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E52" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H52" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I52" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J52" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K52" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L52" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M52" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N52" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O52" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4876,12 +4880,14 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4889,70 +4895,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C53" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D53" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E53" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F53" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I53" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J53" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K53" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L53" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M53" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N53" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O53" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4960,87 +4968,81 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C54" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D54" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E54" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F54" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H54" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I54" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J54" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K54" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L54" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M54" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N54" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O54" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5053,11 +5055,13 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5065,64 +5069,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C55" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D55" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E55" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F55" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H55" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I55" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J55" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K55" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L55" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M55" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N55" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O55" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5133,14 +5137,14 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5149,7 +5153,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5163,69 +5167,71 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C56" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D56" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E56" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F56" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H56" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I56" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J56" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K56" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L56" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M56" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N56" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O56" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5233,71 +5239,69 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C57" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D57" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E57" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F57" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H57" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I57" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J57" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K57" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L57" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M57" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N57" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O57" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
@@ -5305,7 +5309,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5319,7 +5323,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5329,69 +5333,63 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C58" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D58" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E58" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F58" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H58" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I58" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J58" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K58" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L58" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M58" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N58" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O58" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5403,73 +5401,81 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C59" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D59" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E59" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H59" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I59" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J59" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K59" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L59" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M59" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N59" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O59" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5481,146 +5487,148 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C60" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D60" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E60" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F60" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H60" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I60" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J60" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K60" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L60" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M60" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N60" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O60" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C61" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D61" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E61" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F61" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H61" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I61" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J61" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K61" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L61" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M61" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N61" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O61" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,30 +5636,24 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5665,50 +5667,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C62" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D62" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E62" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F62" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H62" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I62" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J62" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K62" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L62" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M62" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N62" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O62" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5721,76 +5723,76 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C63" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D63" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E63" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F63" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H63" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I63" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J63" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K63" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L63" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M63" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N63" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O63" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5801,7 +5803,7 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="7" t="inlineStr">
+      <c r="S63" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5813,13 +5815,15 @@
       </c>
       <c r="U63" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5829,53 +5833,55 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C64" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D64" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E64" t="n">
-        <v>3949.91</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>38.04</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>0.0097</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I64" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J64" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K64" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L64" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M64" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N64" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O64" t="n">
-        <v>3950.84</v>
-      </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+        <v>3983.75</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
@@ -5883,9 +5889,9 @@
       <c r="R64" s="6" t="n">
         <v/>
       </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="inlineStr">
@@ -5893,104 +5899,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V64" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>3963.81</v>
-      </c>
-      <c r="C65" t="n">
-        <v>3967.68</v>
-      </c>
-      <c r="D65" t="n">
-        <v>3945.42</v>
-      </c>
-      <c r="E65" t="n">
-        <v/>
-      </c>
-      <c r="F65" t="n">
-        <v/>
-      </c>
-      <c r="G65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H65" t="n">
-        <v>22.26</v>
-      </c>
-      <c r="I65" t="n">
-        <v>3885.32</v>
-      </c>
-      <c r="J65" t="n">
-        <v>3924.78</v>
-      </c>
-      <c r="K65" t="n">
-        <v>3933.5</v>
-      </c>
-      <c r="L65" t="n">
-        <v>3942.22</v>
-      </c>
-      <c r="M65" t="n">
-        <v>3966.31</v>
-      </c>
-      <c r="N65" t="n">
-        <v>3990.4</v>
-      </c>
-      <c r="O65" t="n">
-        <v>3983.75</v>
-      </c>
-      <c r="P65" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R65" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S65" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V65" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W65" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -5837,13 +5837,13 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3963.81</v>
+        <v>3951.37</v>
       </c>
       <c r="C64" t="n">
-        <v>3967.68</v>
+        <v>3951.52</v>
       </c>
       <c r="D64" t="n">
-        <v>3945.42</v>
+        <v>3941.39</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5855,7 +5855,7 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>22.26</v>
+        <v>10.14</v>
       </c>
       <c r="I64" t="n">
         <v>3885.32</v>
@@ -5894,10 +5894,8 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T64" s="8" t="n">
+        <v/>
       </c>
       <c r="U64" s="8" t="n">
         <v/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -5843,7 +5843,7 @@
         <v>3951.52</v>
       </c>
       <c r="D64" t="n">
-        <v>3941.39</v>
+        <v>3939.72</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5855,7 +5855,7 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>10.14</v>
+        <v>11.8</v>
       </c>
       <c r="I64" t="n">
         <v>3885.32</v>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -5843,7 +5843,7 @@
         <v>3951.52</v>
       </c>
       <c r="D64" t="n">
-        <v>3939.72</v>
+        <v>3937.2</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5855,7 +5855,7 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>11.8</v>
+        <v>14.32</v>
       </c>
       <c r="I64" t="n">
         <v>3885.32</v>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5833,7 +5830,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B64" t="n">
@@ -5843,19 +5840,19 @@
         <v>3951.52</v>
       </c>
       <c r="D64" t="n">
-        <v>3937.2</v>
+        <v>3934.46</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>3936.52</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-13.39</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0034</v>
       </c>
       <c r="H64" t="n">
-        <v>14.32</v>
+        <v>17.06</v>
       </c>
       <c r="I64" t="n">
         <v>3885.32</v>
@@ -5878,20 +5875,20 @@
       <c r="O64" t="n">
         <v>3983.75</v>
       </c>
-      <c r="P64" s="6" t="inlineStr">
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5908,7 +5905,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5843,13 +5846,13 @@
         <v>3934.46</v>
       </c>
       <c r="E64" t="n">
-        <v>3936.52</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-13.39</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0034</v>
+        <v/>
       </c>
       <c r="H64" t="n">
         <v>17.06</v>
@@ -5875,20 +5878,20 @@
       <c r="O64" t="n">
         <v>3983.75</v>
       </c>
-      <c r="P64" s="6" t="n">
-        <v/>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q64" s="6" t="n">
         <v/>
       </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S64" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5905,11 +5908,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -637,74 +637,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4098.69</v>
+        <v>4026.69</v>
       </c>
       <c r="C2" t="n">
-        <v>4099.78</v>
+        <v>4075.33</v>
       </c>
       <c r="D2" t="n">
-        <v>4007.86</v>
+        <v>3992.55</v>
       </c>
       <c r="E2" t="n">
-        <v>4027.26</v>
+        <v>4073.9</v>
       </c>
       <c r="F2" t="n">
-        <v>-93.02</v>
+        <v>46.64</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0116</v>
       </c>
       <c r="H2" t="n">
-        <v>91.92</v>
+        <v>82.78</v>
       </c>
       <c r="I2" t="n">
-        <v>4052.92</v>
+        <v>3915.94</v>
       </c>
       <c r="J2" t="n">
-        <v>4083.81</v>
+        <v>3922.07</v>
       </c>
       <c r="K2" t="n">
-        <v>4100.24</v>
+        <v>3981.3</v>
       </c>
       <c r="L2" t="n">
-        <v>4116.67</v>
+        <v>4040.54</v>
       </c>
       <c r="M2" t="n">
-        <v>4140.33</v>
+        <v>4073.23</v>
       </c>
       <c r="N2" t="n">
-        <v>4163.98</v>
+        <v>4105.91</v>
       </c>
       <c r="O2" t="n">
-        <v>4173.19</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>4191.7</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -713,58 +709,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C3" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D3" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E3" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F3" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H3" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I3" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J3" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L3" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M3" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N3" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O3" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -775,7 +775,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -793,62 +793,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C4" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D4" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E4" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F4" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H4" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I4" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J4" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K4" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L4" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M4" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N4" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O4" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,7 +855,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -872,176 +868,168 @@
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C5" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D5" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E5" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F5" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H5" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J5" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K5" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L5" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M5" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N5" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O5" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C6" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D6" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E6" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F6" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H6" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I6" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J6" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K6" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L6" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M6" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N6" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O6" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1049,60 +1037,64 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C7" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D7" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E7" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F7" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I7" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J7" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K7" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L7" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M7" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N7" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O7" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1110,18 +1102,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1129,79 +1121,77 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C8" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D8" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E8" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H8" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I8" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J8" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K8" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L8" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M8" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N8" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O8" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1213,7 +1203,7 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1223,65 +1213,63 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C9" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D9" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E9" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F9" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H9" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I9" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J9" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K9" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L9" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M9" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N9" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O9" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1295,7 +1283,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1305,50 +1293,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C10" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D10" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E10" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F10" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H10" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I10" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K10" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L10" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M10" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N10" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O10" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,77 +1346,87 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C11" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D11" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E11" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F11" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H11" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I11" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J11" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K11" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L11" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M11" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N11" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O11" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,30 +1436,24 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W11" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1475,63 +1467,65 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C12" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D12" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E12" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F12" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H12" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I12" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J12" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K12" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L12" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M12" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N12" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O12" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1545,150 +1539,150 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C13" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D13" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E13" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F13" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H13" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J13" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K13" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L13" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M13" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N13" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O13" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C14" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D14" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E14" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F14" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H14" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I14" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J14" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K14" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L14" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N14" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O14" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,20 +1690,16 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,77 +1707,83 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C15" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D15" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E15" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F15" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H15" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J15" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K15" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L15" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M15" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N15" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O15" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1801,62 +1797,58 @@
       </c>
       <c r="W15" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C16" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D16" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E16" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F16" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H16" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I16" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J16" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K16" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L16" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M16" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N16" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O16" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -1873,7 +1865,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1887,7 +1879,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1897,73 +1889,69 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C17" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D17" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E17" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F17" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I17" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J17" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K17" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L17" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N17" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O17" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1971,60 +1959,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C18" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D18" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E18" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F18" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H18" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I18" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J18" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K18" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L18" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M18" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N18" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O18" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2032,17 +2024,19 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U18" s="8" t="n">
@@ -2051,64 +2045,64 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C19" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D19" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E19" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F19" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H19" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I19" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J19" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K19" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L19" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M19" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N19" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O19" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2116,20 +2110,16 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2137,7 +2127,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2151,50 +2141,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C20" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D20" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E20" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F20" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H20" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I20" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J20" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K20" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L20" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M20" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N20" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O20" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2205,7 +2195,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -2219,77 +2209,83 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C21" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D21" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E21" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F21" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H21" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I21" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J21" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K21" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L21" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M21" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N21" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O21" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2301,177 +2297,175 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C22" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D22" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E22" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H22" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I22" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J22" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K22" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L22" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M22" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N22" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O22" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C23" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D23" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E23" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F23" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H23" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I23" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J23" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K23" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L23" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M23" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N23" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O23" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2485,157 +2479,157 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C24" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D24" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E24" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F24" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H24" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I24" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J24" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K24" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L24" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M24" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N24" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O24" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C25" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D25" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E25" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F25" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H25" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I25" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J25" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K25" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L25" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N25" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O25" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2643,169 +2637,167 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C26" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D26" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E26" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F26" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H26" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I26" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J26" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K26" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L26" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M26" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N26" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O26" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C27" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D27" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E27" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F27" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H27" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I27" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J27" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K27" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L27" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M27" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N27" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O27" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2813,148 +2805,144 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C28" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D28" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E28" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F28" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H28" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I28" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J28" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K28" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L28" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M28" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N28" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O28" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C29" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D29" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E29" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F29" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H29" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I29" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J29" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K29" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L29" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M29" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N29" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O29" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2965,23 +2953,27 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2991,50 +2983,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C30" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D30" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E30" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F30" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H30" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I30" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J30" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K30" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L30" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M30" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N30" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O30" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3045,27 +3037,23 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3075,50 +3063,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C31" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D31" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E31" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F31" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H31" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I31" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J31" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K31" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L31" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M31" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N31" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3129,23 +3117,25 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3155,50 +3145,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C32" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D32" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E32" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F32" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H32" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I32" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J32" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K32" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L32" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M32" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N32" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O32" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3209,25 +3199,23 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3237,69 +3225,71 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C33" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D33" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E33" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F33" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I33" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J33" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K33" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L33" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M33" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N33" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O33" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3309,7 +3299,7 @@
       </c>
       <c r="W33" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3317,150 +3307,156 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C34" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D34" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E34" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F34" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H34" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I34" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J34" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K34" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L34" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M34" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N34" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O34" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C35" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D35" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E35" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F35" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H35" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I35" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J35" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K35" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L35" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M35" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N35" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O35" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3469,7 +3465,7 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3483,73 +3479,69 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C36" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D36" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E36" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F36" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H36" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I36" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J36" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K36" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L36" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M36" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N36" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O36" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q36" s="6" t="n">
+        <v/>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3557,7 +3549,7 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3571,50 +3563,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C37" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D37" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E37" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F37" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H37" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I37" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J37" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K37" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L37" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M37" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N37" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O37" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3622,83 +3614,83 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C38" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D38" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E38" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F38" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I38" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J38" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K38" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L38" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M38" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N38" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O38" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3709,27 +3701,23 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3739,69 +3727,73 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C39" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D39" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E39" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F39" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H39" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I39" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J39" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K39" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L39" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M39" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N39" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O39" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3811,7 +3803,7 @@
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr"/>
@@ -3819,69 +3811,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C40" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D40" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E40" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F40" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H40" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I40" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J40" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K40" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L40" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M40" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N40" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O40" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3893,60 +3879,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C41" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D41" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E41" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F41" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H41" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I41" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J41" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K41" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L41" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M41" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N41" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O41" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3954,12 +3944,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3971,70 +3963,74 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C42" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D42" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E42" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F42" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H42" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I42" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J42" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K42" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L42" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M42" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N42" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O42" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4043,7 +4039,7 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4055,74 +4051,66 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C43" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D43" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E43" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F43" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H43" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I43" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J43" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K43" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L43" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M43" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N43" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O43" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4131,7 +4119,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4143,60 +4131,64 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C44" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D44" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E44" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F44" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H44" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I44" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J44" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K44" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L44" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M44" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N44" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O44" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4204,18 +4196,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4223,64 +4215,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C45" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D45" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E45" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F45" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H45" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I45" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J45" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K45" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L45" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M45" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N45" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O45" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4291,23 +4283,25 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4321,50 +4315,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C46" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D46" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E46" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F46" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H46" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I46" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J46" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K46" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L46" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N46" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O46" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,82 +4369,78 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C47" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D47" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E47" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H47" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I47" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J47" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K47" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L47" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M47" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N47" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O47" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4458,81 +4448,89 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C48" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D48" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E48" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F48" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H48" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I48" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J48" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K48" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L48" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M48" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N48" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O48" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4540,32 +4538,24 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4579,63 +4569,69 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C49" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D49" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E49" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F49" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H49" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I49" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J49" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K49" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L49" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M49" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N49" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O49" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4649,85 +4645,77 @@
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C50" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D50" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E50" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F50" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H50" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I50" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J50" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K50" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L50" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M50" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N50" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O50" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4735,60 +4723,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C51" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D51" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E51" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I51" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J51" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K51" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L51" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M51" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N51" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O51" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4796,12 +4788,14 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4809,70 +4803,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C52" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D52" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E52" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F52" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I52" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J52" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K52" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L52" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M52" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N52" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O52" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4880,87 +4876,81 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C53" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D53" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E53" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F53" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H53" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I53" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J53" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K53" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L53" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M53" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N53" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O53" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4973,11 +4963,13 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4985,64 +4977,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C54" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D54" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E54" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F54" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H54" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I54" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J54" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K54" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L54" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M54" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N54" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O54" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5053,14 +5045,14 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5069,7 +5061,7 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5083,69 +5075,71 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C55" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D55" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E55" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F55" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H55" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I55" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J55" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K55" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L55" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M55" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N55" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O55" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5153,71 +5147,69 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C56" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D56" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E56" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F56" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H56" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I56" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J56" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K56" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L56" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M56" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N56" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O56" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
@@ -5225,7 +5217,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5239,7 +5231,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5249,69 +5241,63 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C57" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D57" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E57" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F57" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H57" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I57" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J57" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K57" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L57" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M57" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N57" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O57" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5323,73 +5309,81 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C58" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D58" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E58" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H58" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I58" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J58" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K58" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L58" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M58" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N58" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O58" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5401,146 +5395,148 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C59" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D59" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E59" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F59" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H59" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I59" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J59" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K59" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L59" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M59" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N59" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O59" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C60" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D60" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E60" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F60" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H60" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I60" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J60" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K60" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L60" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M60" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N60" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O60" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5548,30 +5544,24 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5585,50 +5575,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C61" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D61" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E61" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F61" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H61" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I61" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J61" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K61" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L61" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M61" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N61" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O61" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5641,76 +5631,76 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C62" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D62" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E62" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F62" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H62" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I62" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J62" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K62" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L62" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M62" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N62" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O62" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5721,7 +5711,7 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5733,13 +5723,15 @@
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5749,50 +5741,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3920.27</v>
+        <v>3951.37</v>
       </c>
       <c r="C63" t="n">
-        <v>3950.94</v>
+        <v>3951.52</v>
       </c>
       <c r="D63" t="n">
-        <v>3918.13</v>
+        <v>3934.46</v>
       </c>
       <c r="E63" t="n">
-        <v>3949.91</v>
+        <v>3936.52</v>
       </c>
       <c r="F63" t="n">
-        <v>38.04</v>
+        <v>-13.39</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0097</v>
+        <v>-0.0034</v>
       </c>
       <c r="H63" t="n">
-        <v>32.81</v>
+        <v>17.06</v>
       </c>
       <c r="I63" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J63" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K63" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L63" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M63" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N63" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O63" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5800,50 +5792,50 @@
       <c r="Q63" s="6" t="n">
         <v/>
       </c>
-      <c r="R63" s="6" t="n">
-        <v/>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3951.37</v>
+        <v>3925.32</v>
       </c>
       <c r="C64" t="n">
-        <v>3951.52</v>
+        <v>3930.5</v>
       </c>
       <c r="D64" t="n">
-        <v>3934.46</v>
+        <v>3888.37</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5855,39 +5847,43 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>17.06</v>
+        <v>42.12</v>
       </c>
       <c r="I64" t="n">
-        <v>3885.32</v>
+        <v>3917.39</v>
       </c>
       <c r="J64" t="n">
-        <v>3924.78</v>
+        <v>3916.22</v>
       </c>
       <c r="K64" t="n">
-        <v>3933.5</v>
+        <v>3927.99</v>
       </c>
       <c r="L64" t="n">
-        <v>3942.22</v>
+        <v>3939.76</v>
       </c>
       <c r="M64" t="n">
-        <v>3966.31</v>
+        <v>3945.05</v>
       </c>
       <c r="N64" t="n">
-        <v>3990.4</v>
+        <v>3950.35</v>
       </c>
       <c r="O64" t="n">
-        <v>3983.75</v>
+        <v>3968.59</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R64" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S64" s="12" t="inlineStr">
         <is>
@@ -5903,12 +5899,16 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
+      <c r="W64" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4026.69</v>
+        <v>4058.17</v>
       </c>
       <c r="C2" t="n">
-        <v>4075.33</v>
+        <v>4097.42</v>
       </c>
       <c r="D2" t="n">
-        <v>3992.55</v>
+        <v>4052.17</v>
       </c>
       <c r="E2" t="n">
-        <v>4073.9</v>
+        <v>4094.4</v>
       </c>
       <c r="F2" t="n">
-        <v>46.64</v>
+        <v>20.49</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.005</v>
       </c>
       <c r="H2" t="n">
-        <v>82.78</v>
+        <v>45.25</v>
       </c>
       <c r="I2" t="n">
-        <v>3915.94</v>
+        <v>3909.77</v>
       </c>
       <c r="J2" t="n">
-        <v>3922.07</v>
+        <v>4011.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3981.3</v>
+        <v>4032.51</v>
       </c>
       <c r="L2" t="n">
-        <v>4040.54</v>
+        <v>4053.92</v>
       </c>
       <c r="M2" t="n">
-        <v>4073.23</v>
+        <v>4115.29</v>
       </c>
       <c r="N2" t="n">
-        <v>4105.91</v>
+        <v>4176.66</v>
       </c>
       <c r="O2" t="n">
-        <v>4191.7</v>
+        <v>4158.12</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -712,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C3" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D3" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E3" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F3" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H3" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I3" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J3" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K3" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L3" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M3" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N3" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O3" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -788,8 +781,10 @@
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -801,81 +796,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C4" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D4" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E4" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F4" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H4" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J4" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K4" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L4" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M4" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N4" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O4" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>4199.09</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -883,73 +880,69 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C5" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D5" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E5" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F5" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H5" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I5" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J5" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K5" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L5" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M5" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N5" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O5" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+        <v>4168.14</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -962,55 +955,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C6" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D6" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E6" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F6" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I6" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J6" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K6" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L6" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M6" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N6" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O6" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1018,18 +1015,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1042,65 +1039,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C7" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D7" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E7" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H7" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I7" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J7" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K7" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L7" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M7" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N7" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O7" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
@@ -1109,7 +1104,7 @@
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1131,62 +1126,60 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C8" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D8" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E8" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F8" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H8" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I8" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J8" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K8" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L8" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M8" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N8" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
@@ -1213,50 +1206,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C9" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D9" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E9" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F9" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H9" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I9" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J9" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K9" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L9" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M9" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N9" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O9" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,77 +1259,87 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W9" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="W9" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C10" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D10" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E10" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F10" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H10" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I10" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J10" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K10" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L10" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N10" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O10" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1346,28 +1349,22 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1383,60 +1380,62 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C11" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D11" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E11" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F11" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H11" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I11" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J11" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K11" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L11" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M11" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N11" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O11" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
@@ -1460,79 +1459,79 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C12" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D12" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E12" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F12" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H12" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J12" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K12" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L12" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M12" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N12" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O12" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1546,57 +1545,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C13" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D13" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E13" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F13" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H13" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I13" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J13" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L13" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N13" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O13" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,20 +1603,16 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1632,70 +1627,76 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C14" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D14" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E14" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F14" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H14" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J14" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K14" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L14" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M14" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N14" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O14" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4019.65</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1707,64 +1708,60 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C15" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D15" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E15" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F15" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H15" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I15" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J15" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K15" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L15" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M15" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N15" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O15" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -1805,73 +1802,69 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C16" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D16" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E16" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F16" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I16" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J16" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K16" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L16" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M16" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N16" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O16" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+        <v>3993.26</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1884,55 +1877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C17" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D17" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E17" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F17" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H17" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I17" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J17" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K17" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L17" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M17" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N17" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O17" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,17 +1937,19 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U17" s="8" t="n">
@@ -1966,57 +1965,57 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C18" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D18" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E18" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F18" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H18" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I18" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J18" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K18" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L18" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M18" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N18" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O18" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2024,20 +2023,16 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R18" s="6" t="n">
+        <v/>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2059,50 +2054,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C19" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D19" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E19" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F19" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H19" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I19" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J19" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K19" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L19" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M19" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N19" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O19" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2134,70 +2129,76 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C20" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D20" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E20" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F20" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H20" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I20" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J20" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K20" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L20" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M20" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N20" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O20" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3905.96</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2214,167 +2215,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C21" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D21" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E21" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H21" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I21" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J21" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K21" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L21" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M21" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O21" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C22" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D22" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E22" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F22" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H22" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I22" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J22" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K22" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L22" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M22" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N22" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O22" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
+      <c r="Q22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2393,72 +2392,72 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C23" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D23" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E23" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F23" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H23" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I23" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J23" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K23" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L23" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M23" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N23" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O23" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2472,79 +2471,79 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C24" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D24" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E24" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F24" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H24" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I24" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J24" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K24" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L24" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N24" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O24" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2558,79 +2557,77 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C25" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D25" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E25" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F25" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H25" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I25" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J25" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K25" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L25" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M25" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N25" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O25" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2642,79 +2639,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C26" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D26" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E26" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F26" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H26" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I26" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J26" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K26" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L26" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N26" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O26" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+        <v>3871.81</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2726,79 +2723,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C27" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D27" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E27" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F27" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H27" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I27" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J27" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K27" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L27" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M27" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N27" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O27" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2810,59 +2807,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C28" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D28" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E28" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F28" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H28" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I28" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J28" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K28" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L28" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M28" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N28" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O28" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2880,14 +2873,18 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2899,50 +2896,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C29" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D29" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E29" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F29" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H29" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I29" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J29" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K29" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L29" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M29" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N29" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O29" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2960,18 +2957,14 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2983,50 +2976,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C30" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D30" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E30" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F30" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H30" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I30" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J30" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K30" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L30" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N30" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3044,14 +3037,16 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3063,50 +3058,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C31" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D31" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E31" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F31" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H31" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I31" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J31" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K31" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L31" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M31" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N31" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O31" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3124,16 +3119,14 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3145,79 +3138,81 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C32" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D32" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E32" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F32" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I32" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J32" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K32" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L32" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M32" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N32" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="Q32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr"/>
@@ -3225,72 +3220,70 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C33" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D33" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E33" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F33" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H33" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I33" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J33" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K33" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L33" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M33" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N33" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O33" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3302,73 +3295,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C34" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D34" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E34" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F34" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H34" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I34" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J34" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K34" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L34" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M34" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N34" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O34" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U34" s="8" t="n">
@@ -3391,58 +3392,56 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C35" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D35" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E35" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F35" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H35" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I35" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J35" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K35" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L35" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M35" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N35" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O35" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q35" s="6" t="n">
+        <v/>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3451,13 +3450,11 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3479,50 +3476,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C36" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D36" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E36" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F36" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H36" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I36" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J36" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K36" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L36" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M36" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N36" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O36" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3530,83 +3527,83 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C37" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D37" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E37" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F37" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I37" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J37" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K37" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L37" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M37" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N37" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O37" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3624,18 +3621,14 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3647,79 +3640,83 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C38" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D38" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E38" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F38" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H38" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I38" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J38" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K38" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L38" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M38" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N38" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O38" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>4032.76</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr"/>
@@ -3727,69 +3724,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C39" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D39" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E39" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F39" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H39" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I39" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J39" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K39" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L39" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M39" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N39" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O39" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4042.69</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3806,55 +3797,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C40" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D40" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E40" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F40" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H40" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I40" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J40" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K40" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L40" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M40" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N40" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O40" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3862,12 +3857,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3886,72 +3883,76 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C41" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D41" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E41" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F41" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H41" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I41" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J41" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K41" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L41" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M41" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N41" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O41" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3968,78 +3969,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C42" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D42" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E42" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F42" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H42" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I42" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J42" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K42" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L42" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M42" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N42" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O42" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4056,55 +4049,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C43" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D43" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E43" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F43" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H43" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I43" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J43" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K43" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L43" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M43" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N43" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O43" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4112,18 +4109,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4138,57 +4135,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C44" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D44" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E44" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F44" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H44" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I44" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J44" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K44" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L44" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M44" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N44" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O44" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4206,11 +4203,13 @@
       </c>
       <c r="T44" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4229,50 +4228,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C45" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D45" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E45" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F45" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H45" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I45" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J45" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K45" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L45" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M45" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N45" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O45" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4285,18 +4284,14 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4308,57 +4303,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C46" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D46" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E46" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F46" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H46" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I46" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J46" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K46" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L46" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M46" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N46" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O46" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,81 +4361,89 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C47" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D47" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E47" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F47" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I47" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J47" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K47" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L47" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M47" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N47" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O47" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4448,30 +4451,22 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4487,63 +4482,69 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C48" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D48" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E48" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F48" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H48" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I48" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J48" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K48" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L48" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M48" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N48" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O48" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4013.88</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4555,87 +4556,79 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C49" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D49" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E49" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F49" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H49" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I49" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J49" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K49" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L49" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M49" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N49" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O49" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3999.37</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4648,55 +4641,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C50" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D50" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E50" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I50" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J50" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K50" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L50" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M50" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N50" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O50" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4704,12 +4701,14 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4717,8 +4716,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4730,57 +4731,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C51" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D51" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E51" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F51" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I51" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J51" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K51" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L51" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M51" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N51" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O51" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4788,25 +4789,19 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4818,57 +4813,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C52" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D52" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E52" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F52" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I52" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J52" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K52" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L52" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M52" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N52" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O52" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,13 +4874,15 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4900,57 +4897,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C53" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D53" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E53" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F53" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H53" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I53" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J53" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K53" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L53" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M53" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N53" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O53" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4963,12 +4960,12 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4991,70 +4988,72 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C54" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D54" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E54" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F54" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H54" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I54" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J54" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K54" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L54" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M54" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N54" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O54" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5066,66 +5065,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C55" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D55" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E55" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F55" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H55" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I55" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J55" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K55" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L55" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M55" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N55" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O55" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
@@ -5157,69 +5154,63 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C56" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D56" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E56" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F56" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H56" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I56" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J56" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K56" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L56" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M56" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N56" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O56" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3972.62</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5236,68 +5227,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C57" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D57" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E57" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H57" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I57" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J57" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K57" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L57" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M57" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N57" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O57" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5314,84 +5313,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C58" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D58" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E58" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F58" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H58" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I58" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J58" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K58" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L58" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M58" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N58" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O58" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
@@ -5400,55 +5397,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C59" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D59" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E59" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F59" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H59" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I59" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J59" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K59" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L59" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M59" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N59" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O59" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5456,25 +5457,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5493,50 +5488,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C60" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D60" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E60" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F60" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H60" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I60" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J60" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K60" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L60" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M60" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N60" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O60" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5547,78 +5542,78 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C61" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D61" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E61" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F61" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H61" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I61" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J61" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K61" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L61" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M61" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N61" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O61" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5641,11 +5636,13 @@
       </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5657,50 +5654,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C62" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D62" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E62" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F62" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H62" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I62" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J62" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K62" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L62" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M62" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N62" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O62" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5713,7 +5710,7 @@
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
@@ -5721,15 +5718,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5757,34 +5750,34 @@
         <v>3936.52</v>
       </c>
       <c r="F63" t="n">
-        <v>-13.39</v>
+        <v>-15.61</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0034</v>
+        <v>-0.0039</v>
       </c>
       <c r="H63" t="n">
         <v>17.06</v>
       </c>
       <c r="I63" t="n">
-        <v>3885.32</v>
+        <v>3923.15</v>
       </c>
       <c r="J63" t="n">
-        <v>3924.78</v>
+        <v>3927.65</v>
       </c>
       <c r="K63" t="n">
-        <v>3933.5</v>
+        <v>3941</v>
       </c>
       <c r="L63" t="n">
-        <v>3942.22</v>
+        <v>3954.34</v>
       </c>
       <c r="M63" t="n">
-        <v>3966.31</v>
+        <v>3963.26</v>
       </c>
       <c r="N63" t="n">
-        <v>3990.4</v>
+        <v>3972.18</v>
       </c>
       <c r="O63" t="n">
-        <v>3983.75</v>
+        <v>3989.94</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5818,7 +5811,7 @@
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5838,13 +5831,13 @@
         <v>3888.37</v>
       </c>
       <c r="E64" t="n">
-        <v/>
+        <v>3888.37</v>
       </c>
       <c r="F64" t="n">
-        <v/>
+        <v>-48.15</v>
       </c>
       <c r="G64" s="5" t="n">
-        <v/>
+        <v>-0.0122</v>
       </c>
       <c r="H64" t="n">
         <v>42.12</v>
@@ -5872,22 +5865,22 @@
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="R64" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">
@@ -5899,16 +5892,12 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W64" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,50 +637,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4058.17</v>
+        <v>4090.76</v>
       </c>
       <c r="C2" t="n">
-        <v>4097.42</v>
+        <v>4143.31</v>
       </c>
       <c r="D2" t="n">
-        <v>4052.17</v>
+        <v>4087.53</v>
       </c>
       <c r="E2" t="n">
-        <v>4094.4</v>
+        <v>4112.44</v>
       </c>
       <c r="F2" t="n">
-        <v>20.49</v>
+        <v>18.05</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.005</v>
+        <v>0.0044</v>
       </c>
       <c r="H2" t="n">
-        <v>45.25</v>
+        <v>55.78</v>
       </c>
       <c r="I2" t="n">
-        <v>3909.77</v>
+        <v>4006.92</v>
       </c>
       <c r="J2" t="n">
-        <v>4011.1</v>
+        <v>4058.95</v>
       </c>
       <c r="K2" t="n">
-        <v>4032.51</v>
+        <v>4071.77</v>
       </c>
       <c r="L2" t="n">
-        <v>4053.92</v>
+        <v>4084.59</v>
       </c>
       <c r="M2" t="n">
-        <v>4115.29</v>
+        <v>4117.02</v>
       </c>
       <c r="N2" t="n">
-        <v>4176.66</v>
+        <v>4149.44</v>
       </c>
       <c r="O2" t="n">
-        <v>4158.12</v>
+        <v>4142.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -701,8 +704,10 @@
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -714,81 +719,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C3" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D3" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E3" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F3" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H3" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J3" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K3" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L3" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M3" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N3" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O3" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>4199.09</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -796,73 +803,69 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C4" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D4" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E4" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F4" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H4" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I4" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J4" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K4" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L4" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M4" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N4" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O4" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+        <v>4168.14</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,55 +878,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C5" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D5" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E5" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F5" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I5" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J5" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K5" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L5" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M5" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N5" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O5" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,18 +938,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,65 +962,63 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C6" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D6" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E6" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H6" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I6" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J6" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K6" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L6" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M6" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N6" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O6" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
@@ -1022,7 +1027,7 @@
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1044,62 +1049,60 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C7" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D7" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E7" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F7" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H7" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I7" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J7" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K7" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L7" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M7" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N7" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O7" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
@@ -1126,50 +1129,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C8" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D8" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E8" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F8" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H8" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I8" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J8" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K8" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L8" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M8" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N8" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O8" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1179,77 +1182,87 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C9" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D9" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E9" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F9" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H9" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I9" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J9" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K9" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L9" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M9" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N9" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O9" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1259,28 +1272,22 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1296,60 +1303,62 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C10" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D10" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E10" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F10" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H10" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I10" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J10" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K10" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L10" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M10" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N10" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O10" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
@@ -1373,79 +1382,79 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C11" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D11" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E11" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F11" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H11" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J11" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K11" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L11" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M11" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N11" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O11" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1459,57 +1468,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C12" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D12" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E12" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F12" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H12" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I12" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J12" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K12" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L12" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N12" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O12" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,20 +1526,16 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1545,70 +1550,76 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C13" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D13" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E13" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F13" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H13" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J13" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K13" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L13" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M13" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N13" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O13" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4019.65</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1620,64 +1631,60 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C14" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D14" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E14" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F14" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H14" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I14" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J14" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K14" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L14" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M14" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N14" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O14" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -1718,73 +1725,69 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C15" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D15" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E15" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F15" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I15" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J15" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K15" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L15" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N15" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O15" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+        <v>3993.26</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1797,55 +1800,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C16" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D16" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E16" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F16" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H16" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I16" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J16" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K16" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L16" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M16" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N16" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O16" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,17 +1860,19 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U16" s="8" t="n">
@@ -1879,57 +1888,57 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C17" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D17" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E17" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F17" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H17" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I17" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J17" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K17" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L17" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M17" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N17" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,20 +1946,16 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R17" s="6" t="n">
+        <v/>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1972,50 +1977,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C18" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D18" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E18" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F18" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H18" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I18" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J18" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K18" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L18" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M18" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N18" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O18" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2047,70 +2052,76 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C19" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D19" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E19" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F19" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H19" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I19" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J19" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K19" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L19" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M19" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N19" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O19" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3905.96</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2127,167 +2138,165 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C20" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D20" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E20" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H20" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I20" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J20" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K20" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L20" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M20" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N20" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O20" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C21" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D21" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E21" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F21" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H21" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I21" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J21" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K21" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L21" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M21" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N21" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O21" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2306,72 +2315,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C22" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D22" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E22" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F22" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H22" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I22" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J22" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K22" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L22" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M22" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N22" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O22" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
@@ -2385,79 +2394,79 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C23" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D23" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E23" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F23" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H23" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I23" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J23" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K23" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L23" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N23" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O23" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2471,79 +2480,77 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C24" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D24" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E24" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F24" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H24" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I24" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J24" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K24" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L24" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M24" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N24" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O24" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
@@ -2555,79 +2562,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C25" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D25" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E25" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F25" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H25" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I25" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J25" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K25" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L25" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N25" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O25" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
+        <v>3871.81</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
@@ -2639,79 +2646,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C26" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D26" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E26" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F26" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H26" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I26" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J26" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K26" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L26" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M26" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N26" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O26" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
@@ -2723,59 +2730,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C27" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D27" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E27" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F27" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H27" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I27" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J27" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K27" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L27" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M27" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N27" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O27" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2793,14 +2796,18 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2812,50 +2819,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C28" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D28" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E28" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F28" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H28" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I28" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J28" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K28" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L28" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M28" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N28" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O28" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,18 +2880,14 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2896,50 +2899,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C29" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D29" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E29" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F29" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H29" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I29" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J29" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K29" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L29" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M29" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N29" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2957,14 +2960,16 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2976,50 +2981,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C30" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D30" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E30" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F30" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H30" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I30" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J30" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K30" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L30" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M30" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N30" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O30" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3037,16 +3042,14 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3058,79 +3061,81 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C31" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D31" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E31" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F31" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I31" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J31" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K31" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L31" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M31" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N31" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O31" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="Q31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3138,72 +3143,70 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C32" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D32" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E32" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F32" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H32" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I32" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J32" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K32" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L32" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M32" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N32" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O32" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3215,73 +3218,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C33" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D33" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E33" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F33" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H33" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I33" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J33" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K33" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L33" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M33" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N33" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O33" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3304,58 +3315,56 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C34" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D34" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E34" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F34" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H34" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I34" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J34" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K34" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L34" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M34" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N34" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O34" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q34" s="6" t="n">
+        <v/>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
@@ -3364,13 +3373,11 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3392,50 +3399,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C35" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D35" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E35" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F35" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H35" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I35" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J35" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K35" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L35" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M35" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N35" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O35" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3443,83 +3450,83 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C36" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D36" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E36" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F36" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H36" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I36" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J36" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K36" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L36" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M36" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N36" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O36" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3537,18 +3544,14 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3560,79 +3563,83 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C37" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D37" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E37" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F37" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H37" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I37" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J37" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K37" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L37" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M37" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N37" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O37" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+        <v>4032.76</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr"/>
@@ -3640,69 +3647,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C38" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D38" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E38" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F38" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H38" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I38" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J38" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K38" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L38" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M38" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N38" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O38" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4042.69</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3719,55 +3720,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C39" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D39" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E39" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F39" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H39" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I39" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J39" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K39" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L39" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M39" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N39" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O39" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,12 +3780,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3799,72 +3806,76 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C40" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D40" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E40" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F40" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I40" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J40" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K40" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L40" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M40" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N40" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O40" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3881,78 +3892,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C41" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D41" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E41" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F41" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H41" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I41" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J41" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K41" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L41" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M41" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N41" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O41" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3969,55 +3972,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C42" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D42" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E42" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F42" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H42" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I42" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J42" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K42" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L42" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M42" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N42" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O42" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4025,18 +4032,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4051,57 +4058,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C43" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D43" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E43" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F43" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H43" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I43" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J43" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K43" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L43" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M43" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N43" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O43" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4119,11 +4126,13 @@
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4142,50 +4151,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C44" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D44" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E44" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F44" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H44" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I44" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J44" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K44" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L44" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M44" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N44" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O44" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4198,18 +4207,14 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4221,57 +4226,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C45" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D45" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E45" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F45" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H45" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I45" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J45" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K45" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L45" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M45" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N45" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O45" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4279,81 +4284,89 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C46" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D46" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E46" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F46" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I46" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J46" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K46" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L46" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M46" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N46" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O46" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4361,30 +4374,22 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4400,63 +4405,69 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C47" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D47" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E47" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F47" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H47" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I47" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J47" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K47" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L47" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M47" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N47" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O47" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4013.88</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4468,87 +4479,79 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C48" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D48" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E48" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F48" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H48" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I48" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J48" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K48" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L48" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M48" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N48" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O48" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3999.37</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4561,55 +4564,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C49" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D49" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E49" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I49" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J49" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K49" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L49" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M49" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N49" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O49" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,12 +4624,14 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4630,8 +4639,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4643,57 +4654,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C50" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D50" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E50" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F50" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I50" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J50" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K50" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L50" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M50" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N50" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O50" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4701,25 +4712,19 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4731,57 +4736,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C51" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D51" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E51" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F51" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I51" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J51" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K51" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L51" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M51" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N51" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O51" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4792,13 +4797,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4813,57 +4820,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C52" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D52" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E52" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F52" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H52" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I52" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J52" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K52" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L52" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M52" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N52" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O52" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4876,12 +4883,12 @@
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4904,70 +4911,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C53" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D53" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E53" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F53" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H53" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I53" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J53" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K53" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L53" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M53" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N53" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O53" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4979,66 +4988,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C54" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D54" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E54" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F54" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H54" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I54" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J54" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K54" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L54" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M54" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N54" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O54" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
@@ -5070,69 +5077,63 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C55" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D55" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E55" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F55" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H55" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I55" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J55" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K55" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L55" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M55" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N55" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O55" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3972.62</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5149,68 +5150,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C56" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D56" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E56" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H56" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I56" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J56" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K56" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L56" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M56" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N56" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O56" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5227,84 +5236,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C57" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D57" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E57" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F57" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H57" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I57" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J57" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K57" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L57" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M57" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N57" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O57" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5313,55 +5320,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C58" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D58" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E58" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F58" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H58" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I58" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J58" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K58" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L58" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M58" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N58" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O58" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5369,25 +5380,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5406,50 +5411,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C59" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D59" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E59" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F59" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H59" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I59" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J59" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K59" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L59" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M59" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N59" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O59" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5460,78 +5465,78 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C60" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D60" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E60" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F60" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H60" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I60" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K60" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L60" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M60" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N60" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O60" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5554,11 +5559,13 @@
       </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5570,50 +5577,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C61" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D61" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E61" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F61" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I61" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J61" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K61" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L61" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M61" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N61" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O61" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5626,7 +5633,7 @@
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5634,15 +5641,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5654,50 +5657,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3963.81</v>
+        <v>3951.37</v>
       </c>
       <c r="C62" t="n">
-        <v>3967.68</v>
+        <v>3951.52</v>
       </c>
       <c r="D62" t="n">
-        <v>3945.42</v>
+        <v>3934.46</v>
       </c>
       <c r="E62" t="n">
-        <v>3952.13</v>
+        <v>3936.52</v>
       </c>
       <c r="F62" t="n">
-        <v>2.22</v>
+        <v>-15.61</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="H62" t="n">
-        <v>22.26</v>
+        <v>17.06</v>
       </c>
       <c r="I62" t="n">
-        <v>3885.32</v>
+        <v>3923.15</v>
       </c>
       <c r="J62" t="n">
-        <v>3924.78</v>
+        <v>3927.65</v>
       </c>
       <c r="K62" t="n">
-        <v>3933.5</v>
+        <v>3941</v>
       </c>
       <c r="L62" t="n">
-        <v>3942.22</v>
+        <v>3954.34</v>
       </c>
       <c r="M62" t="n">
-        <v>3966.31</v>
+        <v>3963.26</v>
       </c>
       <c r="N62" t="n">
-        <v>3990.4</v>
+        <v>3972.18</v>
       </c>
       <c r="O62" t="n">
-        <v>3983.75</v>
+        <v>3989.94</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5705,18 +5708,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5729,65 +5732,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3951.37</v>
+        <v>3925.32</v>
       </c>
       <c r="C63" t="n">
-        <v>3951.52</v>
+        <v>3930.5</v>
       </c>
       <c r="D63" t="n">
-        <v>3934.46</v>
+        <v>3888.37</v>
       </c>
       <c r="E63" t="n">
-        <v>3936.52</v>
+        <v>3888.37</v>
       </c>
       <c r="F63" t="n">
-        <v>-15.61</v>
+        <v>-48.15</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0122</v>
       </c>
       <c r="H63" t="n">
-        <v>17.06</v>
+        <v>42.12</v>
       </c>
       <c r="I63" t="n">
-        <v>3923.15</v>
+        <v>3917.39</v>
       </c>
       <c r="J63" t="n">
-        <v>3927.65</v>
+        <v>3916.22</v>
       </c>
       <c r="K63" t="n">
-        <v>3941</v>
+        <v>3927.99</v>
       </c>
       <c r="L63" t="n">
-        <v>3954.34</v>
+        <v>3939.76</v>
       </c>
       <c r="M63" t="n">
-        <v>3963.26</v>
+        <v>3945.05</v>
       </c>
       <c r="N63" t="n">
-        <v>3972.18</v>
+        <v>3950.35</v>
       </c>
       <c r="O63" t="n">
-        <v>3989.94</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
+        <v>3968.59</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R63" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S63" s="10" t="inlineStr">
@@ -5804,73 +5815,69 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3925.32</v>
+        <v>3878.41</v>
       </c>
       <c r="C64" t="n">
-        <v>3930.5</v>
+        <v>3878.41</v>
       </c>
       <c r="D64" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E64" t="n">
-        <v>3888.37</v>
+        <v/>
       </c>
       <c r="F64" t="n">
-        <v>-48.15</v>
+        <v/>
       </c>
       <c r="G64" s="5" t="n">
-        <v>-0.0122</v>
+        <v/>
       </c>
       <c r="H64" t="n">
-        <v>42.12</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>3917.39</v>
+        <v>3846.25</v>
       </c>
       <c r="J64" t="n">
-        <v>3916.22</v>
+        <v>3835.72</v>
       </c>
       <c r="K64" t="n">
-        <v>3927.99</v>
+        <v>3867.31</v>
       </c>
       <c r="L64" t="n">
-        <v>3939.76</v>
+        <v>3898.9</v>
       </c>
       <c r="M64" t="n">
-        <v>3945.05</v>
+        <v>3909.44</v>
       </c>
       <c r="N64" t="n">
-        <v>3950.35</v>
+        <v>3919.97</v>
       </c>
       <c r="O64" t="n">
-        <v>3968.59</v>
+        <v>3972.62</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q64" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R64" s="6" t="inlineStr">
@@ -5878,9 +5885,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S64" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S64" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T64" s="8" t="n">

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -637,81 +637,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4090.76</v>
+        <v>4054.09</v>
       </c>
       <c r="C2" t="n">
-        <v>4143.31</v>
+        <v>4093.68</v>
       </c>
       <c r="D2" t="n">
-        <v>4087.53</v>
+        <v>4019.22</v>
       </c>
       <c r="E2" t="n">
-        <v>4112.44</v>
+        <v>4028.9</v>
       </c>
       <c r="F2" t="n">
-        <v>18.05</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0203</v>
       </c>
       <c r="H2" t="n">
-        <v>55.78</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>4006.92</v>
+        <v>4031.76</v>
       </c>
       <c r="J2" t="n">
-        <v>4058.95</v>
+        <v>4055.18</v>
       </c>
       <c r="K2" t="n">
-        <v>4071.77</v>
+        <v>4084.56</v>
       </c>
       <c r="L2" t="n">
-        <v>4084.59</v>
+        <v>4113.93</v>
       </c>
       <c r="M2" t="n">
-        <v>4117.02</v>
+        <v>4140.33</v>
       </c>
       <c r="N2" t="n">
-        <v>4149.44</v>
+        <v>4166.73</v>
       </c>
       <c r="O2" t="n">
-        <v>4142.66</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>4199.09</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -719,73 +721,69 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C3" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D3" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E3" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F3" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H3" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I3" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J3" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K3" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L3" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M3" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N3" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O3" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,60 +791,64 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C4" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D4" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E4" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F4" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J4" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K4" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L4" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M4" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N4" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O4" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,18 +856,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -873,79 +875,77 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C5" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D5" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E5" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H5" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I5" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J5" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K5" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L5" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M5" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N5" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O5" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -957,7 +957,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -967,65 +967,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C6" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D6" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E6" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F6" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H6" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I6" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J6" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K6" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L6" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M6" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N6" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O6" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1039,7 +1037,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1049,50 +1047,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C7" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D7" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E7" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F7" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H7" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I7" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J7" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K7" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L7" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M7" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N7" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O7" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1102,77 +1100,87 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
       <c r="W7" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C8" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D8" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E8" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F8" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H8" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I8" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J8" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K8" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L8" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M8" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N8" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O8" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1182,30 +1190,24 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W8" s="9" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1219,63 +1221,65 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C9" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D9" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E9" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F9" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H9" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I9" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J9" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K9" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L9" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M9" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N9" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O9" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1289,150 +1293,150 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C10" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D10" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E10" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F10" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H10" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J10" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K10" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L10" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M10" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N10" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O10" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C11" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D11" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E11" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F11" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H11" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I11" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J11" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K11" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L11" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M11" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N11" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O11" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1440,20 +1444,16 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1461,77 +1461,83 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C12" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D12" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E12" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F12" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H12" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J12" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L12" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M12" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N12" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O12" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1545,62 +1551,58 @@
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C13" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D13" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E13" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F13" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H13" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J13" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K13" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L13" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M13" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N13" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O13" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -1617,7 +1619,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1631,7 +1633,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1641,73 +1643,69 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C14" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D14" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E14" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F14" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I14" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J14" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K14" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L14" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M14" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N14" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O14" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1715,60 +1713,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C15" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D15" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E15" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F15" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H15" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I15" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J15" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K15" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L15" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M15" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N15" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O15" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,17 +1778,19 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U15" s="8" t="n">
@@ -1795,64 +1799,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C16" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D16" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E16" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F16" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H16" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I16" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J16" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K16" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L16" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M16" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N16" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O16" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,20 +1864,16 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1881,7 +1881,7 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1895,50 +1895,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C17" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D17" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E17" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F17" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H17" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I17" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J17" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K17" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L17" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M17" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N17" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O17" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1949,7 +1949,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1963,77 +1963,83 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C18" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D18" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E18" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F18" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H18" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I18" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J18" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K18" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L18" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M18" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N18" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O18" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2045,177 +2051,175 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C19" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D19" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E19" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H19" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I19" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J19" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K19" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L19" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M19" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N19" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O19" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C20" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D20" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E20" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F20" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H20" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I20" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J20" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K20" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L20" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M20" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N20" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2229,157 +2233,157 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C21" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D21" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E21" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F21" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H21" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I21" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J21" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K21" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L21" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M21" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N21" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O21" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C22" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D22" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E22" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F22" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H22" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I22" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J22" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K22" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L22" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N22" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O22" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2387,169 +2391,167 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C23" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D23" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E23" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F23" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H23" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I23" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J23" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K23" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L23" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M23" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N23" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O23" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C24" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D24" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E24" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F24" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H24" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I24" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J24" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K24" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L24" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M24" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N24" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O24" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2557,148 +2559,144 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C25" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D25" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E25" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H25" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I25" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J25" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K25" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L25" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M25" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N25" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O25" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
       <c r="U25" s="8" t="n">
         <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C26" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D26" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E26" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F26" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H26" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I26" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J26" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K26" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L26" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M26" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N26" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O26" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2709,23 +2707,27 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2735,50 +2737,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C27" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D27" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E27" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F27" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H27" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I27" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J27" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K27" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L27" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M27" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N27" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O27" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2789,27 +2791,23 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2819,50 +2817,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C28" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D28" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E28" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F28" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H28" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I28" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J28" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K28" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L28" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M28" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N28" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2873,23 +2871,25 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2899,50 +2899,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C29" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D29" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E29" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F29" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H29" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I29" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J29" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K29" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L29" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M29" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N29" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O29" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2953,25 +2953,23 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="V29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2981,69 +2979,71 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C30" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D30" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E30" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F30" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I30" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J30" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K30" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L30" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M30" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N30" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3053,7 +3053,7 @@
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3061,150 +3061,156 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C31" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D31" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E31" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F31" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H31" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I31" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J31" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K31" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L31" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M31" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N31" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O31" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C32" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D32" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E32" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F32" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H32" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I32" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J32" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K32" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L32" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M32" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N32" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O32" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U32" s="8" t="n">
@@ -3213,7 +3219,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3227,73 +3233,69 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C33" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D33" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E33" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F33" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H33" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I33" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J33" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K33" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L33" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M33" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N33" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O33" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q33" s="6" t="n">
+        <v/>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3301,7 +3303,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3315,50 +3317,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C34" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D34" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E34" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F34" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H34" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I34" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J34" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K34" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L34" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M34" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N34" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O34" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3366,83 +3368,83 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W34" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C35" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D35" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E35" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F35" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H35" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I35" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J35" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K35" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L35" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M35" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N35" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O35" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,27 +3455,23 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3483,69 +3481,73 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C36" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D36" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E36" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F36" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H36" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I36" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J36" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K36" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L36" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M36" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N36" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O36" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3555,7 +3557,7 @@
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr"/>
@@ -3563,69 +3565,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C37" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D37" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E37" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F37" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H37" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I37" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J37" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K37" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L37" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M37" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N37" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O37" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3637,60 +3633,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C38" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D38" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E38" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F38" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H38" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I38" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J38" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K38" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L38" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M38" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N38" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O38" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3698,12 +3698,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3715,70 +3717,74 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C39" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D39" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E39" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F39" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I39" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J39" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K39" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L39" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M39" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N39" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O39" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3787,7 +3793,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3799,74 +3805,66 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C40" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D40" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E40" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F40" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H40" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I40" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J40" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K40" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L40" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M40" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N40" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O40" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3875,7 +3873,7 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3887,60 +3885,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C41" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D41" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E41" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F41" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H41" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I41" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J41" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K41" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L41" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M41" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N41" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O41" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,18 +3950,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3967,64 +3969,64 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C42" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D42" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E42" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F42" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H42" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I42" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J42" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K42" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L42" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M42" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N42" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O42" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,23 +4037,25 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4065,50 +4069,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C43" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D43" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E43" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F43" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H43" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I43" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J43" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K43" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L43" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M43" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N43" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O43" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4119,82 +4123,78 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C44" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D44" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E44" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F44" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H44" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I44" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J44" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K44" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L44" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M44" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N44" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O44" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,81 +4202,89 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C45" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D45" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E45" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F45" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I45" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J45" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K45" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L45" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M45" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N45" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O45" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4284,32 +4292,24 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4323,63 +4323,69 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C46" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D46" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E46" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F46" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H46" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I46" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J46" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K46" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L46" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M46" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N46" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O46" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4393,85 +4399,77 @@
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C47" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D47" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E47" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F47" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H47" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I47" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J47" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K47" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L47" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M47" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N47" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O47" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4479,60 +4477,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C48" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D48" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E48" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I48" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J48" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K48" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L48" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M48" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N48" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O48" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4540,12 +4542,14 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
@@ -4553,70 +4557,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C49" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D49" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E49" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F49" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I49" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J49" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K49" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L49" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M49" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N49" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O49" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4624,87 +4630,81 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C50" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D50" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E50" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F50" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I50" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J50" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K50" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L50" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M50" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N50" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O50" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4717,11 +4717,13 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4729,64 +4731,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C51" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D51" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E51" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F51" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H51" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I51" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J51" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K51" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L51" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M51" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N51" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O51" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4797,14 +4799,14 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4813,7 +4815,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4827,69 +4829,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C52" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D52" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E52" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F52" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H52" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I52" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J52" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K52" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L52" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M52" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N52" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O52" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4897,71 +4901,69 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C53" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D53" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E53" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F53" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H53" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I53" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J53" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K53" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L53" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M53" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N53" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O53" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
@@ -4969,7 +4971,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4983,7 +4985,7 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4993,69 +4995,63 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C54" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D54" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E54" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F54" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H54" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I54" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J54" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K54" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L54" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M54" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N54" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O54" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5067,73 +5063,81 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C55" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D55" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E55" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H55" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I55" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J55" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K55" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L55" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M55" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N55" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O55" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5145,146 +5149,148 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C56" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D56" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E56" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F56" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H56" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I56" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J56" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K56" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L56" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M56" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N56" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O56" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C57" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D57" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E57" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F57" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H57" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I57" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J57" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K57" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L57" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M57" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N57" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O57" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5292,30 +5298,24 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5329,50 +5329,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C58" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D58" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E58" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F58" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H58" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I58" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J58" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K58" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L58" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M58" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N58" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O58" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5385,76 +5385,76 @@
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
       <c r="W58" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C59" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D59" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E59" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F59" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H59" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I59" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J59" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K59" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L59" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M59" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N59" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O59" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5465,7 +5465,7 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5477,13 +5477,15 @@
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5493,50 +5495,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C60" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D60" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E60" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F60" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H60" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I60" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K60" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L60" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M60" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N60" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O60" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5547,9 +5549,9 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5557,17 +5559,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5577,50 +5575,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3963.81</v>
+        <v>3951.37</v>
       </c>
       <c r="C61" t="n">
-        <v>3967.68</v>
+        <v>3951.52</v>
       </c>
       <c r="D61" t="n">
-        <v>3945.42</v>
+        <v>3934.46</v>
       </c>
       <c r="E61" t="n">
-        <v>3952.13</v>
+        <v>3936.52</v>
       </c>
       <c r="F61" t="n">
-        <v>2.22</v>
+        <v>-15.61</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="H61" t="n">
-        <v>22.26</v>
+        <v>17.06</v>
       </c>
       <c r="I61" t="n">
-        <v>3885.32</v>
+        <v>3923.15</v>
       </c>
       <c r="J61" t="n">
-        <v>3924.78</v>
+        <v>3927.65</v>
       </c>
       <c r="K61" t="n">
-        <v>3933.5</v>
+        <v>3941</v>
       </c>
       <c r="L61" t="n">
-        <v>3942.22</v>
+        <v>3954.34</v>
       </c>
       <c r="M61" t="n">
-        <v>3966.31</v>
+        <v>3963.26</v>
       </c>
       <c r="N61" t="n">
-        <v>3990.4</v>
+        <v>3972.18</v>
       </c>
       <c r="O61" t="n">
-        <v>3983.75</v>
+        <v>3989.94</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5628,18 +5626,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5647,73 +5645,81 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3951.37</v>
+        <v>3925.32</v>
       </c>
       <c r="C62" t="n">
-        <v>3951.52</v>
+        <v>3930.5</v>
       </c>
       <c r="D62" t="n">
-        <v>3934.46</v>
+        <v>3888.37</v>
       </c>
       <c r="E62" t="n">
-        <v>3936.52</v>
+        <v>3888.37</v>
       </c>
       <c r="F62" t="n">
-        <v>-15.61</v>
+        <v>-48.15</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0122</v>
       </c>
       <c r="H62" t="n">
-        <v>17.06</v>
+        <v>42.12</v>
       </c>
       <c r="I62" t="n">
-        <v>3923.15</v>
+        <v>3917.39</v>
       </c>
       <c r="J62" t="n">
-        <v>3927.65</v>
+        <v>3916.22</v>
       </c>
       <c r="K62" t="n">
-        <v>3941</v>
+        <v>3927.99</v>
       </c>
       <c r="L62" t="n">
-        <v>3954.34</v>
+        <v>3939.76</v>
       </c>
       <c r="M62" t="n">
-        <v>3963.26</v>
+        <v>3945.05</v>
       </c>
       <c r="N62" t="n">
-        <v>3972.18</v>
+        <v>3950.35</v>
       </c>
       <c r="O62" t="n">
-        <v>3989.94</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+        <v>3968.59</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5729,62 +5735,58 @@
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3925.32</v>
+        <v>3878.41</v>
       </c>
       <c r="C63" t="n">
-        <v>3930.5</v>
+        <v>3878.41</v>
       </c>
       <c r="D63" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E63" t="n">
-        <v>3888.37</v>
+        <v>3823.62</v>
       </c>
       <c r="F63" t="n">
-        <v>-48.15</v>
+        <v>-64.75</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0122</v>
+        <v>-0.0167</v>
       </c>
       <c r="H63" t="n">
-        <v>42.12</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I63" t="n">
-        <v>3917.39</v>
+        <v>3846.25</v>
       </c>
       <c r="J63" t="n">
-        <v>3916.22</v>
+        <v>3835.72</v>
       </c>
       <c r="K63" t="n">
-        <v>3927.99</v>
+        <v>3867.31</v>
       </c>
       <c r="L63" t="n">
-        <v>3939.76</v>
+        <v>3898.9</v>
       </c>
       <c r="M63" t="n">
-        <v>3945.05</v>
+        <v>3909.44</v>
       </c>
       <c r="N63" t="n">
-        <v>3950.35</v>
+        <v>3919.97</v>
       </c>
       <c r="O63" t="n">
-        <v>3968.59</v>
+        <v>3972.62</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -5801,7 +5803,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S63" s="10" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5815,7 +5817,7 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5825,17 +5827,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3878.41</v>
+        <v>3816.15</v>
       </c>
       <c r="C64" t="n">
-        <v>3878.41</v>
+        <v>3843.84</v>
       </c>
       <c r="D64" t="n">
-        <v>3806.67</v>
+        <v>3810.81</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5847,43 +5849,39 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>71.73999999999999</v>
+        <v>33.03</v>
       </c>
       <c r="I64" t="n">
-        <v>3846.25</v>
+        <v>3734.93</v>
       </c>
       <c r="J64" t="n">
-        <v>3835.72</v>
+        <v>3742.42</v>
       </c>
       <c r="K64" t="n">
-        <v>3867.31</v>
+        <v>3787.75</v>
       </c>
       <c r="L64" t="n">
-        <v>3898.9</v>
+        <v>3833.08</v>
       </c>
       <c r="M64" t="n">
-        <v>3909.44</v>
+        <v>3859.49</v>
       </c>
       <c r="N64" t="n">
-        <v>3919.97</v>
+        <v>3885.9</v>
       </c>
       <c r="O64" t="n">
-        <v>3972.62</v>
+        <v>3950.15</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R64" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
       </c>
       <c r="S64" s="12" t="inlineStr">
         <is>
@@ -5899,12 +5897,16 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="11" t="inlineStr">
+      <c r="W64" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr"/>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -637,73 +637,69 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4054.09</v>
+        <v>4031.33</v>
       </c>
       <c r="C2" t="n">
-        <v>4093.68</v>
+        <v>4073.88</v>
       </c>
       <c r="D2" t="n">
-        <v>4019.22</v>
+        <v>4027.25</v>
       </c>
       <c r="E2" t="n">
-        <v>4028.9</v>
+        <v>4043.64</v>
       </c>
       <c r="F2" t="n">
-        <v>-83.54000000000001</v>
+        <v>14.74</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0203</v>
+        <v>0.0037</v>
       </c>
       <c r="H2" t="n">
-        <v>74.45999999999999</v>
+        <v>46.62</v>
       </c>
       <c r="I2" t="n">
-        <v>4031.76</v>
+        <v>3944.75</v>
       </c>
       <c r="J2" t="n">
-        <v>4055.18</v>
+        <v>3940.67</v>
       </c>
       <c r="K2" t="n">
-        <v>4084.56</v>
+        <v>3991.67</v>
       </c>
       <c r="L2" t="n">
-        <v>4113.93</v>
+        <v>4042.68</v>
       </c>
       <c r="M2" t="n">
-        <v>4140.33</v>
+        <v>4066.14</v>
       </c>
       <c r="N2" t="n">
-        <v>4166.73</v>
+        <v>4089.6</v>
       </c>
       <c r="O2" t="n">
-        <v>4199.09</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4168.14</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -713,58 +709,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C3" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D3" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E3" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F3" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I3" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J3" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K3" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L3" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M3" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N3" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O3" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,18 +772,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -793,77 +793,79 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C4" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D4" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E4" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H4" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J4" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K4" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L4" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M4" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N4" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O4" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -875,7 +877,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
+      <c r="W4" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -885,65 +887,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C5" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D5" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E5" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F5" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H5" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I5" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J5" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K5" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L5" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M5" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N5" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O5" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -957,7 +957,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -967,50 +967,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C6" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D6" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E6" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F6" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H6" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I6" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J6" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K6" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L6" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M6" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N6" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O6" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,77 +1020,87 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C7" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D7" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E7" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F7" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H7" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I7" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J7" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K7" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L7" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M7" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N7" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O7" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,30 +1110,24 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W7" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1137,63 +1141,65 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C8" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D8" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E8" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F8" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H8" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I8" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J8" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K8" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L8" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M8" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N8" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O8" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1207,150 +1213,150 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C9" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D9" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E9" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F9" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H9" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J9" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K9" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L9" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M9" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N9" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O9" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C10" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D10" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E10" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F10" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H10" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I10" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J10" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K10" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L10" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M10" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N10" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O10" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,20 +1364,16 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1379,77 +1381,83 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C11" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D11" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E11" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F11" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H11" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J11" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K11" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L11" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M11" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N11" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O11" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1463,62 +1471,58 @@
       </c>
       <c r="W11" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C12" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D12" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E12" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F12" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H12" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I12" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J12" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K12" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L12" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N12" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O12" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -1535,7 +1539,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1549,7 +1553,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1559,73 +1563,69 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C13" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D13" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E13" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F13" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I13" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J13" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K13" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L13" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M13" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N13" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O13" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3993.26</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1633,60 +1633,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C14" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D14" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E14" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F14" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H14" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I14" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J14" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K14" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L14" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M14" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N14" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O14" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,17 +1698,19 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U14" s="8" t="n">
@@ -1713,64 +1719,64 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C15" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D15" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E15" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F15" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H15" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I15" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J15" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K15" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L15" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M15" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N15" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,20 +1784,16 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1799,7 +1801,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1813,50 +1815,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C16" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D16" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E16" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F16" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H16" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I16" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J16" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K16" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L16" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M16" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N16" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1867,7 +1869,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1881,77 +1883,83 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C17" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D17" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E17" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F17" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H17" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I17" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J17" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K17" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L17" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M17" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N17" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O17" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1963,177 +1971,175 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C18" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D18" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E18" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H18" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I18" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J18" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K18" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L18" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M18" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N18" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O18" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C19" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D19" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E19" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F19" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H19" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I19" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J19" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K19" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L19" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M19" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N19" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2147,157 +2153,157 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C20" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D20" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E20" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F20" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H20" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I20" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J20" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K20" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L20" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M20" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N20" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O20" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C21" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D21" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F21" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H21" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I21" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J21" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K21" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L21" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N21" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O21" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2305,169 +2311,167 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C22" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D22" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E22" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F22" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H22" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I22" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J22" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K22" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L22" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M22" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N22" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O22" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C23" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D23" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E23" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F23" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H23" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I23" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J23" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K23" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L23" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M23" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N23" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O23" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2475,148 +2479,144 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C24" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D24" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E24" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H24" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I24" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J24" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K24" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L24" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M24" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N24" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O24" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
       <c r="U24" s="8" t="n">
         <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C25" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D25" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E25" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F25" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H25" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I25" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J25" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K25" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L25" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M25" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N25" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O25" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,23 +2627,27 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2653,50 +2657,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C26" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D26" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E26" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F26" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H26" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I26" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J26" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K26" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L26" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M26" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N26" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O26" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2707,27 +2711,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2737,50 +2737,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C27" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D27" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E27" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F27" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H27" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I27" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J27" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K27" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L27" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M27" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N27" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2791,23 +2791,25 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2817,50 +2819,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C28" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D28" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E28" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F28" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H28" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I28" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J28" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K28" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L28" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M28" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N28" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O28" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2871,25 +2873,23 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="V28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2899,69 +2899,71 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C29" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D29" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E29" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F29" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I29" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J29" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K29" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L29" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M29" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N29" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O29" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2971,7 +2973,7 @@
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2979,150 +2981,156 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C30" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D30" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E30" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F30" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H30" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I30" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J30" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K30" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L30" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M30" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N30" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O30" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C31" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D31" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E31" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F31" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H31" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I31" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J31" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K31" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L31" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M31" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N31" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O31" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U31" s="8" t="n">
@@ -3131,7 +3139,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3145,73 +3153,69 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C32" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D32" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E32" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F32" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H32" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I32" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J32" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K32" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L32" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M32" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N32" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O32" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q32" s="6" t="n">
+        <v/>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3219,7 +3223,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3233,50 +3237,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C33" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D33" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E33" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F33" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H33" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I33" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J33" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K33" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L33" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M33" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N33" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O33" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3284,83 +3288,83 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C34" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D34" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E34" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F34" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H34" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I34" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J34" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K34" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L34" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M34" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N34" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O34" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3371,27 +3375,23 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3401,69 +3401,73 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C35" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D35" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E35" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F35" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H35" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I35" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J35" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K35" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L35" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M35" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N35" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O35" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3473,7 +3477,7 @@
       </c>
       <c r="W35" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr"/>
@@ -3481,69 +3485,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C36" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D36" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E36" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F36" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H36" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I36" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J36" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K36" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L36" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M36" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N36" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O36" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3555,60 +3553,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C37" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D37" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E37" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F37" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H37" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I37" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J37" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K37" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L37" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M37" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N37" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O37" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3616,12 +3618,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3633,70 +3637,74 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C38" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D38" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E38" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F38" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I38" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J38" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K38" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L38" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M38" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N38" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O38" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3705,7 +3713,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3717,74 +3725,66 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C39" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D39" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E39" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F39" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H39" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I39" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J39" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K39" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L39" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M39" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N39" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O39" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3805,60 +3805,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C40" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D40" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E40" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F40" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I40" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J40" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K40" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L40" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M40" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N40" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O40" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3866,18 +3870,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3885,64 +3889,64 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C41" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D41" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E41" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F41" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H41" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I41" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J41" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K41" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L41" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M41" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N41" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O41" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3953,23 +3957,25 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3983,50 +3989,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C42" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D42" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E42" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F42" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H42" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I42" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J42" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K42" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L42" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M42" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N42" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O42" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4037,82 +4043,78 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C43" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D43" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E43" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F43" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H43" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I43" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J43" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K43" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L43" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M43" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N43" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O43" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4120,81 +4122,89 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C44" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D44" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E44" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F44" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I44" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J44" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K44" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L44" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M44" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N44" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O44" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4202,32 +4212,24 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4241,63 +4243,69 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C45" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D45" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E45" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F45" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H45" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I45" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J45" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K45" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L45" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M45" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N45" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O45" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4311,85 +4319,77 @@
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C46" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D46" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E46" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F46" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H46" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I46" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J46" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K46" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L46" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M46" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N46" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O46" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4397,60 +4397,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C47" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D47" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E47" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I47" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J47" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K47" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L47" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M47" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N47" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O47" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4458,12 +4462,14 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
@@ -4471,70 +4477,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C48" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D48" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E48" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F48" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I48" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J48" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K48" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L48" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M48" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N48" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O48" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4542,87 +4550,81 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C49" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D49" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E49" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F49" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I49" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J49" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K49" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L49" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M49" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N49" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O49" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,11 +4637,13 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4647,64 +4651,64 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C50" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D50" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E50" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F50" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H50" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I50" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J50" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K50" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L50" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M50" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N50" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O50" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4715,14 +4719,14 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U50" s="8" t="n">
@@ -4731,7 +4735,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4745,69 +4749,71 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C51" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D51" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E51" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F51" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H51" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I51" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J51" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K51" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L51" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M51" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N51" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O51" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4815,71 +4821,69 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C52" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D52" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E52" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F52" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H52" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I52" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J52" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K52" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L52" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M52" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N52" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O52" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
@@ -4887,7 +4891,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4901,7 +4905,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4911,69 +4915,63 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C53" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D53" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E53" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F53" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I53" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J53" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K53" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L53" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M53" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N53" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O53" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3972.62</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4985,73 +4983,81 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C54" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D54" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E54" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H54" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I54" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J54" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K54" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L54" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M54" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N54" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O54" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5063,146 +5069,148 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C55" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D55" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E55" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F55" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H55" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I55" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J55" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K55" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L55" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M55" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N55" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O55" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C56" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D56" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E56" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F56" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H56" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I56" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J56" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K56" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L56" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M56" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N56" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O56" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5210,30 +5218,24 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5247,50 +5249,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C57" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D57" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E57" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F57" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H57" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I57" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J57" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K57" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L57" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M57" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N57" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O57" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5303,76 +5305,76 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C58" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D58" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E58" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F58" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H58" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I58" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J58" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K58" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L58" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M58" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N58" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O58" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5383,7 +5385,7 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
+      <c r="S58" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5395,13 +5397,15 @@
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5411,50 +5415,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C59" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D59" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E59" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F59" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I59" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J59" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K59" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L59" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M59" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N59" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O59" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5465,9 +5469,9 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5475,17 +5479,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5495,50 +5495,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3963.81</v>
+        <v>3951.37</v>
       </c>
       <c r="C60" t="n">
-        <v>3967.68</v>
+        <v>3951.52</v>
       </c>
       <c r="D60" t="n">
-        <v>3945.42</v>
+        <v>3934.46</v>
       </c>
       <c r="E60" t="n">
-        <v>3952.13</v>
+        <v>3936.52</v>
       </c>
       <c r="F60" t="n">
-        <v>2.22</v>
+        <v>-15.61</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="H60" t="n">
-        <v>22.26</v>
+        <v>17.06</v>
       </c>
       <c r="I60" t="n">
-        <v>3885.32</v>
+        <v>3923.15</v>
       </c>
       <c r="J60" t="n">
-        <v>3924.78</v>
+        <v>3927.65</v>
       </c>
       <c r="K60" t="n">
-        <v>3933.5</v>
+        <v>3941</v>
       </c>
       <c r="L60" t="n">
-        <v>3942.22</v>
+        <v>3954.34</v>
       </c>
       <c r="M60" t="n">
-        <v>3966.31</v>
+        <v>3963.26</v>
       </c>
       <c r="N60" t="n">
-        <v>3990.4</v>
+        <v>3972.18</v>
       </c>
       <c r="O60" t="n">
-        <v>3983.75</v>
+        <v>3989.94</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5546,18 +5546,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5565,73 +5565,81 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3951.37</v>
+        <v>3925.32</v>
       </c>
       <c r="C61" t="n">
-        <v>3951.52</v>
+        <v>3930.5</v>
       </c>
       <c r="D61" t="n">
-        <v>3934.46</v>
+        <v>3888.37</v>
       </c>
       <c r="E61" t="n">
-        <v>3936.52</v>
+        <v>3888.37</v>
       </c>
       <c r="F61" t="n">
-        <v>-15.61</v>
+        <v>-48.15</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0122</v>
       </c>
       <c r="H61" t="n">
-        <v>17.06</v>
+        <v>42.12</v>
       </c>
       <c r="I61" t="n">
-        <v>3923.15</v>
+        <v>3917.39</v>
       </c>
       <c r="J61" t="n">
-        <v>3927.65</v>
+        <v>3916.22</v>
       </c>
       <c r="K61" t="n">
-        <v>3941</v>
+        <v>3927.99</v>
       </c>
       <c r="L61" t="n">
-        <v>3954.34</v>
+        <v>3939.76</v>
       </c>
       <c r="M61" t="n">
-        <v>3963.26</v>
+        <v>3945.05</v>
       </c>
       <c r="N61" t="n">
-        <v>3972.18</v>
+        <v>3950.35</v>
       </c>
       <c r="O61" t="n">
-        <v>3989.94</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>3968.59</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5647,62 +5655,58 @@
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3925.32</v>
+        <v>3878.41</v>
       </c>
       <c r="C62" t="n">
-        <v>3930.5</v>
+        <v>3878.41</v>
       </c>
       <c r="D62" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E62" t="n">
-        <v>3888.37</v>
+        <v>3823.62</v>
       </c>
       <c r="F62" t="n">
-        <v>-48.15</v>
+        <v>-64.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0122</v>
+        <v>-0.0167</v>
       </c>
       <c r="H62" t="n">
-        <v>42.12</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I62" t="n">
-        <v>3917.39</v>
+        <v>3846.25</v>
       </c>
       <c r="J62" t="n">
-        <v>3916.22</v>
+        <v>3835.72</v>
       </c>
       <c r="K62" t="n">
-        <v>3927.99</v>
+        <v>3867.31</v>
       </c>
       <c r="L62" t="n">
-        <v>3939.76</v>
+        <v>3898.9</v>
       </c>
       <c r="M62" t="n">
-        <v>3945.05</v>
+        <v>3909.44</v>
       </c>
       <c r="N62" t="n">
-        <v>3950.35</v>
+        <v>3919.97</v>
       </c>
       <c r="O62" t="n">
-        <v>3968.59</v>
+        <v>3972.62</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -5719,7 +5723,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5733,7 +5737,7 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5743,69 +5747,63 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3878.41</v>
+        <v>3816.15</v>
       </c>
       <c r="C63" t="n">
-        <v>3878.41</v>
+        <v>3843.84</v>
       </c>
       <c r="D63" t="n">
-        <v>3806.67</v>
+        <v>3810.81</v>
       </c>
       <c r="E63" t="n">
-        <v>3823.62</v>
+        <v>3830.45</v>
       </c>
       <c r="F63" t="n">
-        <v>-64.75</v>
+        <v>6.83</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0018</v>
       </c>
       <c r="H63" t="n">
-        <v>71.73999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="I63" t="n">
-        <v>3846.25</v>
+        <v>3734.93</v>
       </c>
       <c r="J63" t="n">
-        <v>3835.72</v>
+        <v>3742.42</v>
       </c>
       <c r="K63" t="n">
-        <v>3867.31</v>
+        <v>3787.75</v>
       </c>
       <c r="L63" t="n">
-        <v>3898.9</v>
+        <v>3833.08</v>
       </c>
       <c r="M63" t="n">
-        <v>3909.44</v>
+        <v>3859.49</v>
       </c>
       <c r="N63" t="n">
-        <v>3919.97</v>
+        <v>3885.9</v>
       </c>
       <c r="O63" t="n">
-        <v>3972.62</v>
-      </c>
-      <c r="P63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3950.15</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T63" s="8" t="n">
@@ -5817,27 +5815,31 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="W63" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3816.15</v>
+        <v>3839.25</v>
       </c>
       <c r="C64" t="n">
-        <v>3843.84</v>
+        <v>3851.22</v>
       </c>
       <c r="D64" t="n">
-        <v>3810.81</v>
+        <v>3833.09</v>
       </c>
       <c r="E64" t="n">
         <v/>
@@ -5849,28 +5851,28 @@
         <v/>
       </c>
       <c r="H64" t="n">
-        <v>33.03</v>
+        <v>18.13</v>
       </c>
       <c r="I64" t="n">
-        <v>3734.93</v>
+        <v>3777.79</v>
       </c>
       <c r="J64" t="n">
-        <v>3742.42</v>
+        <v>3798.99</v>
       </c>
       <c r="K64" t="n">
-        <v>3787.75</v>
+        <v>3813.94</v>
       </c>
       <c r="L64" t="n">
-        <v>3833.08</v>
+        <v>3828.89</v>
       </c>
       <c r="M64" t="n">
-        <v>3859.49</v>
+        <v>3846.96</v>
       </c>
       <c r="N64" t="n">
-        <v>3885.9</v>
+        <v>3865.04</v>
       </c>
       <c r="O64" t="n">
-        <v>3950.15</v>
+        <v>3876.86</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -5888,8 +5890,10 @@
           <t>=</t>
         </is>
       </c>
-      <c r="T64" s="8" t="n">
-        <v/>
+      <c r="T64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U64" s="8" t="n">
         <v/>
@@ -5897,14 +5901,14 @@
       <c r="V64" s="8" t="n">
         <v/>
       </c>
-      <c r="W64" s="9" t="inlineStr">
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -104,18 +104,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -483,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -637,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4031.33</v>
+        <v>4059.19</v>
       </c>
       <c r="C2" t="n">
-        <v>4073.88</v>
+        <v>4060.07</v>
       </c>
       <c r="D2" t="n">
-        <v>4027.25</v>
+        <v>4005.41</v>
       </c>
       <c r="E2" t="n">
-        <v>4043.64</v>
+        <v>4041.24</v>
       </c>
       <c r="F2" t="n">
-        <v>14.74</v>
+        <v>-2.41</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0037</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="H2" t="n">
-        <v>46.62</v>
+        <v>54.66</v>
       </c>
       <c r="I2" t="n">
-        <v>3944.75</v>
+        <v>3980.63</v>
       </c>
       <c r="J2" t="n">
-        <v>3940.67</v>
+        <v>3993.56</v>
       </c>
       <c r="K2" t="n">
-        <v>3991.67</v>
+        <v>4020.33</v>
       </c>
       <c r="L2" t="n">
-        <v>4042.68</v>
+        <v>4047.11</v>
       </c>
       <c r="M2" t="n">
-        <v>4066.14</v>
+        <v>4066.96</v>
       </c>
       <c r="N2" t="n">
-        <v>4089.6</v>
+        <v>4086.81</v>
       </c>
       <c r="O2" t="n">
-        <v>4168.14</v>
+        <v>4120.5</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -688,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -714,72 +711,74 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C3" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D3" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E3" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H3" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I3" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J3" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K3" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L3" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M3" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N3" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O3" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -791,79 +790,73 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C4" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D4" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E4" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F4" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H4" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I4" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J4" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K4" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L4" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M4" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N4" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O4" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -877,7 +870,7 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -887,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C5" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D5" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E5" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F5" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H5" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I5" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J5" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K5" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L5" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M5" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N5" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O5" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,77 +933,87 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W5" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="W5" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C6" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D6" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E6" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F6" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H6" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I6" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J6" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K6" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L6" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M6" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N6" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O6" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,28 +1023,22 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1057,63 +1054,65 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C7" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D7" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E7" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F7" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H7" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I7" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J7" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K7" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L7" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M7" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N7" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O7" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1134,79 +1133,79 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C8" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D8" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E8" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F8" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H8" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J8" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K8" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L8" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M8" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N8" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O8" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1220,57 +1219,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C9" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D9" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E9" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F9" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H9" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I9" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J9" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K9" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L9" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M9" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N9" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O9" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,20 +1277,16 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1306,70 +1301,76 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C10" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D10" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E10" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F10" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H10" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I10" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J10" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K10" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L10" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M10" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N10" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O10" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+        <v>4019.65</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1381,64 +1382,60 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W10" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C11" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D11" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E11" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F11" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H11" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I11" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J11" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K11" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L11" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M11" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N11" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O11" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -1455,7 +1452,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1469,7 +1466,7 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1479,73 +1476,69 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C12" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D12" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E12" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F12" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I12" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J12" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K12" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L12" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M12" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N12" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O12" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+        <v>3993.26</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1553,60 +1546,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C13" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D13" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E13" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F13" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H13" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I13" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J13" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K13" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L13" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M13" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N13" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O13" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,17 +1611,19 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U13" s="8" t="n">
@@ -1633,64 +1632,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C14" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D14" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E14" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F14" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H14" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I14" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J14" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K14" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L14" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M14" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N14" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O14" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1698,20 +1697,16 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1719,7 +1714,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1733,50 +1728,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C15" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D15" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E15" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F15" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H15" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I15" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J15" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K15" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L15" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M15" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N15" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O15" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1787,7 +1782,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1801,77 +1796,83 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C16" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D16" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E16" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F16" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H16" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I16" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J16" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K16" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L16" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M16" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N16" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O16" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+        <v>3905.96</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S16" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1883,172 +1884,170 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C17" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D17" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E17" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H17" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I17" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J17" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K17" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L17" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N17" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O17" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C18" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D18" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E18" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F18" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H18" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I18" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J18" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K18" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L18" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M18" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N18" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2067,72 +2066,72 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C19" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D19" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E19" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F19" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H19" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I19" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J19" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K19" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L19" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M19" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N19" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O19" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
@@ -2146,78 +2145,78 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C20" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D20" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E20" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F20" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H20" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I20" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J20" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K20" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L20" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N20" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O20" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2232,79 +2231,77 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C21" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D21" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E21" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F21" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H21" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I21" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K21" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L21" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M21" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N21" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O21" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
@@ -2316,78 +2313,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C22" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D22" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E22" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F22" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H22" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I22" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J22" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K22" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L22" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M22" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N22" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O22" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+        <v>3871.81</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2400,79 +2397,79 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C23" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D23" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E23" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H23" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I23" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J23" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K23" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L23" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N23" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O23" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
       <c r="U23" s="8" t="n">
         <v/>
       </c>
@@ -2484,59 +2481,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C24" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D24" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E24" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F24" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H24" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I24" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J24" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K24" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L24" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M24" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N24" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2547,21 +2540,25 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2573,50 +2570,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C25" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D25" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E25" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F25" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H25" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I25" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J25" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K25" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L25" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N25" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O25" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2627,25 +2624,21 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2657,50 +2650,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C26" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D26" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E26" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F26" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H26" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I26" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J26" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K26" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L26" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M26" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N26" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2711,21 +2704,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2737,50 +2732,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C27" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D27" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E27" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F27" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H27" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I27" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J27" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K27" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L27" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M27" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N27" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O27" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2791,23 +2786,21 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2819,69 +2812,71 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C28" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D28" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E28" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F28" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I28" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J28" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K28" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L28" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M28" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N28" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2889,9 +2884,9 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2899,150 +2894,156 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C29" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D29" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E29" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F29" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H29" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I29" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J29" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K29" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L29" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M29" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N29" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O29" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C30" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D30" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E30" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F30" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H30" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I30" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J30" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K30" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L30" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M30" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N30" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O30" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U30" s="8" t="n">
@@ -3051,7 +3052,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3065,73 +3066,69 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C31" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D31" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E31" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F31" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H31" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I31" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J31" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K31" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L31" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M31" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N31" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O31" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q31" s="6" t="n">
+        <v/>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3139,7 +3136,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3153,50 +3150,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C32" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D32" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E32" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F32" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H32" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I32" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J32" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K32" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L32" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M32" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N32" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O32" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3204,83 +3201,83 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C33" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D33" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E33" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F33" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H33" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I33" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J33" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K33" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L33" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M33" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N33" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O33" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,25 +3288,21 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3321,69 +3314,73 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C34" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D34" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E34" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F34" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H34" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I34" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J34" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K34" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L34" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M34" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N34" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O34" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>4032.76</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3391,9 +3388,9 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W34" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr"/>
@@ -3401,69 +3398,63 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C35" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D35" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E35" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F35" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H35" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I35" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J35" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K35" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L35" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M35" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N35" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O35" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>4042.69</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3475,60 +3466,64 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C36" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D36" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E36" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F36" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H36" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I36" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J36" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K36" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L36" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M36" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N36" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O36" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3536,12 +3531,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3553,70 +3550,74 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C37" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D37" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E37" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F37" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H37" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I37" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J37" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K37" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L37" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M37" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N37" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O37" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3625,7 +3626,7 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3637,83 +3638,75 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C38" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D38" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E38" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F38" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H38" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I38" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J38" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K38" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L38" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M38" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N38" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O38" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S38" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3725,60 +3718,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C39" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D39" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E39" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F39" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I39" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J39" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K39" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L39" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M39" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N39" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O39" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,18 +3783,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3805,64 +3802,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C40" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D40" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E40" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F40" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H40" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I40" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J40" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K40" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L40" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M40" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N40" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O40" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3873,23 +3870,25 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3903,50 +3902,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C41" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D41" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E41" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F41" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I41" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J41" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K41" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L41" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M41" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N41" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O41" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3957,82 +3956,78 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C42" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D42" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E42" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F42" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H42" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I42" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J42" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K42" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L42" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M42" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N42" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O42" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4040,81 +4035,89 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C43" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D43" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E43" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F43" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H43" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I43" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J43" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K43" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L43" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M43" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N43" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O43" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4122,30 +4125,22 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4161,63 +4156,69 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C44" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D44" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E44" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F44" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H44" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I44" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J44" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K44" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L44" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M44" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N44" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O44" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>4013.88</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4229,87 +4230,79 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C45" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D45" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E45" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F45" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H45" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I45" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J45" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K45" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L45" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M45" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N45" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O45" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+        <v>3999.37</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4317,60 +4310,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C46" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D46" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E46" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I46" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J46" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K46" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L46" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M46" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N46" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O46" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4378,12 +4375,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
@@ -4391,70 +4390,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C47" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D47" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E47" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F47" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I47" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J47" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K47" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L47" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M47" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N47" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O47" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4462,87 +4463,81 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C48" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D48" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E48" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F48" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I48" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J48" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K48" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L48" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M48" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N48" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O48" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4553,13 +4548,15 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4567,64 +4564,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C49" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D49" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E49" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F49" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H49" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I49" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J49" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K49" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L49" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M49" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N49" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O49" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4635,14 +4632,14 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U49" s="8" t="n">
@@ -4651,7 +4648,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4665,69 +4662,71 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C50" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D50" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E50" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F50" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H50" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I50" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J50" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K50" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L50" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M50" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N50" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O50" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4735,71 +4734,69 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C51" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D51" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E51" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F51" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H51" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I51" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J51" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K51" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L51" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M51" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N51" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O51" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
@@ -4807,7 +4804,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4821,7 +4818,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4831,69 +4828,63 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C52" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D52" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E52" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F52" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I52" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J52" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K52" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L52" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M52" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N52" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O52" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3972.62</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4905,73 +4896,81 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C53" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D53" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E53" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H53" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I53" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J53" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K53" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L53" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M53" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N53" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O53" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4983,146 +4982,148 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C54" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D54" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E54" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F54" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H54" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I54" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J54" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K54" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L54" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M54" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N54" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O54" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C55" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D55" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E55" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F55" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H55" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I55" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J55" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K55" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L55" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M55" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N55" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O55" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5130,30 +5131,24 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5167,50 +5162,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C56" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D56" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E56" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F56" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H56" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I56" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J56" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K56" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L56" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M56" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N56" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O56" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5221,78 +5216,78 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="S56" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C57" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D57" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E57" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F57" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H57" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I57" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J57" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K57" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L57" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M57" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N57" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O57" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5303,7 +5298,7 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5315,11 +5310,13 @@
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5331,50 +5328,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C58" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D58" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E58" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F58" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H58" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I58" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J58" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K58" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L58" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M58" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N58" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O58" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5385,9 +5382,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5395,15 +5392,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5415,50 +5408,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3963.81</v>
+        <v>3951.37</v>
       </c>
       <c r="C59" t="n">
-        <v>3967.68</v>
+        <v>3951.52</v>
       </c>
       <c r="D59" t="n">
-        <v>3945.42</v>
+        <v>3934.46</v>
       </c>
       <c r="E59" t="n">
-        <v>3952.13</v>
+        <v>3936.52</v>
       </c>
       <c r="F59" t="n">
-        <v>2.22</v>
+        <v>-15.61</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0005999999999999999</v>
+        <v>-0.0039</v>
       </c>
       <c r="H59" t="n">
-        <v>22.26</v>
+        <v>17.06</v>
       </c>
       <c r="I59" t="n">
-        <v>3885.32</v>
+        <v>3923.15</v>
       </c>
       <c r="J59" t="n">
-        <v>3924.78</v>
+        <v>3927.65</v>
       </c>
       <c r="K59" t="n">
-        <v>3933.5</v>
+        <v>3941</v>
       </c>
       <c r="L59" t="n">
-        <v>3942.22</v>
+        <v>3954.34</v>
       </c>
       <c r="M59" t="n">
-        <v>3966.31</v>
+        <v>3963.26</v>
       </c>
       <c r="N59" t="n">
-        <v>3990.4</v>
+        <v>3972.18</v>
       </c>
       <c r="O59" t="n">
-        <v>3983.75</v>
+        <v>3989.94</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5466,18 +5459,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5490,68 +5483,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3951.37</v>
+        <v>3925.32</v>
       </c>
       <c r="C60" t="n">
-        <v>3951.52</v>
+        <v>3930.5</v>
       </c>
       <c r="D60" t="n">
-        <v>3934.46</v>
+        <v>3888.37</v>
       </c>
       <c r="E60" t="n">
-        <v>3936.52</v>
+        <v>3888.37</v>
       </c>
       <c r="F60" t="n">
-        <v>-15.61</v>
+        <v>-48.15</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0039</v>
+        <v>-0.0122</v>
       </c>
       <c r="H60" t="n">
-        <v>17.06</v>
+        <v>42.12</v>
       </c>
       <c r="I60" t="n">
-        <v>3923.15</v>
+        <v>3917.39</v>
       </c>
       <c r="J60" t="n">
-        <v>3927.65</v>
+        <v>3916.22</v>
       </c>
       <c r="K60" t="n">
-        <v>3941</v>
+        <v>3927.99</v>
       </c>
       <c r="L60" t="n">
-        <v>3954.34</v>
+        <v>3939.76</v>
       </c>
       <c r="M60" t="n">
-        <v>3963.26</v>
+        <v>3945.05</v>
       </c>
       <c r="N60" t="n">
-        <v>3972.18</v>
+        <v>3950.35</v>
       </c>
       <c r="O60" t="n">
-        <v>3989.94</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>3968.59</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5565,64 +5566,60 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3925.32</v>
+        <v>3878.41</v>
       </c>
       <c r="C61" t="n">
-        <v>3930.5</v>
+        <v>3878.41</v>
       </c>
       <c r="D61" t="n">
-        <v>3888.37</v>
+        <v>3806.67</v>
       </c>
       <c r="E61" t="n">
-        <v>3888.37</v>
+        <v>3823.62</v>
       </c>
       <c r="F61" t="n">
-        <v>-48.15</v>
+        <v>-64.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0122</v>
+        <v>-0.0167</v>
       </c>
       <c r="H61" t="n">
-        <v>42.12</v>
+        <v>71.73999999999999</v>
       </c>
       <c r="I61" t="n">
-        <v>3917.39</v>
+        <v>3846.25</v>
       </c>
       <c r="J61" t="n">
-        <v>3916.22</v>
+        <v>3835.72</v>
       </c>
       <c r="K61" t="n">
-        <v>3927.99</v>
+        <v>3867.31</v>
       </c>
       <c r="L61" t="n">
-        <v>3939.76</v>
+        <v>3898.9</v>
       </c>
       <c r="M61" t="n">
-        <v>3945.05</v>
+        <v>3909.44</v>
       </c>
       <c r="N61" t="n">
-        <v>3950.35</v>
+        <v>3919.97</v>
       </c>
       <c r="O61" t="n">
-        <v>3968.59</v>
+        <v>3972.62</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -5639,7 +5636,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5653,7 +5650,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5663,69 +5660,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3878.41</v>
+        <v>3816.15</v>
       </c>
       <c r="C62" t="n">
-        <v>3878.41</v>
+        <v>3843.84</v>
       </c>
       <c r="D62" t="n">
-        <v>3806.67</v>
+        <v>3810.81</v>
       </c>
       <c r="E62" t="n">
-        <v>3823.62</v>
+        <v>3830.45</v>
       </c>
       <c r="F62" t="n">
-        <v>-64.75</v>
+        <v>6.83</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0167</v>
+        <v>0.0018</v>
       </c>
       <c r="H62" t="n">
-        <v>71.73999999999999</v>
+        <v>33.02</v>
       </c>
       <c r="I62" t="n">
-        <v>3846.25</v>
+        <v>3734.93</v>
       </c>
       <c r="J62" t="n">
-        <v>3835.72</v>
+        <v>3742.42</v>
       </c>
       <c r="K62" t="n">
-        <v>3867.31</v>
+        <v>3787.75</v>
       </c>
       <c r="L62" t="n">
-        <v>3898.9</v>
+        <v>3833.08</v>
       </c>
       <c r="M62" t="n">
-        <v>3909.44</v>
+        <v>3859.49</v>
       </c>
       <c r="N62" t="n">
-        <v>3919.97</v>
+        <v>3885.9</v>
       </c>
       <c r="O62" t="n">
-        <v>3972.62</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3950.15</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5737,60 +5728,64 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3816.15</v>
+        <v>3839.25</v>
       </c>
       <c r="C63" t="n">
-        <v>3843.84</v>
+        <v>3851.22</v>
       </c>
       <c r="D63" t="n">
-        <v>3810.81</v>
+        <v>3833.09</v>
       </c>
       <c r="E63" t="n">
-        <v>3830.45</v>
+        <v>3842.2</v>
       </c>
       <c r="F63" t="n">
-        <v>6.83</v>
+        <v>11.74</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0018</v>
+        <v>0.0031</v>
       </c>
       <c r="H63" t="n">
-        <v>33.02</v>
+        <v>18.13</v>
       </c>
       <c r="I63" t="n">
-        <v>3734.93</v>
+        <v>3777.79</v>
       </c>
       <c r="J63" t="n">
-        <v>3742.42</v>
+        <v>3798.99</v>
       </c>
       <c r="K63" t="n">
-        <v>3787.75</v>
+        <v>3813.94</v>
       </c>
       <c r="L63" t="n">
-        <v>3833.08</v>
+        <v>3828.89</v>
       </c>
       <c r="M63" t="n">
-        <v>3859.49</v>
+        <v>3846.96</v>
       </c>
       <c r="N63" t="n">
-        <v>3885.9</v>
+        <v>3865.04</v>
       </c>
       <c r="O63" t="n">
-        <v>3950.15</v>
+        <v>3876.86</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5801,13 +5796,15 @@
       <c r="R63" s="6" t="n">
         <v/>
       </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
+      <c r="S63" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U63" s="8" t="n">
         <v/>
@@ -5815,100 +5812,14 @@
       <c r="V63" s="8" t="n">
         <v/>
       </c>
-      <c r="W63" s="11" t="inlineStr">
+      <c r="W63" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>3839.25</v>
-      </c>
-      <c r="C64" t="n">
-        <v>3851.22</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3833.09</v>
-      </c>
-      <c r="E64" t="n">
-        <v/>
-      </c>
-      <c r="F64" t="n">
-        <v/>
-      </c>
-      <c r="G64" s="5" t="n">
-        <v/>
-      </c>
-      <c r="H64" t="n">
-        <v>18.13</v>
-      </c>
-      <c r="I64" t="n">
-        <v>3777.79</v>
-      </c>
-      <c r="J64" t="n">
-        <v>3798.99</v>
-      </c>
-      <c r="K64" t="n">
-        <v>3813.94</v>
-      </c>
-      <c r="L64" t="n">
-        <v>3828.89</v>
-      </c>
-      <c r="M64" t="n">
-        <v>3846.96</v>
-      </c>
-      <c r="N64" t="n">
-        <v>3865.04</v>
-      </c>
-      <c r="O64" t="n">
-        <v>3876.86</v>
-      </c>
-      <c r="P64" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R64" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S64" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
-        </is>
-      </c>
-      <c r="T64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V64" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W64" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X64" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SSE_daily.xlsx
+++ b/three_gate/analysis/SSE_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,56 +634,58 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4059.19</v>
+        <v>4019.49</v>
       </c>
       <c r="C2" t="n">
-        <v>4060.07</v>
+        <v>4028.51</v>
       </c>
       <c r="D2" t="n">
-        <v>4005.41</v>
+        <v>3971.71</v>
       </c>
       <c r="E2" t="n">
-        <v>4041.24</v>
+        <v>3990.24</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.41</v>
+        <v>-51</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0126</v>
       </c>
       <c r="H2" t="n">
-        <v>54.66</v>
+        <v>56.8</v>
       </c>
       <c r="I2" t="n">
-        <v>3980.63</v>
+        <v>3950.76</v>
       </c>
       <c r="J2" t="n">
-        <v>3993.56</v>
+        <v>3990.83</v>
       </c>
       <c r="K2" t="n">
-        <v>4020.33</v>
+        <v>4013.91</v>
       </c>
       <c r="L2" t="n">
-        <v>4047.11</v>
+        <v>4036.99</v>
       </c>
       <c r="M2" t="n">
-        <v>4066.96</v>
+        <v>4068.57</v>
       </c>
       <c r="N2" t="n">
-        <v>4086.81</v>
+        <v>4100.14</v>
       </c>
       <c r="O2" t="n">
-        <v>4120.5</v>
+        <v>4114.72</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,7 +694,7 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -706,76 +708,70 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4019.49</v>
+        <v>3996.81</v>
       </c>
       <c r="C3" t="n">
-        <v>4028.51</v>
+        <v>4016.03</v>
       </c>
       <c r="D3" t="n">
-        <v>3971.71</v>
+        <v>3967.91</v>
       </c>
       <c r="E3" t="n">
-        <v>3990.24</v>
+        <v>3970.88</v>
       </c>
       <c r="F3" t="n">
-        <v>-51</v>
+        <v>-19.36</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0126</v>
+        <v>-0.0049</v>
       </c>
       <c r="H3" t="n">
-        <v>56.8</v>
+        <v>48.11</v>
       </c>
       <c r="I3" t="n">
-        <v>3950.76</v>
+        <v>3914.91</v>
       </c>
       <c r="J3" t="n">
-        <v>3990.83</v>
+        <v>3928.49</v>
       </c>
       <c r="K3" t="n">
-        <v>4013.91</v>
+        <v>3961.83</v>
       </c>
       <c r="L3" t="n">
-        <v>4036.99</v>
+        <v>3995.17</v>
       </c>
       <c r="M3" t="n">
-        <v>4068.57</v>
+        <v>4018.64</v>
       </c>
       <c r="N3" t="n">
-        <v>4100.14</v>
+        <v>4042.1</v>
       </c>
       <c r="O3" t="n">
-        <v>4114.72</v>
+        <v>4085.31</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -790,7 +786,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3996.81</v>
+        <v>3977.55</v>
       </c>
       <c r="C4" t="n">
-        <v>4016.03</v>
+        <v>4040.54</v>
       </c>
       <c r="D4" t="n">
-        <v>3967.91</v>
+        <v>3938.88</v>
       </c>
       <c r="E4" t="n">
-        <v>3970.88</v>
+        <v>4036.59</v>
       </c>
       <c r="F4" t="n">
-        <v>-19.36</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0049</v>
+        <v>0.0165</v>
       </c>
       <c r="H4" t="n">
-        <v>48.11</v>
+        <v>101.66</v>
       </c>
       <c r="I4" t="n">
-        <v>3914.91</v>
+        <v>3919.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3928.49</v>
+        <v>3912.22</v>
       </c>
       <c r="K4" t="n">
-        <v>3961.83</v>
+        <v>3946.82</v>
       </c>
       <c r="L4" t="n">
-        <v>3995.17</v>
+        <v>3981.42</v>
       </c>
       <c r="M4" t="n">
-        <v>4018.64</v>
+        <v>3994.94</v>
       </c>
       <c r="N4" t="n">
-        <v>4042.1</v>
+        <v>4008.45</v>
       </c>
       <c r="O4" t="n">
-        <v>4085.31</v>
+        <v>4064.14</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,77 +849,87 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3977.55</v>
+        <v>4031.54</v>
       </c>
       <c r="C5" t="n">
-        <v>4040.54</v>
+        <v>4074.83</v>
       </c>
       <c r="D5" t="n">
-        <v>3938.88</v>
+        <v>3995.81</v>
       </c>
       <c r="E5" t="n">
-        <v>4036.59</v>
+        <v>3996.16</v>
       </c>
       <c r="F5" t="n">
-        <v>65.70999999999999</v>
+        <v>-40.43</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0165</v>
+        <v>-0.01</v>
       </c>
       <c r="H5" t="n">
-        <v>101.66</v>
+        <v>79.02</v>
       </c>
       <c r="I5" t="n">
-        <v>3919.8</v>
+        <v>3837.21</v>
       </c>
       <c r="J5" t="n">
-        <v>3912.22</v>
+        <v>3958.37</v>
       </c>
       <c r="K5" t="n">
-        <v>3946.82</v>
+        <v>3985.76</v>
       </c>
       <c r="L5" t="n">
-        <v>3981.42</v>
+        <v>4013.15</v>
       </c>
       <c r="M5" t="n">
-        <v>3994.94</v>
+        <v>4087.42</v>
       </c>
       <c r="N5" t="n">
-        <v>4008.45</v>
+        <v>4161.69</v>
       </c>
       <c r="O5" t="n">
-        <v>4064.14</v>
+        <v>4142.2</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,30 +939,24 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -970,60 +970,62 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4031.54</v>
+        <v>3966.02</v>
       </c>
       <c r="C6" t="n">
-        <v>4074.83</v>
+        <v>3983.05</v>
       </c>
       <c r="D6" t="n">
-        <v>3995.81</v>
+        <v>3900.67</v>
       </c>
       <c r="E6" t="n">
-        <v>3996.16</v>
+        <v>3913.79</v>
       </c>
       <c r="F6" t="n">
-        <v>-40.43</v>
+        <v>-82.37</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.0206</v>
       </c>
       <c r="H6" t="n">
-        <v>79.02</v>
+        <v>82.39</v>
       </c>
       <c r="I6" t="n">
-        <v>3837.21</v>
+        <v>3916.79</v>
       </c>
       <c r="J6" t="n">
-        <v>3958.37</v>
+        <v>3897.56</v>
       </c>
       <c r="K6" t="n">
-        <v>3985.76</v>
+        <v>3956.65</v>
       </c>
       <c r="L6" t="n">
-        <v>4013.15</v>
+        <v>4015.74</v>
       </c>
       <c r="M6" t="n">
-        <v>4087.42</v>
+        <v>4035.67</v>
       </c>
       <c r="N6" t="n">
-        <v>4161.69</v>
+        <v>4055.61</v>
       </c>
       <c r="O6" t="n">
-        <v>4142.2</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
+        <v>4153.85</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
@@ -1040,150 +1042,150 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3966.02</v>
+        <v>3909.27</v>
       </c>
       <c r="C7" t="n">
-        <v>3983.05</v>
+        <v>3967.13</v>
       </c>
       <c r="D7" t="n">
-        <v>3900.67</v>
+        <v>3869.3</v>
       </c>
       <c r="E7" t="n">
-        <v>3913.79</v>
+        <v>3967.13</v>
       </c>
       <c r="F7" t="n">
-        <v>-82.37</v>
+        <v>53.33</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0206</v>
+        <v>0.0136</v>
       </c>
       <c r="H7" t="n">
-        <v>82.39</v>
+        <v>97.81999999999999</v>
       </c>
       <c r="I7" t="n">
-        <v>3916.79</v>
+        <v>3818.28</v>
       </c>
       <c r="J7" t="n">
-        <v>3897.56</v>
+        <v>3817.37</v>
       </c>
       <c r="K7" t="n">
-        <v>3956.65</v>
+        <v>3872.6</v>
       </c>
       <c r="L7" t="n">
-        <v>4015.74</v>
+        <v>3927.83</v>
       </c>
       <c r="M7" t="n">
-        <v>4035.67</v>
+        <v>3954.99</v>
       </c>
       <c r="N7" t="n">
-        <v>4055.61</v>
+        <v>3982.15</v>
       </c>
       <c r="O7" t="n">
-        <v>4153.85</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>4065.44</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3909.27</v>
+        <v>3963.73</v>
       </c>
       <c r="C8" t="n">
-        <v>3967.13</v>
+        <v>3981.67</v>
       </c>
       <c r="D8" t="n">
-        <v>3869.3</v>
+        <v>3943.7</v>
       </c>
       <c r="E8" t="n">
-        <v>3967.13</v>
+        <v>3955.58</v>
       </c>
       <c r="F8" t="n">
-        <v>53.33</v>
+        <v>-11.55</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0136</v>
+        <v>-0.0029</v>
       </c>
       <c r="H8" t="n">
-        <v>97.81999999999999</v>
+        <v>37.98</v>
       </c>
       <c r="I8" t="n">
-        <v>3818.28</v>
+        <v>3771.48</v>
       </c>
       <c r="J8" t="n">
-        <v>3817.37</v>
+        <v>3893.76</v>
       </c>
       <c r="K8" t="n">
-        <v>3872.6</v>
+        <v>3918.21</v>
       </c>
       <c r="L8" t="n">
-        <v>3927.83</v>
+        <v>3942.67</v>
       </c>
       <c r="M8" t="n">
-        <v>3954.99</v>
+        <v>4016.04</v>
       </c>
       <c r="N8" t="n">
-        <v>3982.15</v>
+        <v>4089.4</v>
       </c>
       <c r="O8" t="n">
-        <v>4065.44</v>
+        <v>4064.95</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,20 +1193,16 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1212,77 +1210,83 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3963.73</v>
+        <v>3912.38</v>
       </c>
       <c r="C9" t="n">
-        <v>3981.67</v>
+        <v>3940.45</v>
       </c>
       <c r="D9" t="n">
-        <v>3943.7</v>
+        <v>3867.6</v>
       </c>
       <c r="E9" t="n">
-        <v>3955.58</v>
+        <v>3882.41</v>
       </c>
       <c r="F9" t="n">
-        <v>-11.55</v>
+        <v>-73.16</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0029</v>
+        <v>-0.0185</v>
       </c>
       <c r="H9" t="n">
-        <v>37.98</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>3771.48</v>
+        <v>3905.72</v>
       </c>
       <c r="J9" t="n">
-        <v>3893.76</v>
+        <v>3914.05</v>
       </c>
       <c r="K9" t="n">
-        <v>3918.21</v>
+        <v>3936.59</v>
       </c>
       <c r="L9" t="n">
-        <v>3942.67</v>
+        <v>3959.13</v>
       </c>
       <c r="M9" t="n">
-        <v>4016.04</v>
+        <v>3974.57</v>
       </c>
       <c r="N9" t="n">
-        <v>4089.4</v>
+        <v>3990</v>
       </c>
       <c r="O9" t="n">
-        <v>4064.95</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4019.65</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1296,62 +1300,58 @@
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3912.38</v>
+        <v>3865.32</v>
       </c>
       <c r="C10" t="n">
-        <v>3940.45</v>
+        <v>3869.22</v>
       </c>
       <c r="D10" t="n">
-        <v>3867.6</v>
+        <v>3745.17</v>
       </c>
       <c r="E10" t="n">
-        <v>3882.41</v>
+        <v>3764.16</v>
       </c>
       <c r="F10" t="n">
-        <v>-73.16</v>
+        <v>-118.26</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0305</v>
       </c>
       <c r="H10" t="n">
-        <v>72.84999999999999</v>
+        <v>124.04</v>
       </c>
       <c r="I10" t="n">
-        <v>3905.72</v>
+        <v>3794.75</v>
       </c>
       <c r="J10" t="n">
-        <v>3914.05</v>
+        <v>3798.76</v>
       </c>
       <c r="K10" t="n">
-        <v>3936.59</v>
+        <v>3845.99</v>
       </c>
       <c r="L10" t="n">
-        <v>3959.13</v>
+        <v>3893.22</v>
       </c>
       <c r="M10" t="n">
-        <v>3974.57</v>
+        <v>3918.84</v>
       </c>
       <c r="N10" t="n">
-        <v>3990</v>
+        <v>3944.46</v>
       </c>
       <c r="O10" t="n">
-        <v>4019.65</v>
+        <v>4013.3</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -1382,7 +1382,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="10" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1392,73 +1392,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3865.32</v>
+        <v>3791.66</v>
       </c>
       <c r="C11" t="n">
-        <v>3869.22</v>
+        <v>3831.66</v>
       </c>
       <c r="D11" t="n">
-        <v>3745.17</v>
+        <v>3741.11</v>
       </c>
       <c r="E11" t="n">
-        <v>3764.16</v>
+        <v>3796.28</v>
       </c>
       <c r="F11" t="n">
-        <v>-118.26</v>
+        <v>32.13</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0305</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>124.04</v>
+        <v>90.55</v>
       </c>
       <c r="I11" t="n">
-        <v>3794.75</v>
+        <v>3621.13</v>
       </c>
       <c r="J11" t="n">
-        <v>3798.76</v>
+        <v>3618.59</v>
       </c>
       <c r="K11" t="n">
-        <v>3845.99</v>
+        <v>3702.13</v>
       </c>
       <c r="L11" t="n">
-        <v>3893.22</v>
+        <v>3785.67</v>
       </c>
       <c r="M11" t="n">
-        <v>3918.84</v>
+        <v>3826.18</v>
       </c>
       <c r="N11" t="n">
-        <v>3944.46</v>
+        <v>3866.68</v>
       </c>
       <c r="O11" t="n">
-        <v>4013.3</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+        <v>3993.26</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1466,60 +1462,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="10" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3791.66</v>
+        <v>3812.16</v>
       </c>
       <c r="C12" t="n">
-        <v>3831.66</v>
+        <v>3864.6</v>
       </c>
       <c r="D12" t="n">
-        <v>3741.11</v>
+        <v>3743.36</v>
       </c>
       <c r="E12" t="n">
-        <v>3796.28</v>
+        <v>3864.37</v>
       </c>
       <c r="F12" t="n">
-        <v>32.13</v>
+        <v>68.09</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0179</v>
       </c>
       <c r="H12" t="n">
-        <v>90.55</v>
+        <v>121.24</v>
       </c>
       <c r="I12" t="n">
-        <v>3621.13</v>
+        <v>3650.56</v>
       </c>
       <c r="J12" t="n">
-        <v>3618.59</v>
+        <v>3710.68</v>
       </c>
       <c r="K12" t="n">
-        <v>3702.13</v>
+        <v>3751.01</v>
       </c>
       <c r="L12" t="n">
-        <v>3785.67</v>
+        <v>3791.33</v>
       </c>
       <c r="M12" t="n">
-        <v>3826.18</v>
+        <v>3841.56</v>
       </c>
       <c r="N12" t="n">
-        <v>3866.68</v>
+        <v>3891.78</v>
       </c>
       <c r="O12" t="n">
-        <v>3993.26</v>
+        <v>3922.21</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1527,17 +1527,19 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U12" s="8" t="n">
@@ -1546,64 +1548,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="10" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3812.16</v>
+        <v>3839.67</v>
       </c>
       <c r="C13" t="n">
-        <v>3864.6</v>
+        <v>3884.44</v>
       </c>
       <c r="D13" t="n">
-        <v>3743.36</v>
+        <v>3839.67</v>
       </c>
       <c r="E13" t="n">
-        <v>3864.37</v>
+        <v>3867.03</v>
       </c>
       <c r="F13" t="n">
-        <v>68.09</v>
+        <v>2.67</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0007</v>
       </c>
       <c r="H13" t="n">
-        <v>121.24</v>
+        <v>44.77</v>
       </c>
       <c r="I13" t="n">
-        <v>3650.56</v>
+        <v>3622.12</v>
       </c>
       <c r="J13" t="n">
-        <v>3710.68</v>
+        <v>3773.32</v>
       </c>
       <c r="K13" t="n">
-        <v>3751.01</v>
+        <v>3803.75</v>
       </c>
       <c r="L13" t="n">
-        <v>3791.33</v>
+        <v>3834.17</v>
       </c>
       <c r="M13" t="n">
-        <v>3841.56</v>
+        <v>3924.99</v>
       </c>
       <c r="N13" t="n">
-        <v>3891.78</v>
+        <v>4015.8</v>
       </c>
       <c r="O13" t="n">
-        <v>3922.21</v>
+        <v>3985.84</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1611,20 +1613,16 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1632,7 +1630,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="10" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1646,50 +1644,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3839.67</v>
+        <v>3868.09</v>
       </c>
       <c r="C14" t="n">
-        <v>3884.44</v>
+        <v>3878.83</v>
       </c>
       <c r="D14" t="n">
-        <v>3839.67</v>
+        <v>3851.71</v>
       </c>
       <c r="E14" t="n">
-        <v>3867.03</v>
+        <v>3876.78</v>
       </c>
       <c r="F14" t="n">
-        <v>2.67</v>
+        <v>9.74</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.0025</v>
       </c>
       <c r="H14" t="n">
-        <v>44.77</v>
+        <v>27.13</v>
       </c>
       <c r="I14" t="n">
-        <v>3622.12</v>
+        <v>3794.9</v>
       </c>
       <c r="J14" t="n">
-        <v>3773.32</v>
+        <v>3824.76</v>
       </c>
       <c r="K14" t="n">
-        <v>3803.75</v>
+        <v>3844.65</v>
       </c>
       <c r="L14" t="n">
-        <v>3834.17</v>
+        <v>3864.54</v>
       </c>
       <c r="M14" t="n">
-        <v>3924.99</v>
+        <v>3889.42</v>
       </c>
       <c r="N14" t="n">
-        <v>4015.8</v>
+        <v>3914.3</v>
       </c>
       <c r="O14" t="n">
-        <v>3985.84</v>
+        <v>3929.21</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1700,7 +1698,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="11" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
@@ -1714,77 +1712,83 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="10" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3868.09</v>
+        <v>3853.63</v>
       </c>
       <c r="C15" t="n">
-        <v>3878.83</v>
+        <v>3861.04</v>
       </c>
       <c r="D15" t="n">
-        <v>3851.71</v>
+        <v>3808.64</v>
       </c>
       <c r="E15" t="n">
-        <v>3876.78</v>
+        <v>3814.2</v>
       </c>
       <c r="F15" t="n">
-        <v>9.74</v>
+        <v>-62.58</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0025</v>
+        <v>-0.0161</v>
       </c>
       <c r="H15" t="n">
-        <v>27.13</v>
+        <v>52.4</v>
       </c>
       <c r="I15" t="n">
-        <v>3794.9</v>
+        <v>3824.58</v>
       </c>
       <c r="J15" t="n">
-        <v>3824.76</v>
+        <v>3855.41</v>
       </c>
       <c r="K15" t="n">
-        <v>3844.65</v>
+        <v>3863.21</v>
       </c>
       <c r="L15" t="n">
-        <v>3864.54</v>
+        <v>3871.02</v>
       </c>
       <c r="M15" t="n">
-        <v>3889.42</v>
+        <v>3890.34</v>
       </c>
       <c r="N15" t="n">
-        <v>3914.3</v>
+        <v>3909.66</v>
       </c>
       <c r="O15" t="n">
-        <v>3929.21</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>3905.96</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1796,177 +1800,175 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="10" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3853.63</v>
+        <v>3808.9</v>
       </c>
       <c r="C16" t="n">
-        <v>3861.04</v>
+        <v>3858.31</v>
       </c>
       <c r="D16" t="n">
-        <v>3808.64</v>
+        <v>3793.45</v>
       </c>
       <c r="E16" t="n">
-        <v>3814.2</v>
+        <v>3858.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-62.58</v>
+        <v>44.05</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0161</v>
+        <v>0.0115</v>
       </c>
       <c r="H16" t="n">
-        <v>52.4</v>
+        <v>64.86</v>
       </c>
       <c r="I16" t="n">
-        <v>3824.58</v>
+        <v>3756.23</v>
       </c>
       <c r="J16" t="n">
-        <v>3855.41</v>
+        <v>3751.47</v>
       </c>
       <c r="K16" t="n">
-        <v>3863.21</v>
+        <v>3788</v>
       </c>
       <c r="L16" t="n">
-        <v>3871.02</v>
+        <v>3824.52</v>
       </c>
       <c r="M16" t="n">
-        <v>3890.34</v>
+        <v>3840.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3909.66</v>
+        <v>3856.28</v>
       </c>
       <c r="O16" t="n">
-        <v>3905.96</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>3913.44</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3808.9</v>
+        <v>3823.13</v>
       </c>
       <c r="C17" t="n">
-        <v>3858.31</v>
+        <v>3844.01</v>
       </c>
       <c r="D17" t="n">
-        <v>3793.45</v>
+        <v>3797.37</v>
       </c>
       <c r="E17" t="n">
-        <v>3858.25</v>
+        <v>3813.31</v>
       </c>
       <c r="F17" t="n">
-        <v>44.05</v>
+        <v>-44.93</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0115</v>
+        <v>-0.0116</v>
       </c>
       <c r="H17" t="n">
-        <v>64.86</v>
+        <v>46.64</v>
       </c>
       <c r="I17" t="n">
-        <v>3756.23</v>
+        <v>3728.59</v>
       </c>
       <c r="J17" t="n">
-        <v>3751.47</v>
+        <v>3809.57</v>
       </c>
       <c r="K17" t="n">
-        <v>3788</v>
+        <v>3825.81</v>
       </c>
       <c r="L17" t="n">
-        <v>3824.52</v>
+        <v>3842.06</v>
       </c>
       <c r="M17" t="n">
-        <v>3840.4</v>
+        <v>3890.68</v>
       </c>
       <c r="N17" t="n">
-        <v>3856.28</v>
+        <v>3939.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3913.44</v>
+        <v>3923.17</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="Q17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1980,476 +1982,470 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3823.13</v>
+        <v>3823.29</v>
       </c>
       <c r="C18" t="n">
-        <v>3844.01</v>
+        <v>3845.77</v>
       </c>
       <c r="D18" t="n">
-        <v>3797.37</v>
+        <v>3782.48</v>
       </c>
       <c r="E18" t="n">
-        <v>3813.31</v>
+        <v>3828.47</v>
       </c>
       <c r="F18" t="n">
-        <v>-44.93</v>
+        <v>15.15</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0116</v>
+        <v>0.004</v>
       </c>
       <c r="H18" t="n">
-        <v>46.64</v>
+        <v>63.29</v>
       </c>
       <c r="I18" t="n">
-        <v>3728.59</v>
+        <v>3750.73</v>
       </c>
       <c r="J18" t="n">
-        <v>3809.57</v>
+        <v>3762.99</v>
       </c>
       <c r="K18" t="n">
-        <v>3825.81</v>
+        <v>3790</v>
       </c>
       <c r="L18" t="n">
-        <v>3842.06</v>
+        <v>3817</v>
       </c>
       <c r="M18" t="n">
-        <v>3890.68</v>
+        <v>3836.63</v>
       </c>
       <c r="N18" t="n">
-        <v>3939.29</v>
+        <v>3856.27</v>
       </c>
       <c r="O18" t="n">
-        <v>3923.17</v>
+        <v>3890.65</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3823.29</v>
+        <v>3812.11</v>
       </c>
       <c r="C19" t="n">
-        <v>3845.77</v>
+        <v>3839.34</v>
       </c>
       <c r="D19" t="n">
-        <v>3782.48</v>
+        <v>3767.5</v>
       </c>
       <c r="E19" t="n">
-        <v>3828.47</v>
+        <v>3804.69</v>
       </c>
       <c r="F19" t="n">
-        <v>15.15</v>
+        <v>-23.78</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0062</v>
       </c>
       <c r="H19" t="n">
-        <v>63.29</v>
+        <v>71.84</v>
       </c>
       <c r="I19" t="n">
-        <v>3750.73</v>
+        <v>3719.2</v>
       </c>
       <c r="J19" t="n">
-        <v>3762.99</v>
+        <v>3772.36</v>
       </c>
       <c r="K19" t="n">
-        <v>3790</v>
+        <v>3796.83</v>
       </c>
       <c r="L19" t="n">
-        <v>3817</v>
+        <v>3821.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3836.63</v>
+        <v>3860.11</v>
       </c>
       <c r="N19" t="n">
-        <v>3856.27</v>
+        <v>3898.93</v>
       </c>
       <c r="O19" t="n">
-        <v>3890.65</v>
+        <v>3909.05</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3812.11</v>
+        <v>3833.54</v>
       </c>
       <c r="C20" t="n">
-        <v>3839.34</v>
+        <v>3847.09</v>
       </c>
       <c r="D20" t="n">
-        <v>3767.5</v>
+        <v>3822.37</v>
       </c>
       <c r="E20" t="n">
-        <v>3804.69</v>
+        <v>3832.26</v>
       </c>
       <c r="F20" t="n">
-        <v>-23.78</v>
+        <v>27.57</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0062</v>
+        <v>0.0072</v>
       </c>
       <c r="H20" t="n">
-        <v>71.84</v>
+        <v>24.72</v>
       </c>
       <c r="I20" t="n">
-        <v>3719.2</v>
+        <v>3695.66</v>
       </c>
       <c r="J20" t="n">
-        <v>3772.36</v>
+        <v>3733.49</v>
       </c>
       <c r="K20" t="n">
-        <v>3796.83</v>
+        <v>3768.77</v>
       </c>
       <c r="L20" t="n">
-        <v>3821.3</v>
+        <v>3804.06</v>
       </c>
       <c r="M20" t="n">
-        <v>3860.11</v>
+        <v>3840.61</v>
       </c>
       <c r="N20" t="n">
-        <v>3898.93</v>
+        <v>3877.17</v>
       </c>
       <c r="O20" t="n">
-        <v>3909.05</v>
+        <v>3911.18</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
       <c r="U20" s="8" t="n">
         <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3833.54</v>
+        <v>3812.61</v>
       </c>
       <c r="C21" t="n">
-        <v>3847.09</v>
+        <v>3827.64</v>
       </c>
       <c r="D21" t="n">
-        <v>3822.37</v>
+        <v>3797.64</v>
       </c>
       <c r="E21" t="n">
-        <v>3832.26</v>
+        <v>3809.66</v>
       </c>
       <c r="F21" t="n">
-        <v>27.57</v>
+        <v>-22.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0072</v>
+        <v>-0.0059</v>
       </c>
       <c r="H21" t="n">
-        <v>24.72</v>
+        <v>29.99</v>
       </c>
       <c r="I21" t="n">
-        <v>3695.66</v>
+        <v>3797.66</v>
       </c>
       <c r="J21" t="n">
-        <v>3733.49</v>
+        <v>3806.31</v>
       </c>
       <c r="K21" t="n">
-        <v>3768.77</v>
+        <v>3819.9</v>
       </c>
       <c r="L21" t="n">
-        <v>3804.06</v>
+        <v>3833.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3840.61</v>
+        <v>3844.62</v>
       </c>
       <c r="N21" t="n">
-        <v>3877.17</v>
+        <v>3855.75</v>
       </c>
       <c r="O21" t="n">
-        <v>3911.18</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
+        <v>3871.81</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
       <c r="U21" s="8" t="n">
         <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3812.61</v>
+        <v>3816.37</v>
       </c>
       <c r="C22" t="n">
-        <v>3827.64</v>
+        <v>3831.94</v>
       </c>
       <c r="D22" t="n">
-        <v>3797.64</v>
+        <v>3799.52</v>
       </c>
       <c r="E22" t="n">
-        <v>3809.66</v>
+        <v>3822.28</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.6</v>
+        <v>12.62</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0033</v>
       </c>
       <c r="H22" t="n">
-        <v>29.99</v>
+        <v>32.42</v>
       </c>
       <c r="I22" t="n">
-        <v>3797.66</v>
+        <v>3767.65</v>
       </c>
       <c r="J22" t="n">
-        <v>3806.31</v>
+        <v>3778.18</v>
       </c>
       <c r="K22" t="n">
-        <v>3819.9</v>
+        <v>3794.67</v>
       </c>
       <c r="L22" t="n">
-        <v>3833.5</v>
+        <v>3811.15</v>
       </c>
       <c r="M22" t="n">
-        <v>3844.62</v>
+        <v>3824.66</v>
       </c>
       <c r="N22" t="n">
-        <v>3855.75</v>
+        <v>3838.17</v>
       </c>
       <c r="O22" t="n">
-        <v>3871.81</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
+        <v>3857.63</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
       <c r="U22" s="8" t="n">
         <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3816.37</v>
+        <v>3815.12</v>
       </c>
       <c r="C23" t="n">
-        <v>3831.94</v>
+        <v>3884.4</v>
       </c>
       <c r="D23" t="n">
-        <v>3799.52</v>
+        <v>3815.12</v>
       </c>
       <c r="E23" t="n">
-        <v>3822.28</v>
+        <v>3878.43</v>
       </c>
       <c r="F23" t="n">
-        <v>12.62</v>
+        <v>56.15</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0033</v>
+        <v>0.0147</v>
       </c>
       <c r="H23" t="n">
-        <v>32.42</v>
+        <v>69.27</v>
       </c>
       <c r="I23" t="n">
-        <v>3767.65</v>
+        <v>3767.11</v>
       </c>
       <c r="J23" t="n">
-        <v>3778.18</v>
+        <v>3793.15</v>
       </c>
       <c r="K23" t="n">
-        <v>3794.67</v>
+        <v>3806.08</v>
       </c>
       <c r="L23" t="n">
-        <v>3811.15</v>
+        <v>3819.01</v>
       </c>
       <c r="M23" t="n">
-        <v>3824.66</v>
+        <v>3838.49</v>
       </c>
       <c r="N23" t="n">
-        <v>3838.17</v>
+        <v>3857.98</v>
       </c>
       <c r="O23" t="n">
-        <v>3857.63</v>
+        <v>3864.36</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2460,23 +2456,27 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="11" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2486,50 +2486,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="C24" t="n">
-        <v>3884.4</v>
+        <v>3902.05</v>
       </c>
       <c r="D24" t="n">
-        <v>3815.12</v>
+        <v>3864.27</v>
       </c>
       <c r="E24" t="n">
-        <v>3878.43</v>
+        <v>3900.35</v>
       </c>
       <c r="F24" t="n">
-        <v>56.15</v>
+        <v>21.92</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0057</v>
       </c>
       <c r="H24" t="n">
-        <v>69.27</v>
+        <v>37.78</v>
       </c>
       <c r="I24" t="n">
-        <v>3767.11</v>
+        <v>3745.85</v>
       </c>
       <c r="J24" t="n">
-        <v>3793.15</v>
+        <v>3823.49</v>
       </c>
       <c r="K24" t="n">
-        <v>3806.08</v>
+        <v>3843.79</v>
       </c>
       <c r="L24" t="n">
-        <v>3819.01</v>
+        <v>3864.09</v>
       </c>
       <c r="M24" t="n">
-        <v>3838.49</v>
+        <v>3913.07</v>
       </c>
       <c r="N24" t="n">
-        <v>3857.98</v>
+        <v>3962.04</v>
       </c>
       <c r="O24" t="n">
-        <v>3864.36</v>
+        <v>3953.67</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2540,27 +2540,23 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="11" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2570,50 +2566,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3864.27</v>
+        <v>3896.49</v>
       </c>
       <c r="C25" t="n">
-        <v>3902.05</v>
+        <v>3940.94</v>
       </c>
       <c r="D25" t="n">
-        <v>3864.27</v>
+        <v>3885.62</v>
       </c>
       <c r="E25" t="n">
-        <v>3900.35</v>
+        <v>3940.04</v>
       </c>
       <c r="F25" t="n">
-        <v>21.92</v>
+        <v>39.69</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0102</v>
       </c>
       <c r="H25" t="n">
-        <v>37.78</v>
+        <v>55.31</v>
       </c>
       <c r="I25" t="n">
-        <v>3745.85</v>
+        <v>3826.49</v>
       </c>
       <c r="J25" t="n">
-        <v>3823.49</v>
+        <v>3871.17</v>
       </c>
       <c r="K25" t="n">
-        <v>3843.79</v>
+        <v>3881.46</v>
       </c>
       <c r="L25" t="n">
-        <v>3864.09</v>
+        <v>3891.76</v>
       </c>
       <c r="M25" t="n">
-        <v>3913.07</v>
+        <v>3919.24</v>
       </c>
       <c r="N25" t="n">
-        <v>3962.04</v>
+        <v>3946.73</v>
       </c>
       <c r="O25" t="n">
-        <v>3953.67</v>
+        <v>3939.83</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2624,23 +2620,25 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="11" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2650,50 +2648,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3896.49</v>
+        <v>3943.82</v>
       </c>
       <c r="C26" t="n">
-        <v>3940.94</v>
+        <v>3967.59</v>
       </c>
       <c r="D26" t="n">
-        <v>3885.62</v>
+        <v>3938.62</v>
       </c>
       <c r="E26" t="n">
-        <v>3940.04</v>
+        <v>3966.59</v>
       </c>
       <c r="F26" t="n">
-        <v>39.69</v>
+        <v>26.56</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0067</v>
       </c>
       <c r="H26" t="n">
-        <v>55.31</v>
+        <v>28.97</v>
       </c>
       <c r="I26" t="n">
-        <v>3826.49</v>
+        <v>3830.31</v>
       </c>
       <c r="J26" t="n">
-        <v>3871.17</v>
+        <v>3898.11</v>
       </c>
       <c r="K26" t="n">
-        <v>3881.46</v>
+        <v>3912.38</v>
       </c>
       <c r="L26" t="n">
-        <v>3891.76</v>
+        <v>3926.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3919.24</v>
+        <v>3967.69</v>
       </c>
       <c r="N26" t="n">
-        <v>3946.73</v>
+        <v>4008.73</v>
       </c>
       <c r="O26" t="n">
-        <v>3939.83</v>
+        <v>3996.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2704,25 +2702,23 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="11" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
       </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2732,70 +2728,72 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3943.82</v>
+        <v>3950.71</v>
       </c>
       <c r="C27" t="n">
-        <v>3967.59</v>
+        <v>3966.39</v>
       </c>
       <c r="D27" t="n">
-        <v>3938.62</v>
+        <v>3930.64</v>
       </c>
       <c r="E27" t="n">
-        <v>3966.59</v>
+        <v>3934.09</v>
       </c>
       <c r="F27" t="n">
-        <v>26.56</v>
+        <v>-32.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>28.97</v>
+        <v>35.75</v>
       </c>
       <c r="I27" t="n">
-        <v>3830.31</v>
+        <v>3909.66</v>
       </c>
       <c r="J27" t="n">
-        <v>3898.11</v>
+        <v>3944.37</v>
       </c>
       <c r="K27" t="n">
-        <v>3912.38</v>
+        <v>3952.11</v>
       </c>
       <c r="L27" t="n">
-        <v>3926.66</v>
+        <v>3959.85</v>
       </c>
       <c r="M27" t="n">
-        <v>3967.69</v>
+        <v>3981.08</v>
       </c>
       <c r="N27" t="n">
-        <v>4008.73</v>
+        <v>4002.3</v>
       </c>
       <c r="O27" t="n">
-        <v>3996.25</v>
+        <v>3996.56</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
       <c r="U27" s="8" t="n">
         <v/>
       </c>
@@ -2804,7 +2802,7 @@
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2812,150 +2810,156 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3950.71</v>
+        <v>3933.55</v>
       </c>
       <c r="C28" t="n">
-        <v>3966.39</v>
+        <v>3950.62</v>
       </c>
       <c r="D28" t="n">
-        <v>3930.64</v>
+        <v>3927.55</v>
       </c>
       <c r="E28" t="n">
-        <v>3934.09</v>
+        <v>3946.68</v>
       </c>
       <c r="F28" t="n">
-        <v>-32.5</v>
+        <v>12.58</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H28" t="n">
-        <v>35.75</v>
+        <v>23.07</v>
       </c>
       <c r="I28" t="n">
-        <v>3909.66</v>
+        <v>3894.89</v>
       </c>
       <c r="J28" t="n">
-        <v>3944.37</v>
+        <v>3891.13</v>
       </c>
       <c r="K28" t="n">
-        <v>3952.11</v>
+        <v>3916.22</v>
       </c>
       <c r="L28" t="n">
-        <v>3959.85</v>
+        <v>3941.3</v>
       </c>
       <c r="M28" t="n">
-        <v>3981.08</v>
+        <v>3951.97</v>
       </c>
       <c r="N28" t="n">
-        <v>4002.3</v>
+        <v>3962.63</v>
       </c>
       <c r="O28" t="n">
-        <v>3996.56</v>
+        <v>4002.14</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3933.55</v>
+        <v>3957.16</v>
       </c>
       <c r="C29" t="n">
-        <v>3950.62</v>
+        <v>3968.48</v>
       </c>
       <c r="D29" t="n">
-        <v>3927.55</v>
+        <v>3924.64</v>
       </c>
       <c r="E29" t="n">
-        <v>3946.68</v>
+        <v>3926.97</v>
       </c>
       <c r="F29" t="n">
-        <v>12.58</v>
+        <v>-19.71</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.005</v>
       </c>
       <c r="H29" t="n">
-        <v>23.07</v>
+        <v>43.83</v>
       </c>
       <c r="I29" t="n">
-        <v>3894.89</v>
+        <v>3904.48</v>
       </c>
       <c r="J29" t="n">
-        <v>3891.13</v>
+        <v>3927.4</v>
       </c>
       <c r="K29" t="n">
-        <v>3916.22</v>
+        <v>3935.14</v>
       </c>
       <c r="L29" t="n">
-        <v>3941.3</v>
+        <v>3942.88</v>
       </c>
       <c r="M29" t="n">
-        <v>3951.97</v>
+        <v>3958.21</v>
       </c>
       <c r="N29" t="n">
-        <v>3962.63</v>
+        <v>3973.54</v>
       </c>
       <c r="O29" t="n">
-        <v>4002.14</v>
+        <v>3973.69</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U29" s="8" t="n">
@@ -2964,7 +2968,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2978,58 +2982,56 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3957.16</v>
+        <v>3930.02</v>
       </c>
       <c r="C30" t="n">
-        <v>3968.48</v>
+        <v>3932.64</v>
       </c>
       <c r="D30" t="n">
-        <v>3924.64</v>
+        <v>3903.71</v>
       </c>
       <c r="E30" t="n">
-        <v>3926.97</v>
+        <v>3927.18</v>
       </c>
       <c r="F30" t="n">
-        <v>-19.71</v>
+        <v>0.21</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.005</v>
+        <v>0.0001</v>
       </c>
       <c r="H30" t="n">
-        <v>43.83</v>
+        <v>28.93</v>
       </c>
       <c r="I30" t="n">
-        <v>3904.48</v>
+        <v>3880.81</v>
       </c>
       <c r="J30" t="n">
-        <v>3927.4</v>
+        <v>3873.33</v>
       </c>
       <c r="K30" t="n">
-        <v>3935.14</v>
+        <v>3905.05</v>
       </c>
       <c r="L30" t="n">
-        <v>3942.88</v>
+        <v>3936.76</v>
       </c>
       <c r="M30" t="n">
-        <v>3958.21</v>
+        <v>3948.88</v>
       </c>
       <c r="N30" t="n">
-        <v>3973.54</v>
+        <v>3961</v>
       </c>
       <c r="O30" t="n">
-        <v>3973.69</v>
+        <v>4012.31</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
@@ -3038,13 +3040,11 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3052,7 +3052,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="10" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3066,50 +3066,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3930.02</v>
+        <v>3930.1</v>
       </c>
       <c r="C31" t="n">
-        <v>3932.64</v>
+        <v>3983.51</v>
       </c>
       <c r="D31" t="n">
-        <v>3903.71</v>
+        <v>3924.47</v>
       </c>
       <c r="E31" t="n">
-        <v>3927.18</v>
+        <v>3982.65</v>
       </c>
       <c r="F31" t="n">
-        <v>0.21</v>
+        <v>55.48</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.0141</v>
       </c>
       <c r="H31" t="n">
-        <v>28.93</v>
+        <v>59.03</v>
       </c>
       <c r="I31" t="n">
-        <v>3880.81</v>
+        <v>3874.77</v>
       </c>
       <c r="J31" t="n">
-        <v>3873.33</v>
+        <v>3902.74</v>
       </c>
       <c r="K31" t="n">
-        <v>3905.05</v>
+        <v>3912.71</v>
       </c>
       <c r="L31" t="n">
-        <v>3936.76</v>
+        <v>3922.67</v>
       </c>
       <c r="M31" t="n">
-        <v>3948.88</v>
+        <v>3941.64</v>
       </c>
       <c r="N31" t="n">
-        <v>3961</v>
+        <v>3960.61</v>
       </c>
       <c r="O31" t="n">
-        <v>4012.31</v>
+        <v>3961.57</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3117,83 +3117,83 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3930.1</v>
+        <v>3979.49</v>
       </c>
       <c r="C32" t="n">
-        <v>3983.51</v>
+        <v>3994.18</v>
       </c>
       <c r="D32" t="n">
-        <v>3924.47</v>
+        <v>3955.6</v>
       </c>
       <c r="E32" t="n">
-        <v>3982.65</v>
+        <v>3990.3</v>
       </c>
       <c r="F32" t="n">
-        <v>55.48</v>
+        <v>7.65</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0141</v>
+        <v>0.0019</v>
       </c>
       <c r="H32" t="n">
-        <v>59.03</v>
+        <v>38.58</v>
       </c>
       <c r="I32" t="n">
-        <v>3874.77</v>
+        <v>3865.44</v>
       </c>
       <c r="J32" t="n">
-        <v>3902.74</v>
+        <v>3937.95</v>
       </c>
       <c r="K32" t="n">
-        <v>3912.71</v>
+        <v>3953.14</v>
       </c>
       <c r="L32" t="n">
-        <v>3922.67</v>
+        <v>3968.32</v>
       </c>
       <c r="M32" t="n">
-        <v>3941.64</v>
+        <v>4012.17</v>
       </c>
       <c r="N32" t="n">
-        <v>3960.61</v>
+        <v>4056.02</v>
       </c>
       <c r="O32" t="n">
-        <v>3961.57</v>
+        <v>4042.54</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3204,27 +3204,23 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="11" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3234,70 +3230,74 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3979.49</v>
+        <v>3952.12</v>
       </c>
       <c r="C33" t="n">
-        <v>3994.18</v>
+        <v>3961.14</v>
       </c>
       <c r="D33" t="n">
-        <v>3955.6</v>
+        <v>3879.58</v>
       </c>
       <c r="E33" t="n">
-        <v>3990.3</v>
+        <v>3894.42</v>
       </c>
       <c r="F33" t="n">
-        <v>7.65</v>
+        <v>-95.88</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0019</v>
+        <v>-0.024</v>
       </c>
       <c r="H33" t="n">
-        <v>38.58</v>
+        <v>81.56</v>
       </c>
       <c r="I33" t="n">
-        <v>3865.44</v>
+        <v>3917.02</v>
       </c>
       <c r="J33" t="n">
-        <v>3937.95</v>
+        <v>3959.43</v>
       </c>
       <c r="K33" t="n">
-        <v>3953.14</v>
+        <v>3971.01</v>
       </c>
       <c r="L33" t="n">
-        <v>3968.32</v>
+        <v>3982.6</v>
       </c>
       <c r="M33" t="n">
-        <v>4012.17</v>
+        <v>4009.59</v>
       </c>
       <c r="N33" t="n">
-        <v>4056.02</v>
+        <v>4036.59</v>
       </c>
       <c r="O33" t="n">
-        <v>4042.54</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+        <v>4032.76</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3306,7 +3306,7 @@
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr"/>
@@ -3314,69 +3314,63 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3952.12</v>
+        <v>3907.21</v>
       </c>
       <c r="C34" t="n">
-        <v>3961.14</v>
+        <v>3925.06</v>
       </c>
       <c r="D34" t="n">
-        <v>3879.58</v>
+        <v>3888.1</v>
       </c>
       <c r="E34" t="n">
-        <v>3894.42</v>
+        <v>3903.72</v>
       </c>
       <c r="F34" t="n">
-        <v>-95.88</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.024</v>
+        <v>0.0024</v>
       </c>
       <c r="H34" t="n">
-        <v>81.56</v>
+        <v>36.96</v>
       </c>
       <c r="I34" t="n">
-        <v>3917.02</v>
+        <v>3798.02</v>
       </c>
       <c r="J34" t="n">
-        <v>3959.43</v>
+        <v>3799.9</v>
       </c>
       <c r="K34" t="n">
-        <v>3971.01</v>
+        <v>3853.64</v>
       </c>
       <c r="L34" t="n">
-        <v>3982.6</v>
+        <v>3907.39</v>
       </c>
       <c r="M34" t="n">
-        <v>4009.59</v>
+        <v>3935.2</v>
       </c>
       <c r="N34" t="n">
-        <v>4036.59</v>
+        <v>3963.01</v>
       </c>
       <c r="O34" t="n">
-        <v>4032.76</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>4042.69</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3388,60 +3382,64 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="10" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3907.21</v>
+        <v>3891.18</v>
       </c>
       <c r="C35" t="n">
-        <v>3925.06</v>
+        <v>3912.13</v>
       </c>
       <c r="D35" t="n">
-        <v>3888.1</v>
+        <v>3883.79</v>
       </c>
       <c r="E35" t="n">
-        <v>3903.72</v>
+        <v>3905.2</v>
       </c>
       <c r="F35" t="n">
-        <v>9.300000000000001</v>
+        <v>1.48</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0024</v>
+        <v>0.0004</v>
       </c>
       <c r="H35" t="n">
-        <v>36.96</v>
+        <v>28.34</v>
       </c>
       <c r="I35" t="n">
-        <v>3798.02</v>
+        <v>3851.14</v>
       </c>
       <c r="J35" t="n">
-        <v>3799.9</v>
+        <v>3865.33</v>
       </c>
       <c r="K35" t="n">
-        <v>3853.64</v>
+        <v>3885.24</v>
       </c>
       <c r="L35" t="n">
-        <v>3907.39</v>
+        <v>3905.15</v>
       </c>
       <c r="M35" t="n">
-        <v>3935.2</v>
+        <v>3922.2</v>
       </c>
       <c r="N35" t="n">
-        <v>3963.01</v>
+        <v>3939.25</v>
       </c>
       <c r="O35" t="n">
-        <v>4042.69</v>
+        <v>3962.02</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,12 +3447,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3466,79 +3466,83 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="10" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>3891.18</v>
+        <v>3902.7</v>
       </c>
       <c r="C36" t="n">
-        <v>3912.13</v>
+        <v>3910.24</v>
       </c>
       <c r="D36" t="n">
-        <v>3883.79</v>
+        <v>3855.35</v>
       </c>
       <c r="E36" t="n">
-        <v>3905.2</v>
+        <v>3882.01</v>
       </c>
       <c r="F36" t="n">
-        <v>1.48</v>
+        <v>-23.19</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0004</v>
+        <v>-0.0059</v>
       </c>
       <c r="H36" t="n">
-        <v>28.34</v>
+        <v>54.89</v>
       </c>
       <c r="I36" t="n">
-        <v>3851.14</v>
+        <v>3855.44</v>
       </c>
       <c r="J36" t="n">
-        <v>3865.33</v>
+        <v>3880.48</v>
       </c>
       <c r="K36" t="n">
-        <v>3885.24</v>
+        <v>3891.03</v>
       </c>
       <c r="L36" t="n">
-        <v>3905.15</v>
+        <v>3901.58</v>
       </c>
       <c r="M36" t="n">
-        <v>3922.2</v>
+        <v>3919.37</v>
       </c>
       <c r="N36" t="n">
-        <v>3939.25</v>
+        <v>3937.17</v>
       </c>
       <c r="O36" t="n">
-        <v>3962.02</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>3940.48</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3550,83 +3554,75 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="10" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>3902.7</v>
+        <v>3863.37</v>
       </c>
       <c r="C37" t="n">
-        <v>3910.24</v>
+        <v>3896.21</v>
       </c>
       <c r="D37" t="n">
-        <v>3855.35</v>
+        <v>3850.86</v>
       </c>
       <c r="E37" t="n">
-        <v>3882.01</v>
+        <v>3889.45</v>
       </c>
       <c r="F37" t="n">
-        <v>-23.19</v>
+        <v>7.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0059</v>
+        <v>0.0019</v>
       </c>
       <c r="H37" t="n">
-        <v>54.89</v>
+        <v>45.34</v>
       </c>
       <c r="I37" t="n">
-        <v>3855.44</v>
+        <v>3800.46</v>
       </c>
       <c r="J37" t="n">
-        <v>3880.48</v>
+        <v>3826.73</v>
       </c>
       <c r="K37" t="n">
-        <v>3891.03</v>
+        <v>3854.56</v>
       </c>
       <c r="L37" t="n">
-        <v>3901.58</v>
+        <v>3882.4</v>
       </c>
       <c r="M37" t="n">
-        <v>3919.37</v>
+        <v>3909.45</v>
       </c>
       <c r="N37" t="n">
-        <v>3937.17</v>
+        <v>3936.5</v>
       </c>
       <c r="O37" t="n">
-        <v>3940.48</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+        <v>3965.13</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3638,60 +3634,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="10" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3863.37</v>
+        <v>3881.74</v>
       </c>
       <c r="C38" t="n">
-        <v>3896.21</v>
+        <v>3926.44</v>
       </c>
       <c r="D38" t="n">
-        <v>3850.86</v>
+        <v>3881.74</v>
       </c>
       <c r="E38" t="n">
-        <v>3889.45</v>
+        <v>3912.52</v>
       </c>
       <c r="F38" t="n">
-        <v>7.44</v>
+        <v>23.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0019</v>
+        <v>0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>45.34</v>
+        <v>44.69</v>
       </c>
       <c r="I38" t="n">
-        <v>3800.46</v>
+        <v>3805.52</v>
       </c>
       <c r="J38" t="n">
-        <v>3826.73</v>
+        <v>3852.06</v>
       </c>
       <c r="K38" t="n">
-        <v>3854.56</v>
+        <v>3866.77</v>
       </c>
       <c r="L38" t="n">
-        <v>3882.4</v>
+        <v>3881.49</v>
       </c>
       <c r="M38" t="n">
-        <v>3909.45</v>
+        <v>3912.12</v>
       </c>
       <c r="N38" t="n">
-        <v>3936.5</v>
+        <v>3942.74</v>
       </c>
       <c r="O38" t="n">
-        <v>3965.13</v>
+        <v>3941.55</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,18 +3699,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3718,64 +3718,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>3881.74</v>
+        <v>3911.89</v>
       </c>
       <c r="C39" t="n">
-        <v>3926.44</v>
+        <v>3958.03</v>
       </c>
       <c r="D39" t="n">
-        <v>3881.74</v>
+        <v>3909.31</v>
       </c>
       <c r="E39" t="n">
-        <v>3912.52</v>
+        <v>3956.57</v>
       </c>
       <c r="F39" t="n">
-        <v>23.08</v>
+        <v>44.05</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0113</v>
       </c>
       <c r="H39" t="n">
-        <v>44.69</v>
+        <v>48.72</v>
       </c>
       <c r="I39" t="n">
-        <v>3805.52</v>
+        <v>3837.05</v>
       </c>
       <c r="J39" t="n">
-        <v>3852.06</v>
+        <v>3872.05</v>
       </c>
       <c r="K39" t="n">
-        <v>3866.77</v>
+        <v>3890.18</v>
       </c>
       <c r="L39" t="n">
-        <v>3881.49</v>
+        <v>3908.31</v>
       </c>
       <c r="M39" t="n">
-        <v>3912.12</v>
+        <v>3934.87</v>
       </c>
       <c r="N39" t="n">
-        <v>3942.74</v>
+        <v>3961.43</v>
       </c>
       <c r="O39" t="n">
-        <v>3941.55</v>
+        <v>3971.13</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3786,23 +3786,25 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="11" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3816,50 +3818,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3911.89</v>
+        <v>3950.24</v>
       </c>
       <c r="C40" t="n">
-        <v>3958.03</v>
+        <v>3970.31</v>
       </c>
       <c r="D40" t="n">
-        <v>3909.31</v>
+        <v>3947.8</v>
       </c>
       <c r="E40" t="n">
-        <v>3956.57</v>
+        <v>3952.18</v>
       </c>
       <c r="F40" t="n">
-        <v>44.05</v>
+        <v>-4.39</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0113</v>
+        <v>-0.0011</v>
       </c>
       <c r="H40" t="n">
-        <v>48.72</v>
+        <v>22.51</v>
       </c>
       <c r="I40" t="n">
-        <v>3837.05</v>
+        <v>3860.59</v>
       </c>
       <c r="J40" t="n">
-        <v>3872.05</v>
+        <v>3919.3</v>
       </c>
       <c r="K40" t="n">
-        <v>3890.18</v>
+        <v>3932.21</v>
       </c>
       <c r="L40" t="n">
-        <v>3908.31</v>
+        <v>3945.12</v>
       </c>
       <c r="M40" t="n">
-        <v>3934.87</v>
+        <v>3980.93</v>
       </c>
       <c r="N40" t="n">
-        <v>3961.43</v>
+        <v>4016.74</v>
       </c>
       <c r="O40" t="n">
-        <v>3971.13</v>
+        <v>4006.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3870,82 +3872,78 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="10" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>3950.24</v>
+        <v>3926.53</v>
       </c>
       <c r="C41" t="n">
-        <v>3970.31</v>
+        <v>3986.3</v>
       </c>
       <c r="D41" t="n">
-        <v>3947.8</v>
+        <v>3926.5</v>
       </c>
       <c r="E41" t="n">
-        <v>3952.18</v>
+        <v>3986.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.39</v>
+        <v>34.12</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.0086</v>
       </c>
       <c r="H41" t="n">
-        <v>22.51</v>
+        <v>59.79</v>
       </c>
       <c r="I41" t="n">
-        <v>3860.59</v>
+        <v>3925.29</v>
       </c>
       <c r="J41" t="n">
-        <v>3919.3</v>
+        <v>3926.23</v>
       </c>
       <c r="K41" t="n">
-        <v>3932.21</v>
+        <v>3940.92</v>
       </c>
       <c r="L41" t="n">
-        <v>3945.12</v>
+        <v>3955.62</v>
       </c>
       <c r="M41" t="n">
-        <v>3980.93</v>
+        <v>3963.43</v>
       </c>
       <c r="N41" t="n">
-        <v>4016.74</v>
+        <v>3971.25</v>
       </c>
       <c r="O41" t="n">
-        <v>4006.75</v>
+        <v>3992.82</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3953,81 +3951,89 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W41" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>3926.53</v>
+        <v>3979.88</v>
       </c>
       <c r="C42" t="n">
-        <v>3986.3</v>
+        <v>3995.18</v>
       </c>
       <c r="D42" t="n">
-        <v>3926.5</v>
+        <v>3976.47</v>
       </c>
       <c r="E42" t="n">
-        <v>3986.3</v>
+        <v>3979.89</v>
       </c>
       <c r="F42" t="n">
-        <v>34.12</v>
+        <v>-6.41</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.0016</v>
       </c>
       <c r="H42" t="n">
-        <v>59.79</v>
+        <v>18.71</v>
       </c>
       <c r="I42" t="n">
-        <v>3925.29</v>
+        <v>3866.71</v>
       </c>
       <c r="J42" t="n">
-        <v>3926.23</v>
+        <v>3941.45</v>
       </c>
       <c r="K42" t="n">
-        <v>3940.92</v>
+        <v>3956.4</v>
       </c>
       <c r="L42" t="n">
-        <v>3955.62</v>
+        <v>3971.35</v>
       </c>
       <c r="M42" t="n">
-        <v>3963.43</v>
+        <v>4016.2</v>
       </c>
       <c r="N42" t="n">
-        <v>3971.25</v>
+        <v>4061.04</v>
       </c>
       <c r="O42" t="n">
-        <v>3992.82</v>
+        <v>4046.09</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4035,32 +4041,24 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4074,63 +4072,69 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3979.88</v>
+        <v>3963.07</v>
       </c>
       <c r="C43" t="n">
-        <v>3995.18</v>
+        <v>3965.81</v>
       </c>
       <c r="D43" t="n">
-        <v>3976.47</v>
+        <v>3932.25</v>
       </c>
       <c r="E43" t="n">
-        <v>3979.89</v>
+        <v>3941.39</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.41</v>
+        <v>-38.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0016</v>
+        <v>-0.0097</v>
       </c>
       <c r="H43" t="n">
-        <v>18.71</v>
+        <v>33.56</v>
       </c>
       <c r="I43" t="n">
-        <v>3866.71</v>
+        <v>3957.76</v>
       </c>
       <c r="J43" t="n">
-        <v>3941.45</v>
+        <v>3958.21</v>
       </c>
       <c r="K43" t="n">
-        <v>3956.4</v>
+        <v>3970.53</v>
       </c>
       <c r="L43" t="n">
-        <v>3971.35</v>
+        <v>3982.85</v>
       </c>
       <c r="M43" t="n">
-        <v>4016.2</v>
+        <v>3989.24</v>
       </c>
       <c r="N43" t="n">
-        <v>4061.04</v>
+        <v>3995.63</v>
       </c>
       <c r="O43" t="n">
-        <v>4046.09</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>4013.88</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4144,85 +4148,77 @@
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>3963.07</v>
+        <v>3952.79</v>
       </c>
       <c r="C44" t="n">
-        <v>3965.81</v>
+        <v>3968.11</v>
       </c>
       <c r="D44" t="n">
-        <v>3932.25</v>
+        <v>3930.45</v>
       </c>
       <c r="E44" t="n">
-        <v>3941.39</v>
+        <v>3942.09</v>
       </c>
       <c r="F44" t="n">
-        <v>-38.5</v>
+        <v>0.7</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0097</v>
+        <v>0.0002</v>
       </c>
       <c r="H44" t="n">
-        <v>33.56</v>
+        <v>37.67</v>
       </c>
       <c r="I44" t="n">
-        <v>3957.76</v>
+        <v>3898.69</v>
       </c>
       <c r="J44" t="n">
-        <v>3958.21</v>
+        <v>3904.01</v>
       </c>
       <c r="K44" t="n">
-        <v>3970.53</v>
+        <v>3924.61</v>
       </c>
       <c r="L44" t="n">
-        <v>3982.85</v>
+        <v>3945.21</v>
       </c>
       <c r="M44" t="n">
-        <v>3989.24</v>
+        <v>3958.16</v>
       </c>
       <c r="N44" t="n">
-        <v>3995.63</v>
+        <v>3971.12</v>
       </c>
       <c r="O44" t="n">
-        <v>4013.88</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>3999.37</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4230,60 +4226,64 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="10" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3952.79</v>
+        <v>3955.55</v>
       </c>
       <c r="C45" t="n">
-        <v>3968.11</v>
+        <v>3980.2</v>
       </c>
       <c r="D45" t="n">
-        <v>3930.45</v>
+        <v>3915.22</v>
       </c>
       <c r="E45" t="n">
-        <v>3942.09</v>
+        <v>3930.12</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7</v>
+        <v>-11.97</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0002</v>
+        <v>-0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>37.67</v>
+        <v>64.98</v>
       </c>
       <c r="I45" t="n">
-        <v>3898.69</v>
+        <v>3892.78</v>
       </c>
       <c r="J45" t="n">
-        <v>3904.01</v>
+        <v>3900.83</v>
       </c>
       <c r="K45" t="n">
-        <v>3924.61</v>
+        <v>3923.26</v>
       </c>
       <c r="L45" t="n">
-        <v>3945.21</v>
+        <v>3945.68</v>
       </c>
       <c r="M45" t="n">
-        <v>3958.16</v>
+        <v>3960.92</v>
       </c>
       <c r="N45" t="n">
-        <v>3971.12</v>
+        <v>3976.16</v>
       </c>
       <c r="O45" t="n">
-        <v>3999.37</v>
+        <v>4005.78</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4291,12 +4291,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
@@ -4304,70 +4306,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="10" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3955.55</v>
+        <v>3942.51</v>
       </c>
       <c r="C46" t="n">
-        <v>3980.2</v>
+        <v>3948.42</v>
       </c>
       <c r="D46" t="n">
-        <v>3915.22</v>
+        <v>3916.49</v>
       </c>
       <c r="E46" t="n">
-        <v>3930.12</v>
+        <v>3932.7</v>
       </c>
       <c r="F46" t="n">
-        <v>-11.97</v>
+        <v>2.58</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.003</v>
+        <v>0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>64.98</v>
+        <v>31.93</v>
       </c>
       <c r="I46" t="n">
-        <v>3892.78</v>
+        <v>3850.24</v>
       </c>
       <c r="J46" t="n">
-        <v>3900.83</v>
+        <v>3856.34</v>
       </c>
       <c r="K46" t="n">
-        <v>3923.26</v>
+        <v>3897.63</v>
       </c>
       <c r="L46" t="n">
-        <v>3945.68</v>
+        <v>3938.91</v>
       </c>
       <c r="M46" t="n">
-        <v>3960.92</v>
+        <v>3962.61</v>
       </c>
       <c r="N46" t="n">
-        <v>3976.16</v>
+        <v>3986.3</v>
       </c>
       <c r="O46" t="n">
-        <v>4005.78</v>
+        <v>4045.18</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4375,87 +4379,81 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="10" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3942.51</v>
+        <v>3935.55</v>
       </c>
       <c r="C47" t="n">
-        <v>3948.42</v>
+        <v>3951.32</v>
       </c>
       <c r="D47" t="n">
-        <v>3916.49</v>
+        <v>3925.72</v>
       </c>
       <c r="E47" t="n">
-        <v>3932.7</v>
+        <v>3940.55</v>
       </c>
       <c r="F47" t="n">
-        <v>2.58</v>
+        <v>7.85</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0007</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="n">
-        <v>31.93</v>
+        <v>25.6</v>
       </c>
       <c r="I47" t="n">
-        <v>3850.24</v>
+        <v>3884.56</v>
       </c>
       <c r="J47" t="n">
-        <v>3856.34</v>
+        <v>3900.89</v>
       </c>
       <c r="K47" t="n">
-        <v>3897.63</v>
+        <v>3916.73</v>
       </c>
       <c r="L47" t="n">
-        <v>3938.91</v>
+        <v>3932.58</v>
       </c>
       <c r="M47" t="n">
-        <v>3962.61</v>
+        <v>3948.66</v>
       </c>
       <c r="N47" t="n">
-        <v>3986.3</v>
+        <v>3964.75</v>
       </c>
       <c r="O47" t="n">
-        <v>4045.18</v>
+        <v>3980.35</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4466,13 +4464,15 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4480,64 +4480,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="10" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3935.55</v>
+        <v>3943.92</v>
       </c>
       <c r="C48" t="n">
-        <v>3951.32</v>
+        <v>3958.12</v>
       </c>
       <c r="D48" t="n">
-        <v>3925.72</v>
+        <v>3933.47</v>
       </c>
       <c r="E48" t="n">
-        <v>3940.55</v>
+        <v>3951.51</v>
       </c>
       <c r="F48" t="n">
-        <v>7.85</v>
+        <v>10.96</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0028</v>
       </c>
       <c r="H48" t="n">
-        <v>25.6</v>
+        <v>24.65</v>
       </c>
       <c r="I48" t="n">
-        <v>3884.56</v>
+        <v>3900.12</v>
       </c>
       <c r="J48" t="n">
-        <v>3900.89</v>
+        <v>3915.96</v>
       </c>
       <c r="K48" t="n">
-        <v>3916.73</v>
+        <v>3927.75</v>
       </c>
       <c r="L48" t="n">
-        <v>3932.58</v>
+        <v>3939.54</v>
       </c>
       <c r="M48" t="n">
-        <v>3948.66</v>
+        <v>3953.35</v>
       </c>
       <c r="N48" t="n">
-        <v>3964.75</v>
+        <v>3967.17</v>
       </c>
       <c r="O48" t="n">
-        <v>3980.35</v>
+        <v>3976.92</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4548,14 +4548,14 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U48" s="8" t="n">
@@ -4564,7 +4564,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4578,141 +4578,141 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3943.92</v>
+        <v>3939.09</v>
       </c>
       <c r="C49" t="n">
-        <v>3958.12</v>
+        <v>3949.25</v>
       </c>
       <c r="D49" t="n">
-        <v>3933.47</v>
+        <v>3927.35</v>
       </c>
       <c r="E49" t="n">
-        <v>3951.51</v>
+        <v>3934.4</v>
       </c>
       <c r="F49" t="n">
-        <v>10.96</v>
+        <v>-17.1</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0028</v>
+        <v>-0.0043</v>
       </c>
       <c r="H49" t="n">
-        <v>24.65</v>
+        <v>21.91</v>
       </c>
       <c r="I49" t="n">
-        <v>3900.12</v>
+        <v>3908.82</v>
       </c>
       <c r="J49" t="n">
-        <v>3915.96</v>
+        <v>3929.72</v>
       </c>
       <c r="K49" t="n">
-        <v>3927.75</v>
+        <v>3939.18</v>
       </c>
       <c r="L49" t="n">
-        <v>3939.54</v>
+        <v>3948.65</v>
       </c>
       <c r="M49" t="n">
-        <v>3953.35</v>
+        <v>3963.83</v>
       </c>
       <c r="N49" t="n">
-        <v>3967.17</v>
+        <v>3979.01</v>
       </c>
       <c r="O49" t="n">
-        <v>3976.92</v>
+        <v>3982.76</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="10" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3939.09</v>
+        <v>3910.92</v>
       </c>
       <c r="C50" t="n">
-        <v>3949.25</v>
+        <v>3912.32</v>
       </c>
       <c r="D50" t="n">
-        <v>3927.35</v>
+        <v>3852.03</v>
       </c>
       <c r="E50" t="n">
-        <v>3934.4</v>
+        <v>3888.11</v>
       </c>
       <c r="F50" t="n">
-        <v>-17.1</v>
+        <v>-46.29</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0043</v>
+        <v>-0.0118</v>
       </c>
       <c r="H50" t="n">
-        <v>21.91</v>
+        <v>60.29</v>
       </c>
       <c r="I50" t="n">
-        <v>3908.82</v>
+        <v>3905.44</v>
       </c>
       <c r="J50" t="n">
-        <v>3929.72</v>
+        <v>3910.55</v>
       </c>
       <c r="K50" t="n">
-        <v>3939.18</v>
+        <v>3923.45</v>
       </c>
       <c r="L50" t="n">
-        <v>3948.65</v>
+        <v>3936.35</v>
       </c>
       <c r="M50" t="n">
-        <v>3963.83</v>
+        <v>3945.36</v>
       </c>
       <c r="N50" t="n">
-        <v>3979.01</v>
+        <v>3954.36</v>
       </c>
       <c r="O50" t="n">
-        <v>3982.76</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
+        <v>3971.16</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
@@ -4734,7 +4734,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="10" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4744,69 +4744,63 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3910.92</v>
+        <v>3867.02</v>
       </c>
       <c r="C51" t="n">
-        <v>3912.32</v>
+        <v>3895.51</v>
       </c>
       <c r="D51" t="n">
-        <v>3852.03</v>
+        <v>3867.02</v>
       </c>
       <c r="E51" t="n">
-        <v>3888.11</v>
+        <v>3885.33</v>
       </c>
       <c r="F51" t="n">
-        <v>-46.29</v>
+        <v>-2.78</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>60.29</v>
+        <v>28.49</v>
       </c>
       <c r="I51" t="n">
-        <v>3905.44</v>
+        <v>3791.74</v>
       </c>
       <c r="J51" t="n">
-        <v>3910.55</v>
+        <v>3830.78</v>
       </c>
       <c r="K51" t="n">
-        <v>3923.45</v>
+        <v>3857.96</v>
       </c>
       <c r="L51" t="n">
-        <v>3936.35</v>
+        <v>3885.14</v>
       </c>
       <c r="M51" t="n">
-        <v>3945.36</v>
+        <v>3918.26</v>
       </c>
       <c r="N51" t="n">
-        <v>3954.36</v>
+        <v>3951.37</v>
       </c>
       <c r="O51" t="n">
-        <v>3971.16</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>3972.62</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4818,73 +4812,81 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="10" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3867.02</v>
+        <v>3879.73</v>
       </c>
       <c r="C52" t="n">
-        <v>3895.51</v>
+        <v>3891.62</v>
       </c>
       <c r="D52" t="n">
-        <v>3867.02</v>
+        <v>3858.15</v>
       </c>
       <c r="E52" t="n">
-        <v>3885.33</v>
+        <v>3864.28</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.78</v>
+        <v>-21.05</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0007</v>
+        <v>-0.0054</v>
       </c>
       <c r="H52" t="n">
-        <v>28.49</v>
+        <v>33.47</v>
       </c>
       <c r="I52" t="n">
-        <v>3791.74</v>
+        <v>3838.53</v>
       </c>
       <c r="J52" t="n">
-        <v>3830.78</v>
+        <v>3858.88</v>
       </c>
       <c r="K52" t="n">
-        <v>3857.96</v>
+        <v>3871.09</v>
       </c>
       <c r="L52" t="n">
-        <v>3885.14</v>
+        <v>3883.3</v>
       </c>
       <c r="M52" t="n">
-        <v>3918.26</v>
+        <v>3899.58</v>
       </c>
       <c r="N52" t="n">
-        <v>3951.37</v>
+        <v>3915.86</v>
       </c>
       <c r="O52" t="n">
-        <v>3972.62</v>
+        <v>3924</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4896,146 +4898,148 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="10" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3879.73</v>
+        <v>3861.75</v>
       </c>
       <c r="C53" t="n">
-        <v>3891.62</v>
+        <v>3894.66</v>
       </c>
       <c r="D53" t="n">
-        <v>3858.15</v>
+        <v>3842.72</v>
       </c>
       <c r="E53" t="n">
-        <v>3864.28</v>
+        <v>3891.6</v>
       </c>
       <c r="F53" t="n">
-        <v>-21.05</v>
+        <v>27.32</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0054</v>
+        <v>0.0071</v>
       </c>
       <c r="H53" t="n">
-        <v>33.47</v>
+        <v>51.94</v>
       </c>
       <c r="I53" t="n">
-        <v>3838.53</v>
+        <v>3824.68</v>
       </c>
       <c r="J53" t="n">
-        <v>3858.88</v>
+        <v>3825.51</v>
       </c>
       <c r="K53" t="n">
-        <v>3871.09</v>
+        <v>3847.54</v>
       </c>
       <c r="L53" t="n">
-        <v>3883.3</v>
+        <v>3869.58</v>
       </c>
       <c r="M53" t="n">
-        <v>3899.58</v>
+        <v>3881.01</v>
       </c>
       <c r="N53" t="n">
-        <v>3915.86</v>
+        <v>3892.45</v>
       </c>
       <c r="O53" t="n">
-        <v>3924</v>
+        <v>3925.09</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="10" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3861.75</v>
+        <v>3877</v>
       </c>
       <c r="C54" t="n">
-        <v>3894.66</v>
+        <v>3898.84</v>
       </c>
       <c r="D54" t="n">
-        <v>3842.72</v>
+        <v>3866.89</v>
       </c>
       <c r="E54" t="n">
-        <v>3891.6</v>
+        <v>3875.6</v>
       </c>
       <c r="F54" t="n">
-        <v>27.32</v>
+        <v>-16</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.0041</v>
       </c>
       <c r="H54" t="n">
-        <v>51.94</v>
+        <v>31.94</v>
       </c>
       <c r="I54" t="n">
-        <v>3824.68</v>
+        <v>3790.78</v>
       </c>
       <c r="J54" t="n">
-        <v>3825.51</v>
+        <v>3851.11</v>
       </c>
       <c r="K54" t="n">
-        <v>3847.54</v>
+        <v>3865.63</v>
       </c>
       <c r="L54" t="n">
-        <v>3869.58</v>
+        <v>3880.15</v>
       </c>
       <c r="M54" t="n">
-        <v>3881.01</v>
+        <v>3917.57</v>
       </c>
       <c r="N54" t="n">
-        <v>3892.45</v>
+        <v>3955</v>
       </c>
       <c r="O54" t="n">
-        <v>3925.09</v>
+        <v>3946.61</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5043,30 +5047,24 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="10" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5080,50 +5078,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3877</v>
+        <v>3891.96</v>
       </c>
       <c r="C55" t="n">
-        <v>3898.84</v>
+        <v>3919.67</v>
       </c>
       <c r="D55" t="n">
-        <v>3866.89</v>
+        <v>3888.5</v>
       </c>
       <c r="E55" t="n">
-        <v>3875.6</v>
+        <v>3911.87</v>
       </c>
       <c r="F55" t="n">
-        <v>-16</v>
+        <v>36.27</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0041</v>
+        <v>0.0094</v>
       </c>
       <c r="H55" t="n">
-        <v>31.94</v>
+        <v>31.17</v>
       </c>
       <c r="I55" t="n">
-        <v>3790.78</v>
+        <v>3834.95</v>
       </c>
       <c r="J55" t="n">
-        <v>3851.11</v>
+        <v>3840.03</v>
       </c>
       <c r="K55" t="n">
-        <v>3865.63</v>
+        <v>3859.63</v>
       </c>
       <c r="L55" t="n">
-        <v>3880.15</v>
+        <v>3879.23</v>
       </c>
       <c r="M55" t="n">
-        <v>3917.57</v>
+        <v>3891.58</v>
       </c>
       <c r="N55" t="n">
-        <v>3955</v>
+        <v>3903.92</v>
       </c>
       <c r="O55" t="n">
-        <v>3946.61</v>
+        <v>3930.78</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5134,78 +5132,78 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>3891.96</v>
+        <v>3920.27</v>
       </c>
       <c r="C56" t="n">
-        <v>3919.67</v>
+        <v>3950.94</v>
       </c>
       <c r="D56" t="n">
-        <v>3888.5</v>
+        <v>3918.13</v>
       </c>
       <c r="E56" t="n">
-        <v>3911.87</v>
+        <v>3949.91</v>
       </c>
       <c r="F56" t="n">
-        <v>36.27</v>
+        <v>38.04</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0094</v>
+        <v>0.0097</v>
       </c>
       <c r="H56" t="n">
-        <v>31.17</v>
+        <v>32.81</v>
       </c>
       <c r="I56" t="n">
-        <v>3834.95</v>
+        <v>3857.32</v>
       </c>
       <c r="J56" t="n">
-        <v>3840.03</v>
+        <v>3884.59</v>
       </c>
       <c r="K56" t="n">
-        <v>3859.63</v>
+        <v>3896.28</v>
       </c>
       <c r="L56" t="n">
-        <v>3879.23</v>
+        <v>3907.98</v>
       </c>
       <c r="M56" t="n">
-        <v>3891.58</v>
+        <v>3927.46</v>
       </c>
       <c r="N56" t="n">
-        <v>3903.92</v>
+        <v>3946.94</v>
       </c>
       <c r="O56" t="n">
-        <v>3930.78</v>
+        <v>3950.84</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5216,7 +5214,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5228,13 +5226,15 @@
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5244,50 +5244,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3920.27</v>
+        <v>3963.81</v>
       </c>
       <c r="C57" t="n">
-        <v>3950.94</v>
+        <v>3967.68</v>
       </c>
       <c r="D57" t="n">
-        <v>3918.13</v>
+        <v>3945.42</v>
       </c>
       <c r="E57" t="n">
-        <v>3949.91</v>
+        <v>3952.13</v>
       </c>
       <c r="F57" t="n">
-        <v>38.04</v>
+        <v>2.22</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0097</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="H57" t="n">
-        <v>32.81</v>
+        <v>22.26</v>
       </c>
       <c r="I57" t="n">
-        <v>3857.32</v>
+        <v>3885.32</v>
       </c>
       <c r="J57" t="n">
-        <v>3884.59</v>
+        <v>3924.78</v>
       </c>
       <c r="K57" t="n">
-        <v>3896.28</v>
+        <v>3933.5</v>
       </c>
       <c r="L57" t="n">
-        <v>3907.98</v>
+        <v>3942.22</v>
       </c>
       <c r="M57" t="n">
-        <v>3927.46</v>
+        <v>3966.31</v>
       </c>
       <c r="N57" t="n">
-        <v>3946.94</v>
+        <v>3990.4</v>
       </c>
       <c r="O57" t="n">
-        <v>3950.84</v>
+        <v>3983.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5298,9 +5298,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5308,17 +5308,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+  